--- a/data/exports/毛毛矩阵/dist_order_2026-09-25.xlsx
+++ b/data/exports/毛毛矩阵/dist_order_2026-09-25.xlsx
@@ -125,11 +125,11 @@
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="0">
-        <v>50762997</v>
+        <v>50940389</v>
       </c>
       <c r="B2" s="0" t="inlineStr">
         <is>
-          <t>常旭东18834603378</t>
+          <t>相随爱💖GOD💖</t>
         </is>
       </c>
       <c r="C2" s="0" t="inlineStr">
@@ -154,7 +154,7 @@
       </c>
       <c r="G2" s="0" t="inlineStr">
         <is>
-          <t>2026-09-21 06:41:03</t>
+          <t>2026-09-25 07:05:19</t>
         </is>
       </c>
       <c r="H2" s="0" t="inlineStr">
@@ -185,11 +185,11 @@
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="0">
-        <v>50762949</v>
+        <v>50940253</v>
       </c>
       <c r="B3" s="0" t="inlineStr">
         <is>
-          <t>嵩岳侠客</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C3" s="0" t="inlineStr">
@@ -214,7 +214,7 @@
       </c>
       <c r="G3" s="0" t="inlineStr">
         <is>
-          <t>2026-09-21 06:39:57</t>
+          <t>2026-09-25 07:01:03</t>
         </is>
       </c>
       <c r="H3" s="0" t="inlineStr">
@@ -245,11 +245,11 @@
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="0">
-        <v>50762902</v>
+        <v>50939961</v>
       </c>
       <c r="B4" s="0" t="inlineStr">
         <is>
-          <t>伏鸿阁主</t>
+          <t>幸福一生：</t>
         </is>
       </c>
       <c r="C4" s="0" t="inlineStr">
@@ -274,7 +274,7 @@
       </c>
       <c r="G4" s="0" t="inlineStr">
         <is>
-          <t>2026-09-21 06:39:01</t>
+          <t>2026-09-25 06:51:55</t>
         </is>
       </c>
       <c r="H4" s="0" t="inlineStr">
@@ -305,11 +305,11 @@
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="0">
-        <v>50683336</v>
+        <v>50939805</v>
       </c>
       <c r="B5" s="0" t="inlineStr">
         <is>
-          <t>未来，（朝阳）</t>
+          <t>手风琴</t>
         </is>
       </c>
       <c r="C5" s="0" t="inlineStr">
@@ -334,7 +334,7 @@
       </c>
       <c r="G5" s="0" t="inlineStr">
         <is>
-          <t>2026-09-19 06:42:19</t>
+          <t>2026-09-25 06:47:43</t>
         </is>
       </c>
       <c r="H5" s="0" t="inlineStr">
@@ -365,11 +365,11 @@
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="0">
-        <v>50683317</v>
+        <v>50939730</v>
       </c>
       <c r="B6" s="0" t="inlineStr">
         <is>
-          <t>MaiRui</t>
+          <t>Wzj</t>
         </is>
       </c>
       <c r="C6" s="0" t="inlineStr">
@@ -394,7 +394,7 @@
       </c>
       <c r="G6" s="0" t="inlineStr">
         <is>
-          <t>2026-09-19 06:41:56</t>
+          <t>2026-09-25 06:45:49</t>
         </is>
       </c>
       <c r="H6" s="0" t="inlineStr">
@@ -425,11 +425,11 @@
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="0">
-        <v>50683272</v>
+        <v>50939702</v>
       </c>
       <c r="B7" s="0" t="inlineStr">
         <is>
-          <t>天蓝蓝</t>
+          <t>育俪</t>
         </is>
       </c>
       <c r="C7" s="0" t="inlineStr">
@@ -454,7 +454,7 @@
       </c>
       <c r="G7" s="0" t="inlineStr">
         <is>
-          <t>2026-09-19 06:41:05</t>
+          <t>2026-09-25 06:44:47</t>
         </is>
       </c>
       <c r="H7" s="0" t="inlineStr">
@@ -484,17 +484,17 @@
       </c>
       <c r="N7" s="0" t="inlineStr">
         <is>
-          <t>渭南</t>
+          <t>大连</t>
         </is>
       </c>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" s="0">
-        <v>50683240</v>
+        <v>50939694</v>
       </c>
       <c r="B8" s="0" t="inlineStr">
         <is>
-          <t>feng</t>
+          <t>杨素梅</t>
         </is>
       </c>
       <c r="C8" s="0" t="inlineStr">
@@ -519,7 +519,7 @@
       </c>
       <c r="G8" s="0" t="inlineStr">
         <is>
-          <t>2026-09-19 06:40:31</t>
+          <t>2026-09-25 06:44:29</t>
         </is>
       </c>
       <c r="H8" s="0" t="inlineStr">
@@ -550,11 +550,11 @@
     </row>
     <row r="9" spans="1:14">
       <c r="A9" s="0">
-        <v>50683233</v>
+        <v>50939686</v>
       </c>
       <c r="B9" s="0" t="inlineStr">
         <is>
-          <t>健康是福</t>
+          <t>前缘</t>
         </is>
       </c>
       <c r="C9" s="0" t="inlineStr">
@@ -579,7 +579,7 @@
       </c>
       <c r="G9" s="0" t="inlineStr">
         <is>
-          <t>2026-09-19 06:40:21</t>
+          <t>2026-09-25 06:44:15</t>
         </is>
       </c>
       <c r="H9" s="0" t="inlineStr">
@@ -610,11 +610,11 @@
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="0">
-        <v>50683231</v>
+        <v>50939677</v>
       </c>
       <c r="B10" s="0" t="inlineStr">
         <is>
-          <t>燕北郎</t>
+          <t>鸿源家俱18797549985</t>
         </is>
       </c>
       <c r="C10" s="0" t="inlineStr">
@@ -639,7 +639,7 @@
       </c>
       <c r="G10" s="0" t="inlineStr">
         <is>
-          <t>2026-09-19 06:40:16</t>
+          <t>2026-09-25 06:43:57</t>
         </is>
       </c>
       <c r="H10" s="0" t="inlineStr">
@@ -670,11 +670,11 @@
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="0">
-        <v>50683170</v>
+        <v>50939674</v>
       </c>
       <c r="B11" s="0" t="inlineStr">
         <is>
-          <t>汪俭</t>
+          <t>程大灿</t>
         </is>
       </c>
       <c r="C11" s="0" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="G11" s="0" t="inlineStr">
         <is>
-          <t>2026-09-19 06:38:59</t>
+          <t>2026-09-25 06:43:53</t>
         </is>
       </c>
       <c r="H11" s="0" t="inlineStr">
@@ -730,11 +730,11 @@
     </row>
     <row r="12" spans="1:14">
       <c r="A12" s="0">
-        <v>50683167</v>
+        <v>50762997</v>
       </c>
       <c r="B12" s="0" t="inlineStr">
         <is>
-          <t>顺儿</t>
+          <t>常旭东18834603378</t>
         </is>
       </c>
       <c r="C12" s="0" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="G12" s="0" t="inlineStr">
         <is>
-          <t>2026-09-19 06:38:55</t>
+          <t>2026-09-21 06:41:03</t>
         </is>
       </c>
       <c r="H12" s="0" t="inlineStr">
@@ -790,11 +790,11 @@
     </row>
     <row r="13" spans="1:14">
       <c r="A13" s="0">
-        <v>50683132</v>
+        <v>50762949</v>
       </c>
       <c r="B13" s="0" t="inlineStr">
         <is>
-          <t>秋雨</t>
+          <t>嵩岳侠客</t>
         </is>
       </c>
       <c r="C13" s="0" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="G13" s="0" t="inlineStr">
         <is>
-          <t>2026-09-19 06:38:29</t>
+          <t>2026-09-21 06:39:57</t>
         </is>
       </c>
       <c r="H13" s="0" t="inlineStr">
@@ -850,11 +850,11 @@
     </row>
     <row r="14" spans="1:14">
       <c r="A14" s="0">
-        <v>50683126</v>
+        <v>50762902</v>
       </c>
       <c r="B14" s="0" t="inlineStr">
         <is>
-          <t>老谷</t>
+          <t>伏鸿阁主</t>
         </is>
       </c>
       <c r="C14" s="0" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="G14" s="0" t="inlineStr">
         <is>
-          <t>2026-09-19 06:38:25</t>
+          <t>2026-09-21 06:39:01</t>
         </is>
       </c>
       <c r="H14" s="0" t="inlineStr">
@@ -910,11 +910,11 @@
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="0">
-        <v>50683123</v>
+        <v>50683336</v>
       </c>
       <c r="B15" s="0" t="inlineStr">
         <is>
-          <t>隆燊</t>
+          <t>未来，（朝阳）</t>
         </is>
       </c>
       <c r="C15" s="0" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="G15" s="0" t="inlineStr">
         <is>
-          <t>2026-09-19 06:38:23</t>
+          <t>2026-09-19 06:42:19</t>
         </is>
       </c>
       <c r="H15" s="0" t="inlineStr">
@@ -970,11 +970,11 @@
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="0">
-        <v>50683109</v>
+        <v>50683317</v>
       </c>
       <c r="B16" s="0" t="inlineStr">
         <is>
-          <t>Shero小洋</t>
+          <t>MaiRui</t>
         </is>
       </c>
       <c r="C16" s="0" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="G16" s="0" t="inlineStr">
         <is>
-          <t>2026-09-19 06:38:15</t>
+          <t>2026-09-19 06:41:56</t>
         </is>
       </c>
       <c r="H16" s="0" t="inlineStr">
@@ -1030,11 +1030,11 @@
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="0">
-        <v>50620394</v>
+        <v>50683272</v>
       </c>
       <c r="B17" s="0" t="inlineStr">
         <is>
-          <t>建建</t>
+          <t>天蓝蓝</t>
         </is>
       </c>
       <c r="C17" s="0" t="inlineStr">
@@ -1059,7 +1059,7 @@
       </c>
       <c r="G17" s="0" t="inlineStr">
         <is>
-          <t>2026-09-18 07:03:05</t>
+          <t>2026-09-19 06:41:05</t>
         </is>
       </c>
       <c r="H17" s="0" t="inlineStr">
@@ -1085,16 +1085,21 @@
       <c r="L17" s="0" t="inlineStr">
         <is>
           <t>已完成</t>
+        </is>
+      </c>
+      <c r="N17" s="0" t="inlineStr">
+        <is>
+          <t>渭南</t>
         </is>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="0">
-        <v>50619553</v>
+        <v>50683240</v>
       </c>
       <c r="B18" s="0" t="inlineStr">
         <is>
-          <t>杨姐</t>
+          <t>feng</t>
         </is>
       </c>
       <c r="C18" s="0" t="inlineStr">
@@ -1119,7 +1124,7 @@
       </c>
       <c r="G18" s="0" t="inlineStr">
         <is>
-          <t>2026-09-18 06:40:40</t>
+          <t>2026-09-19 06:40:31</t>
         </is>
       </c>
       <c r="H18" s="0" t="inlineStr">
@@ -1150,11 +1155,11 @@
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="0">
-        <v>50619520</v>
+        <v>50683233</v>
       </c>
       <c r="B19" s="0" t="inlineStr">
         <is>
-          <t>CYJ</t>
+          <t>健康是福</t>
         </is>
       </c>
       <c r="C19" s="0" t="inlineStr">
@@ -1179,7 +1184,7 @@
       </c>
       <c r="G19" s="0" t="inlineStr">
         <is>
-          <t>2026-09-18 06:39:37</t>
+          <t>2026-09-19 06:40:21</t>
         </is>
       </c>
       <c r="H19" s="0" t="inlineStr">
@@ -1210,11 +1215,11 @@
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="0">
-        <v>50619517</v>
+        <v>50683231</v>
       </c>
       <c r="B20" s="0" t="inlineStr">
         <is>
-          <t>张廷海</t>
+          <t>燕北郎</t>
         </is>
       </c>
       <c r="C20" s="0" t="inlineStr">
@@ -1239,7 +1244,7 @@
       </c>
       <c r="G20" s="0" t="inlineStr">
         <is>
-          <t>2026-09-18 06:39:33</t>
+          <t>2026-09-19 06:40:16</t>
         </is>
       </c>
       <c r="H20" s="0" t="inlineStr">
@@ -1270,11 +1275,11 @@
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="0">
-        <v>50619509</v>
+        <v>50683170</v>
       </c>
       <c r="B21" s="0" t="inlineStr">
         <is>
-          <t>【朵儿】*</t>
+          <t>汪俭</t>
         </is>
       </c>
       <c r="C21" s="0" t="inlineStr">
@@ -1299,7 +1304,7 @@
       </c>
       <c r="G21" s="0" t="inlineStr">
         <is>
-          <t>2026-09-18 06:39:22</t>
+          <t>2026-09-19 06:38:59</t>
         </is>
       </c>
       <c r="H21" s="0" t="inlineStr">
@@ -1330,11 +1335,11 @@
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="0">
-        <v>50619504</v>
+        <v>50683167</v>
       </c>
       <c r="B22" s="0" t="inlineStr">
         <is>
-          <t>跳蚤</t>
+          <t>顺儿</t>
         </is>
       </c>
       <c r="C22" s="0" t="inlineStr">
@@ -1359,7 +1364,7 @@
       </c>
       <c r="G22" s="0" t="inlineStr">
         <is>
-          <t>2026-09-18 06:39:10</t>
+          <t>2026-09-19 06:38:55</t>
         </is>
       </c>
       <c r="H22" s="0" t="inlineStr">
@@ -1390,11 +1395,11 @@
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="0">
-        <v>50619499</v>
+        <v>50683132</v>
       </c>
       <c r="B23" s="0" t="inlineStr">
         <is>
-          <t>赵豆豆</t>
+          <t>秋雨</t>
         </is>
       </c>
       <c r="C23" s="0" t="inlineStr">
@@ -1419,7 +1424,7 @@
       </c>
       <c r="G23" s="0" t="inlineStr">
         <is>
-          <t>2026-09-18 06:39:07</t>
+          <t>2026-09-19 06:38:29</t>
         </is>
       </c>
       <c r="H23" s="0" t="inlineStr">
@@ -1450,11 +1455,11 @@
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="0">
-        <v>50619496</v>
+        <v>50683126</v>
       </c>
       <c r="B24" s="0" t="inlineStr">
         <is>
-          <t>美好</t>
+          <t>老谷</t>
         </is>
       </c>
       <c r="C24" s="0" t="inlineStr">
@@ -1479,7 +1484,7 @@
       </c>
       <c r="G24" s="0" t="inlineStr">
         <is>
-          <t>2026-09-18 06:39:03</t>
+          <t>2026-09-19 06:38:25</t>
         </is>
       </c>
       <c r="H24" s="0" t="inlineStr">
@@ -1510,11 +1515,11 @@
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="0">
-        <v>50619492</v>
+        <v>50683123</v>
       </c>
       <c r="B25" s="0" t="inlineStr">
         <is>
-          <t>一粒沙</t>
+          <t>隆燊</t>
         </is>
       </c>
       <c r="C25" s="0" t="inlineStr">
@@ -1539,7 +1544,7 @@
       </c>
       <c r="G25" s="0" t="inlineStr">
         <is>
-          <t>2026-09-18 06:38:55</t>
+          <t>2026-09-19 06:38:23</t>
         </is>
       </c>
       <c r="H25" s="0" t="inlineStr">
@@ -1570,11 +1575,11 @@
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="0">
-        <v>50619491</v>
+        <v>50683109</v>
       </c>
       <c r="B26" s="0" t="inlineStr">
         <is>
-          <t>男人本色</t>
+          <t>Shero小洋</t>
         </is>
       </c>
       <c r="C26" s="0" t="inlineStr">
@@ -1599,7 +1604,7 @@
       </c>
       <c r="G26" s="0" t="inlineStr">
         <is>
-          <t>2026-09-18 06:38:51</t>
+          <t>2026-09-19 06:38:15</t>
         </is>
       </c>
       <c r="H26" s="0" t="inlineStr">
@@ -1630,11 +1635,11 @@
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="0">
-        <v>48029291</v>
+        <v>50620394</v>
       </c>
       <c r="B27" s="0" t="inlineStr">
         <is>
-          <t>YZF</t>
+          <t>建建</t>
         </is>
       </c>
       <c r="C27" s="0" t="inlineStr">
@@ -1659,7 +1664,7 @@
       </c>
       <c r="G27" s="0" t="inlineStr">
         <is>
-          <t>2026-07-15 16:34:57</t>
+          <t>2026-09-18 07:03:05</t>
         </is>
       </c>
       <c r="H27" s="0" t="inlineStr">
@@ -1669,7 +1674,7 @@
       </c>
       <c r="I27" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音5</t>
+          <t>常老师-抖音01</t>
         </is>
       </c>
       <c r="J27" s="0" t="inlineStr">
@@ -1690,11 +1695,11 @@
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="0">
-        <v>46516705</v>
+        <v>50619553</v>
       </c>
       <c r="B28" s="0" t="inlineStr">
         <is>
-          <t>砖家</t>
+          <t>杨姐</t>
         </is>
       </c>
       <c r="C28" s="0" t="inlineStr">
@@ -1719,7 +1724,7 @@
       </c>
       <c r="G28" s="0" t="inlineStr">
         <is>
-          <t>2026-06-03 10:22:41</t>
+          <t>2026-09-18 06:40:40</t>
         </is>
       </c>
       <c r="H28" s="0" t="inlineStr">
@@ -1729,7 +1734,7 @@
       </c>
       <c r="I28" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音5</t>
+          <t>常老师-抖音01</t>
         </is>
       </c>
       <c r="J28" s="0" t="inlineStr">
@@ -1750,11 +1755,11 @@
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="0">
-        <v>46301838</v>
+        <v>50619520</v>
       </c>
       <c r="B29" s="0" t="inlineStr">
         <is>
-          <t>xy^_^</t>
+          <t>CYJ</t>
         </is>
       </c>
       <c r="C29" s="0" t="inlineStr">
@@ -1779,7 +1784,7 @@
       </c>
       <c r="G29" s="0" t="inlineStr">
         <is>
-          <t>2026-05-27 15:14:57</t>
+          <t>2026-09-18 06:39:37</t>
         </is>
       </c>
       <c r="H29" s="0" t="inlineStr">
@@ -1789,7 +1794,7 @@
       </c>
       <c r="I29" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音9</t>
+          <t>常老师-抖音01</t>
         </is>
       </c>
       <c r="J29" s="0" t="inlineStr">
@@ -1810,11 +1815,11 @@
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="0">
-        <v>46301760</v>
+        <v>50619517</v>
       </c>
       <c r="B30" s="0" t="inlineStr">
         <is>
-          <t>四月🌞🌻</t>
+          <t>张廷海</t>
         </is>
       </c>
       <c r="C30" s="0" t="inlineStr">
@@ -1839,7 +1844,7 @@
       </c>
       <c r="G30" s="0" t="inlineStr">
         <is>
-          <t>2026-05-27 15:13:02</t>
+          <t>2026-09-18 06:39:33</t>
         </is>
       </c>
       <c r="H30" s="0" t="inlineStr">
@@ -1849,7 +1854,7 @@
       </c>
       <c r="I30" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音9</t>
+          <t>常老师-抖音01</t>
         </is>
       </c>
       <c r="J30" s="0" t="inlineStr">
@@ -1870,11 +1875,11 @@
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="0">
-        <v>46301758</v>
+        <v>50619509</v>
       </c>
       <c r="B31" s="0" t="inlineStr">
         <is>
-          <t>T^T</t>
+          <t>【朵儿】*</t>
         </is>
       </c>
       <c r="C31" s="0" t="inlineStr">
@@ -1899,7 +1904,7 @@
       </c>
       <c r="G31" s="0" t="inlineStr">
         <is>
-          <t>2026-05-27 15:12:51</t>
+          <t>2026-09-18 06:39:22</t>
         </is>
       </c>
       <c r="H31" s="0" t="inlineStr">
@@ -1909,7 +1914,7 @@
       </c>
       <c r="I31" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音9</t>
+          <t>常老师-抖音01</t>
         </is>
       </c>
       <c r="J31" s="0" t="inlineStr">
@@ -1930,11 +1935,11 @@
     </row>
     <row r="32" spans="1:14">
       <c r="A32" s="0">
-        <v>46301612</v>
+        <v>50619504</v>
       </c>
       <c r="B32" s="0" t="inlineStr">
         <is>
-          <t>相濡以沫</t>
+          <t>跳蚤</t>
         </is>
       </c>
       <c r="C32" s="0" t="inlineStr">
@@ -1959,7 +1964,7 @@
       </c>
       <c r="G32" s="0" t="inlineStr">
         <is>
-          <t>2026-05-27 15:07:39</t>
+          <t>2026-09-18 06:39:10</t>
         </is>
       </c>
       <c r="H32" s="0" t="inlineStr">
@@ -1969,7 +1974,7 @@
       </c>
       <c r="I32" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音8</t>
+          <t>常老师-抖音01</t>
         </is>
       </c>
       <c r="J32" s="0" t="inlineStr">
@@ -1990,11 +1995,11 @@
     </row>
     <row r="33" spans="1:14">
       <c r="A33" s="0">
-        <v>46301515</v>
+        <v>50619499</v>
       </c>
       <c r="B33" s="0" t="inlineStr">
         <is>
-          <t>吉祥婚庆婚礼花轿总策划师</t>
+          <t>赵豆豆</t>
         </is>
       </c>
       <c r="C33" s="0" t="inlineStr">
@@ -2019,7 +2024,7 @@
       </c>
       <c r="G33" s="0" t="inlineStr">
         <is>
-          <t>2026-05-27 15:05:29</t>
+          <t>2026-09-18 06:39:07</t>
         </is>
       </c>
       <c r="H33" s="0" t="inlineStr">
@@ -2029,7 +2034,7 @@
       </c>
       <c r="I33" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音8</t>
+          <t>常老师-抖音01</t>
         </is>
       </c>
       <c r="J33" s="0" t="inlineStr">
@@ -2050,11 +2055,11 @@
     </row>
     <row r="34" spans="1:14">
       <c r="A34" s="0">
-        <v>46299134</v>
+        <v>50619496</v>
       </c>
       <c r="B34" s="0" t="inlineStr">
         <is>
-          <t>明理童学</t>
+          <t>美好</t>
         </is>
       </c>
       <c r="C34" s="0" t="inlineStr">
@@ -2079,7 +2084,7 @@
       </c>
       <c r="G34" s="0" t="inlineStr">
         <is>
-          <t>2026-05-27 13:54:47</t>
+          <t>2026-09-18 06:39:03</t>
         </is>
       </c>
       <c r="H34" s="0" t="inlineStr">
@@ -2089,7 +2094,7 @@
       </c>
       <c r="I34" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音7</t>
+          <t>常老师-抖音01</t>
         </is>
       </c>
       <c r="J34" s="0" t="inlineStr">
@@ -2110,11 +2115,11 @@
     </row>
     <row r="35" spans="1:14">
       <c r="A35" s="0">
-        <v>46297028</v>
+        <v>50619492</v>
       </c>
       <c r="B35" s="0" t="inlineStr">
         <is>
-          <t>见清山</t>
+          <t>一粒沙</t>
         </is>
       </c>
       <c r="C35" s="0" t="inlineStr">
@@ -2139,7 +2144,7 @@
       </c>
       <c r="G35" s="0" t="inlineStr">
         <is>
-          <t>2026-05-27 13:02:07</t>
+          <t>2026-09-18 06:38:55</t>
         </is>
       </c>
       <c r="H35" s="0" t="inlineStr">
@@ -2149,7 +2154,7 @@
       </c>
       <c r="I35" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音5</t>
+          <t>常老师-抖音01</t>
         </is>
       </c>
       <c r="J35" s="0" t="inlineStr">
@@ -2170,11 +2175,11 @@
     </row>
     <row r="36" spans="1:14">
       <c r="A36" s="0">
-        <v>46296752</v>
+        <v>50619491</v>
       </c>
       <c r="B36" s="0" t="inlineStr">
         <is>
-          <t>时来运转</t>
+          <t>男人本色</t>
         </is>
       </c>
       <c r="C36" s="0" t="inlineStr">
@@ -2199,7 +2204,7 @@
       </c>
       <c r="G36" s="0" t="inlineStr">
         <is>
-          <t>2026-05-27 12:50:29</t>
+          <t>2026-09-18 06:38:51</t>
         </is>
       </c>
       <c r="H36" s="0" t="inlineStr">
@@ -2209,7 +2214,7 @@
       </c>
       <c r="I36" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音5</t>
+          <t>常老师-抖音01</t>
         </is>
       </c>
       <c r="J36" s="0" t="inlineStr">
@@ -2225,21 +2230,16 @@
       <c r="L36" s="0" t="inlineStr">
         <is>
           <t>已完成</t>
-        </is>
-      </c>
-      <c r="N36" s="0" t="inlineStr">
-        <is>
-          <t>吉林</t>
         </is>
       </c>
     </row>
     <row r="37" spans="1:14">
       <c r="A37" s="0">
-        <v>46294788</v>
+        <v>48029291</v>
       </c>
       <c r="B37" s="0" t="inlineStr">
         <is>
-          <t>A王💰跑</t>
+          <t>YZF</t>
         </is>
       </c>
       <c r="C37" s="0" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="G37" s="0" t="inlineStr">
         <is>
-          <t>2026-05-27 11:33:41</t>
+          <t>2026-07-15 16:34:57</t>
         </is>
       </c>
       <c r="H37" s="0" t="inlineStr">
@@ -2274,7 +2274,7 @@
       </c>
       <c r="I37" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音7</t>
+          <t>安迪-抖音5</t>
         </is>
       </c>
       <c r="J37" s="0" t="inlineStr">
@@ -2295,11 +2295,11 @@
     </row>
     <row r="38" spans="1:14">
       <c r="A38" s="0">
-        <v>46294456</v>
+        <v>46516705</v>
       </c>
       <c r="B38" s="0" t="inlineStr">
         <is>
-          <t>静水微澜</t>
+          <t>砖家</t>
         </is>
       </c>
       <c r="C38" s="0" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="G38" s="0" t="inlineStr">
         <is>
-          <t>2026-05-27 11:20:27</t>
+          <t>2026-06-03 10:22:41</t>
         </is>
       </c>
       <c r="H38" s="0" t="inlineStr">
@@ -2334,7 +2334,7 @@
       </c>
       <c r="I38" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音9</t>
+          <t>安迪-抖音5</t>
         </is>
       </c>
       <c r="J38" s="0" t="inlineStr">
@@ -2355,11 +2355,11 @@
     </row>
     <row r="39" spans="1:14">
       <c r="A39" s="0">
-        <v>46292260</v>
+        <v>46301838</v>
       </c>
       <c r="B39" s="0" t="inlineStr">
         <is>
-          <t>凉爽</t>
+          <t>xy^_^</t>
         </is>
       </c>
       <c r="C39" s="0" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="G39" s="0" t="inlineStr">
         <is>
-          <t>2026-05-27 09:54:25</t>
+          <t>2026-05-27 15:14:57</t>
         </is>
       </c>
       <c r="H39" s="0" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="I39" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音8</t>
+          <t>安迪-抖音9</t>
         </is>
       </c>
       <c r="J39" s="0" t="inlineStr">
@@ -2415,11 +2415,11 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="0">
-        <v>46291162</v>
+        <v>46301760</v>
       </c>
       <c r="B40" s="0" t="inlineStr">
         <is>
-          <t>巫miko🐰</t>
+          <t>四月🌞🌻</t>
         </is>
       </c>
       <c r="C40" s="0" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="G40" s="0" t="inlineStr">
         <is>
-          <t>2026-05-27 09:07:55</t>
+          <t>2026-05-27 15:13:02</t>
         </is>
       </c>
       <c r="H40" s="0" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="I40" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音5</t>
+          <t>安迪-抖音9</t>
         </is>
       </c>
       <c r="J40" s="0" t="inlineStr">
@@ -2475,11 +2475,11 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="0">
-        <v>46270040</v>
+        <v>46301758</v>
       </c>
       <c r="B41" s="0" t="inlineStr">
         <is>
-          <t>星辰</t>
+          <t>T^T</t>
         </is>
       </c>
       <c r="C41" s="0" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="G41" s="0" t="inlineStr">
         <is>
-          <t>2026-05-26 15:44:39</t>
+          <t>2026-05-27 15:12:51</t>
         </is>
       </c>
       <c r="H41" s="0" t="inlineStr">
@@ -2535,11 +2535,11 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="0">
-        <v>46269916</v>
+        <v>46301612</v>
       </c>
       <c r="B42" s="0" t="inlineStr">
         <is>
-          <t>一棵草</t>
+          <t>相濡以沫</t>
         </is>
       </c>
       <c r="C42" s="0" t="inlineStr">
@@ -2564,7 +2564,7 @@
       </c>
       <c r="G42" s="0" t="inlineStr">
         <is>
-          <t>2026-05-26 15:37:43</t>
+          <t>2026-05-27 15:07:39</t>
         </is>
       </c>
       <c r="H42" s="0" t="inlineStr">
@@ -2595,11 +2595,11 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="0">
-        <v>46269744</v>
+        <v>46301515</v>
       </c>
       <c r="B43" s="0" t="inlineStr">
         <is>
-          <t>莫失      莫忘🐌</t>
+          <t>吉祥婚庆婚礼花轿总策划师</t>
         </is>
       </c>
       <c r="C43" s="0" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="G43" s="0" t="inlineStr">
         <is>
-          <t>2026-05-26 15:29:41</t>
+          <t>2026-05-27 15:05:29</t>
         </is>
       </c>
       <c r="H43" s="0" t="inlineStr">
@@ -2655,11 +2655,11 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="0">
-        <v>46269485</v>
+        <v>46299134</v>
       </c>
       <c r="B44" s="0" t="inlineStr">
         <is>
-          <t>Sunflower🌻</t>
+          <t>明理童学</t>
         </is>
       </c>
       <c r="C44" s="0" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="G44" s="0" t="inlineStr">
         <is>
-          <t>2026-05-26 15:18:25</t>
+          <t>2026-05-27 13:54:47</t>
         </is>
       </c>
       <c r="H44" s="0" t="inlineStr">
@@ -2694,7 +2694,7 @@
       </c>
       <c r="I44" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音9</t>
+          <t>安迪-抖音7</t>
         </is>
       </c>
       <c r="J44" s="0" t="inlineStr">
@@ -2715,11 +2715,11 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="0">
-        <v>46269286</v>
+        <v>46297028</v>
       </c>
       <c r="B45" s="0" t="inlineStr">
         <is>
-          <t>王润琴</t>
+          <t>见清山</t>
         </is>
       </c>
       <c r="C45" s="0" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="G45" s="0" t="inlineStr">
         <is>
-          <t>2026-05-26 15:08:43</t>
+          <t>2026-05-27 13:02:07</t>
         </is>
       </c>
       <c r="H45" s="0" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="I45" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音8</t>
+          <t>安迪-抖音5</t>
         </is>
       </c>
       <c r="J45" s="0" t="inlineStr">
@@ -2775,11 +2775,11 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="0">
-        <v>46269283</v>
+        <v>46296752</v>
       </c>
       <c r="B46" s="0" t="inlineStr">
         <is>
-          <t>我爱我家</t>
+          <t>时来运转</t>
         </is>
       </c>
       <c r="C46" s="0" t="inlineStr">
@@ -2804,7 +2804,7 @@
       </c>
       <c r="G46" s="0" t="inlineStr">
         <is>
-          <t>2026-05-26 15:08:33</t>
+          <t>2026-05-27 12:50:29</t>
         </is>
       </c>
       <c r="H46" s="0" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="I46" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音8</t>
+          <t>安迪-抖音5</t>
         </is>
       </c>
       <c r="J46" s="0" t="inlineStr">
@@ -2830,16 +2830,21 @@
       <c r="L46" s="0" t="inlineStr">
         <is>
           <t>已完成</t>
+        </is>
+      </c>
+      <c r="N46" s="0" t="inlineStr">
+        <is>
+          <t>吉林</t>
         </is>
       </c>
     </row>
     <row r="47" spans="1:14">
       <c r="A47" s="0">
-        <v>46268055</v>
+        <v>46294788</v>
       </c>
       <c r="B47" s="0" t="inlineStr">
         <is>
-          <t>Macchiatto</t>
+          <t>A王💰跑</t>
         </is>
       </c>
       <c r="C47" s="0" t="inlineStr">
@@ -2864,7 +2869,7 @@
       </c>
       <c r="G47" s="0" t="inlineStr">
         <is>
-          <t>2026-05-26 14:18:19</t>
+          <t>2026-05-27 11:33:41</t>
         </is>
       </c>
       <c r="H47" s="0" t="inlineStr">
@@ -2895,11 +2900,11 @@
     </row>
     <row r="48" spans="1:14">
       <c r="A48" s="0">
-        <v>46267567</v>
+        <v>46294456</v>
       </c>
       <c r="B48" s="0" t="inlineStr">
         <is>
-          <t>健康快乐</t>
+          <t>静水微澜</t>
         </is>
       </c>
       <c r="C48" s="0" t="inlineStr">
@@ -2924,7 +2929,7 @@
       </c>
       <c r="G48" s="0" t="inlineStr">
         <is>
-          <t>2026-05-26 13:59:15</t>
+          <t>2026-05-27 11:20:27</t>
         </is>
       </c>
       <c r="H48" s="0" t="inlineStr">
@@ -2934,7 +2939,7 @@
       </c>
       <c r="I48" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音7</t>
+          <t>安迪-抖音9</t>
         </is>
       </c>
       <c r="J48" s="0" t="inlineStr">
@@ -2955,11 +2960,11 @@
     </row>
     <row r="49" spans="1:14">
       <c r="A49" s="0">
-        <v>46267441</v>
+        <v>46292260</v>
       </c>
       <c r="B49" s="0" t="inlineStr">
         <is>
-          <t>杨姐</t>
+          <t>凉爽</t>
         </is>
       </c>
       <c r="C49" s="0" t="inlineStr">
@@ -2984,7 +2989,7 @@
       </c>
       <c r="G49" s="0" t="inlineStr">
         <is>
-          <t>2026-05-26 13:53:29</t>
+          <t>2026-05-27 09:54:25</t>
         </is>
       </c>
       <c r="H49" s="0" t="inlineStr">
@@ -2994,7 +2999,7 @@
       </c>
       <c r="I49" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音7</t>
+          <t>安迪-抖音8</t>
         </is>
       </c>
       <c r="J49" s="0" t="inlineStr">
@@ -3015,11 +3020,11 @@
     </row>
     <row r="50" spans="1:14">
       <c r="A50" s="0">
-        <v>46266148</v>
+        <v>46291162</v>
       </c>
       <c r="B50" s="0" t="inlineStr">
         <is>
-          <t>🌸向阳花🌸</t>
+          <t>巫miko🐰</t>
         </is>
       </c>
       <c r="C50" s="0" t="inlineStr">
@@ -3044,7 +3049,7 @@
       </c>
       <c r="G50" s="0" t="inlineStr">
         <is>
-          <t>2026-05-26 12:54:33</t>
+          <t>2026-05-27 09:07:55</t>
         </is>
       </c>
       <c r="H50" s="0" t="inlineStr">
@@ -3075,11 +3080,11 @@
     </row>
     <row r="51" spans="1:14">
       <c r="A51" s="0">
-        <v>46265944</v>
+        <v>46270040</v>
       </c>
       <c r="B51" s="0" t="inlineStr">
         <is>
-          <t>货通联运～周君</t>
+          <t>星辰</t>
         </is>
       </c>
       <c r="C51" s="0" t="inlineStr">
@@ -3104,7 +3109,7 @@
       </c>
       <c r="G51" s="0" t="inlineStr">
         <is>
-          <t>2026-05-26 12:47:34</t>
+          <t>2026-05-26 15:44:39</t>
         </is>
       </c>
       <c r="H51" s="0" t="inlineStr">
@@ -3114,7 +3119,7 @@
       </c>
       <c r="I51" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音5</t>
+          <t>安迪-抖音9</t>
         </is>
       </c>
       <c r="J51" s="0" t="inlineStr">
@@ -3135,11 +3140,11 @@
     </row>
     <row r="52" spans="1:14">
       <c r="A52" s="0">
-        <v>46263571</v>
+        <v>46269916</v>
       </c>
       <c r="B52" s="0" t="inlineStr">
         <is>
-          <t>晓</t>
+          <t>一棵草</t>
         </is>
       </c>
       <c r="C52" s="0" t="inlineStr">
@@ -3164,7 +3169,7 @@
       </c>
       <c r="G52" s="0" t="inlineStr">
         <is>
-          <t>2026-05-26 11:24:01</t>
+          <t>2026-05-26 15:37:43</t>
         </is>
       </c>
       <c r="H52" s="0" t="inlineStr">
@@ -3174,7 +3179,7 @@
       </c>
       <c r="I52" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音9</t>
+          <t>安迪-抖音8</t>
         </is>
       </c>
       <c r="J52" s="0" t="inlineStr">
@@ -3195,11 +3200,11 @@
     </row>
     <row r="53" spans="1:14">
       <c r="A53" s="0">
-        <v>46263564</v>
+        <v>46269744</v>
       </c>
       <c r="B53" s="0" t="inlineStr">
         <is>
-          <t>💫</t>
+          <t>莫失      莫忘🐌</t>
         </is>
       </c>
       <c r="C53" s="0" t="inlineStr">
@@ -3224,7 +3229,7 @@
       </c>
       <c r="G53" s="0" t="inlineStr">
         <is>
-          <t>2026-05-26 11:23:50</t>
+          <t>2026-05-26 15:29:41</t>
         </is>
       </c>
       <c r="H53" s="0" t="inlineStr">
@@ -3234,7 +3239,7 @@
       </c>
       <c r="I53" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音9</t>
+          <t>安迪-抖音8</t>
         </is>
       </c>
       <c r="J53" s="0" t="inlineStr">
@@ -3255,11 +3260,11 @@
     </row>
     <row r="54" spans="1:14">
       <c r="A54" s="0">
-        <v>46263333</v>
+        <v>46269485</v>
       </c>
       <c r="B54" s="0" t="inlineStr">
         <is>
-          <t>心之旅</t>
+          <t>Sunflower🌻</t>
         </is>
       </c>
       <c r="C54" s="0" t="inlineStr">
@@ -3284,7 +3289,7 @@
       </c>
       <c r="G54" s="0" t="inlineStr">
         <is>
-          <t>2026-05-26 11:17:51</t>
+          <t>2026-05-26 15:18:25</t>
         </is>
       </c>
       <c r="H54" s="0" t="inlineStr">
@@ -3294,7 +3299,7 @@
       </c>
       <c r="I54" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音7</t>
+          <t>安迪-抖音9</t>
         </is>
       </c>
       <c r="J54" s="0" t="inlineStr">
@@ -3315,11 +3320,11 @@
     </row>
     <row r="55" spans="1:14">
       <c r="A55" s="0">
-        <v>46262162</v>
+        <v>46269286</v>
       </c>
       <c r="B55" s="0" t="inlineStr">
         <is>
-          <t>阳光刚刚好</t>
+          <t>王润琴</t>
         </is>
       </c>
       <c r="C55" s="0" t="inlineStr">
@@ -3344,7 +3349,7 @@
       </c>
       <c r="G55" s="0" t="inlineStr">
         <is>
-          <t>2026-05-26 10:36:19</t>
+          <t>2026-05-26 15:08:43</t>
         </is>
       </c>
       <c r="H55" s="0" t="inlineStr">
@@ -3354,7 +3359,7 @@
       </c>
       <c r="I55" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音7</t>
+          <t>安迪-抖音8</t>
         </is>
       </c>
       <c r="J55" s="0" t="inlineStr">
@@ -3375,11 +3380,11 @@
     </row>
     <row r="56" spans="1:14">
       <c r="A56" s="0">
-        <v>46262151</v>
+        <v>46269283</v>
       </c>
       <c r="B56" s="0" t="inlineStr">
         <is>
-          <t>李红军</t>
+          <t>我爱我家</t>
         </is>
       </c>
       <c r="C56" s="0" t="inlineStr">
@@ -3404,7 +3409,7 @@
       </c>
       <c r="G56" s="0" t="inlineStr">
         <is>
-          <t>2026-05-26 10:35:55</t>
+          <t>2026-05-26 15:08:33</t>
         </is>
       </c>
       <c r="H56" s="0" t="inlineStr">
@@ -3435,11 +3440,11 @@
     </row>
     <row r="57" spans="1:14">
       <c r="A57" s="0">
-        <v>46261361</v>
+        <v>46268055</v>
       </c>
       <c r="B57" s="0" t="inlineStr">
         <is>
-          <t>LING</t>
+          <t>Macchiatto</t>
         </is>
       </c>
       <c r="C57" s="0" t="inlineStr">
@@ -3464,7 +3469,7 @@
       </c>
       <c r="G57" s="0" t="inlineStr">
         <is>
-          <t>2026-05-26 10:09:23</t>
+          <t>2026-05-26 14:18:19</t>
         </is>
       </c>
       <c r="H57" s="0" t="inlineStr">
@@ -3474,7 +3479,7 @@
       </c>
       <c r="I57" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音8</t>
+          <t>安迪-抖音7</t>
         </is>
       </c>
       <c r="J57" s="0" t="inlineStr">
@@ -3495,11 +3500,11 @@
     </row>
     <row r="58" spans="1:14">
       <c r="A58" s="0">
-        <v>46238439</v>
+        <v>46267567</v>
       </c>
       <c r="B58" s="0" t="inlineStr">
         <is>
-          <t>枫叶红了</t>
+          <t>健康快乐</t>
         </is>
       </c>
       <c r="C58" s="0" t="inlineStr">
@@ -3524,7 +3529,7 @@
       </c>
       <c r="G58" s="0" t="inlineStr">
         <is>
-          <t>2026-05-25 15:40:13</t>
+          <t>2026-05-26 13:59:15</t>
         </is>
       </c>
       <c r="H58" s="0" t="inlineStr">
@@ -3534,7 +3539,7 @@
       </c>
       <c r="I58" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音9</t>
+          <t>安迪-抖音7</t>
         </is>
       </c>
       <c r="J58" s="0" t="inlineStr">
@@ -3555,11 +3560,11 @@
     </row>
     <row r="59" spans="1:14">
       <c r="A59" s="0">
-        <v>46238421</v>
+        <v>46267441</v>
       </c>
       <c r="B59" s="0" t="inlineStr">
         <is>
-          <t>观测员</t>
+          <t>杨姐</t>
         </is>
       </c>
       <c r="C59" s="0" t="inlineStr">
@@ -3584,7 +3589,7 @@
       </c>
       <c r="G59" s="0" t="inlineStr">
         <is>
-          <t>2026-05-25 15:39:15</t>
+          <t>2026-05-26 13:53:29</t>
         </is>
       </c>
       <c r="H59" s="0" t="inlineStr">
@@ -3615,11 +3620,11 @@
     </row>
     <row r="60" spans="1:14">
       <c r="A60" s="0">
-        <v>46237820</v>
+        <v>46266148</v>
       </c>
       <c r="B60" s="0" t="inlineStr">
         <is>
-          <t>Ting.y💛</t>
+          <t>🌸向阳花🌸</t>
         </is>
       </c>
       <c r="C60" s="0" t="inlineStr">
@@ -3644,7 +3649,7 @@
       </c>
       <c r="G60" s="0" t="inlineStr">
         <is>
-          <t>2026-05-25 15:17:49</t>
+          <t>2026-05-26 12:54:33</t>
         </is>
       </c>
       <c r="H60" s="0" t="inlineStr">
@@ -3654,7 +3659,7 @@
       </c>
       <c r="I60" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音8</t>
+          <t>安迪-抖音5</t>
         </is>
       </c>
       <c r="J60" s="0" t="inlineStr">
@@ -3675,11 +3680,11 @@
     </row>
     <row r="61" spans="1:14">
       <c r="A61" s="0">
-        <v>46237576</v>
+        <v>46265944</v>
       </c>
       <c r="B61" s="0" t="inlineStr">
         <is>
-          <t>茶喝到没味</t>
+          <t>货通联运～周君</t>
         </is>
       </c>
       <c r="C61" s="0" t="inlineStr">
@@ -3704,7 +3709,7 @@
       </c>
       <c r="G61" s="0" t="inlineStr">
         <is>
-          <t>2026-05-25 15:08:49</t>
+          <t>2026-05-26 12:47:34</t>
         </is>
       </c>
       <c r="H61" s="0" t="inlineStr">
@@ -3714,7 +3719,7 @@
       </c>
       <c r="I61" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音8</t>
+          <t>安迪-抖音5</t>
         </is>
       </c>
       <c r="J61" s="0" t="inlineStr">
@@ -3735,11 +3740,11 @@
     </row>
     <row r="62" spans="1:14">
       <c r="A62" s="0">
-        <v>46229108</v>
+        <v>46263571</v>
       </c>
       <c r="B62" s="0" t="inlineStr">
         <is>
-          <t>风雨同舟：锋</t>
+          <t>晓</t>
         </is>
       </c>
       <c r="C62" s="0" t="inlineStr">
@@ -3764,7 +3769,7 @@
       </c>
       <c r="G62" s="0" t="inlineStr">
         <is>
-          <t>2026-05-25 11:29:59</t>
+          <t>2026-05-26 11:24:01</t>
         </is>
       </c>
       <c r="H62" s="0" t="inlineStr">
@@ -3795,11 +3800,11 @@
     </row>
     <row r="63" spans="1:14">
       <c r="A63" s="0">
-        <v>46228931</v>
+        <v>46263564</v>
       </c>
       <c r="B63" s="0" t="inlineStr">
         <is>
-          <t>媛媛🍭</t>
+          <t>💫</t>
         </is>
       </c>
       <c r="C63" s="0" t="inlineStr">
@@ -3824,7 +3829,7 @@
       </c>
       <c r="G63" s="0" t="inlineStr">
         <is>
-          <t>2026-05-25 11:22:53</t>
+          <t>2026-05-26 11:23:50</t>
         </is>
       </c>
       <c r="H63" s="0" t="inlineStr">
@@ -3855,11 +3860,11 @@
     </row>
     <row r="64" spans="1:14">
       <c r="A64" s="0">
-        <v>46228254</v>
+        <v>46263333</v>
       </c>
       <c r="B64" s="0" t="inlineStr">
         <is>
-          <t>归于平静</t>
+          <t>心之旅</t>
         </is>
       </c>
       <c r="C64" s="0" t="inlineStr">
@@ -3884,7 +3889,7 @@
       </c>
       <c r="G64" s="0" t="inlineStr">
         <is>
-          <t>2026-05-25 10:57:17</t>
+          <t>2026-05-26 11:17:51</t>
         </is>
       </c>
       <c r="H64" s="0" t="inlineStr">
@@ -3915,11 +3920,11 @@
     </row>
     <row r="65" spans="1:14">
       <c r="A65" s="0">
-        <v>46228150</v>
+        <v>46262162</v>
       </c>
       <c r="B65" s="0" t="inlineStr">
         <is>
-          <t>黄女士</t>
+          <t>阳光刚刚好</t>
         </is>
       </c>
       <c r="C65" s="0" t="inlineStr">
@@ -3944,7 +3949,7 @@
       </c>
       <c r="G65" s="0" t="inlineStr">
         <is>
-          <t>2026-05-25 10:51:01</t>
+          <t>2026-05-26 10:36:19</t>
         </is>
       </c>
       <c r="H65" s="0" t="inlineStr">
@@ -3975,11 +3980,11 @@
     </row>
     <row r="66" spans="1:14">
       <c r="A66" s="0">
-        <v>46208231</v>
+        <v>46262151</v>
       </c>
       <c r="B66" s="0" t="inlineStr">
         <is>
-          <t>玲儿</t>
+          <t>李红军</t>
         </is>
       </c>
       <c r="C66" s="0" t="inlineStr">
@@ -4004,7 +4009,7 @@
       </c>
       <c r="G66" s="0" t="inlineStr">
         <is>
-          <t>2026-05-24 15:32:53</t>
+          <t>2026-05-26 10:35:55</t>
         </is>
       </c>
       <c r="H66" s="0" t="inlineStr">
@@ -4014,7 +4019,7 @@
       </c>
       <c r="I66" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音5</t>
+          <t>安迪-抖音8</t>
         </is>
       </c>
       <c r="J66" s="0" t="inlineStr">
@@ -4035,11 +4040,11 @@
     </row>
     <row r="67" spans="1:14">
       <c r="A67" s="0">
-        <v>46178493</v>
+        <v>46261361</v>
       </c>
       <c r="B67" s="0" t="inlineStr">
         <is>
-          <t>于水</t>
+          <t>LING</t>
         </is>
       </c>
       <c r="C67" s="0" t="inlineStr">
@@ -4064,7 +4069,7 @@
       </c>
       <c r="G67" s="0" t="inlineStr">
         <is>
-          <t>2026-05-23 15:38:59</t>
+          <t>2026-05-26 10:09:23</t>
         </is>
       </c>
       <c r="H67" s="0" t="inlineStr">
@@ -4074,7 +4079,7 @@
       </c>
       <c r="I67" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音9</t>
+          <t>安迪-抖音8</t>
         </is>
       </c>
       <c r="J67" s="0" t="inlineStr">
@@ -4095,11 +4100,11 @@
     </row>
     <row r="68" spans="1:14">
       <c r="A68" s="0">
-        <v>46178489</v>
+        <v>46238439</v>
       </c>
       <c r="B68" s="0" t="inlineStr">
         <is>
-          <t>利群五金</t>
+          <t>枫叶红了</t>
         </is>
       </c>
       <c r="C68" s="0" t="inlineStr">
@@ -4124,7 +4129,7 @@
       </c>
       <c r="G68" s="0" t="inlineStr">
         <is>
-          <t>2026-05-23 15:38:47</t>
+          <t>2026-05-25 15:40:13</t>
         </is>
       </c>
       <c r="H68" s="0" t="inlineStr">
@@ -4155,11 +4160,11 @@
     </row>
     <row r="69" spans="1:14">
       <c r="A69" s="0">
-        <v>46178467</v>
+        <v>46238421</v>
       </c>
       <c r="B69" s="0" t="inlineStr">
         <is>
-          <t>青禾</t>
+          <t>观测员</t>
         </is>
       </c>
       <c r="C69" s="0" t="inlineStr">
@@ -4184,7 +4189,7 @@
       </c>
       <c r="G69" s="0" t="inlineStr">
         <is>
-          <t>2026-05-23 15:37:31</t>
+          <t>2026-05-25 15:39:15</t>
         </is>
       </c>
       <c r="H69" s="0" t="inlineStr">
@@ -4194,7 +4199,7 @@
       </c>
       <c r="I69" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音9</t>
+          <t>安迪-抖音7</t>
         </is>
       </c>
       <c r="J69" s="0" t="inlineStr">
@@ -4215,11 +4220,11 @@
     </row>
     <row r="70" spans="1:14">
       <c r="A70" s="0">
-        <v>46178057</v>
+        <v>46237820</v>
       </c>
       <c r="B70" s="0" t="inlineStr">
         <is>
-          <t>anna</t>
+          <t>Ting.y💛</t>
         </is>
       </c>
       <c r="C70" s="0" t="inlineStr">
@@ -4244,7 +4249,7 @@
       </c>
       <c r="G70" s="0" t="inlineStr">
         <is>
-          <t>2026-05-23 15:18:17</t>
+          <t>2026-05-25 15:17:49</t>
         </is>
       </c>
       <c r="H70" s="0" t="inlineStr">
@@ -4254,7 +4259,7 @@
       </c>
       <c r="I70" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音9</t>
+          <t>安迪-抖音8</t>
         </is>
       </c>
       <c r="J70" s="0" t="inlineStr">
@@ -4275,11 +4280,11 @@
     </row>
     <row r="71" spans="1:14">
       <c r="A71" s="0">
-        <v>46178012</v>
+        <v>46237576</v>
       </c>
       <c r="B71" s="0" t="inlineStr">
         <is>
-          <t>劉龍</t>
+          <t>茶喝到没味</t>
         </is>
       </c>
       <c r="C71" s="0" t="inlineStr">
@@ -4304,7 +4309,7 @@
       </c>
       <c r="G71" s="0" t="inlineStr">
         <is>
-          <t>2026-05-23 15:16:07</t>
+          <t>2026-05-25 15:08:49</t>
         </is>
       </c>
       <c r="H71" s="0" t="inlineStr">
@@ -4314,7 +4319,7 @@
       </c>
       <c r="I71" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音9</t>
+          <t>安迪-抖音8</t>
         </is>
       </c>
       <c r="J71" s="0" t="inlineStr">
@@ -4335,11 +4340,11 @@
     </row>
     <row r="72" spans="1:14">
       <c r="A72" s="0">
-        <v>46178002</v>
+        <v>46229108</v>
       </c>
       <c r="B72" s="0" t="inlineStr">
         <is>
-          <t>杰</t>
+          <t>风雨同舟：锋</t>
         </is>
       </c>
       <c r="C72" s="0" t="inlineStr">
@@ -4364,7 +4369,7 @@
       </c>
       <c r="G72" s="0" t="inlineStr">
         <is>
-          <t>2026-05-23 15:15:19</t>
+          <t>2026-05-25 11:29:59</t>
         </is>
       </c>
       <c r="H72" s="0" t="inlineStr">
@@ -4395,11 +4400,11 @@
     </row>
     <row r="73" spans="1:14">
       <c r="A73" s="0">
-        <v>46172668</v>
+        <v>46228931</v>
       </c>
       <c r="B73" s="0" t="inlineStr">
         <is>
-          <t>ZHANGHAO</t>
+          <t>媛媛🍭</t>
         </is>
       </c>
       <c r="C73" s="0" t="inlineStr">
@@ -4424,7 +4429,7 @@
       </c>
       <c r="G73" s="0" t="inlineStr">
         <is>
-          <t>2026-05-23 11:44:37</t>
+          <t>2026-05-25 11:22:53</t>
         </is>
       </c>
       <c r="H73" s="0" t="inlineStr">
@@ -4455,11 +4460,11 @@
     </row>
     <row r="74" spans="1:14">
       <c r="A74" s="0">
-        <v>46172519</v>
+        <v>46228254</v>
       </c>
       <c r="B74" s="0" t="inlineStr">
         <is>
-          <t>SUSU</t>
+          <t>归于平静</t>
         </is>
       </c>
       <c r="C74" s="0" t="inlineStr">
@@ -4484,7 +4489,7 @@
       </c>
       <c r="G74" s="0" t="inlineStr">
         <is>
-          <t>2026-05-23 11:39:01</t>
+          <t>2026-05-25 10:57:17</t>
         </is>
       </c>
       <c r="H74" s="0" t="inlineStr">
@@ -4515,11 +4520,11 @@
     </row>
     <row r="75" spans="1:14">
       <c r="A75" s="0">
-        <v>46171959</v>
+        <v>46228150</v>
       </c>
       <c r="B75" s="0" t="inlineStr">
         <is>
-          <t>🐸🌸彭渝斐🌸</t>
+          <t>黄女士</t>
         </is>
       </c>
       <c r="C75" s="0" t="inlineStr">
@@ -4544,7 +4549,7 @@
       </c>
       <c r="G75" s="0" t="inlineStr">
         <is>
-          <t>2026-05-23 11:21:19</t>
+          <t>2026-05-25 10:51:01</t>
         </is>
       </c>
       <c r="H75" s="0" t="inlineStr">
@@ -4554,7 +4559,7 @@
       </c>
       <c r="I75" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音9</t>
+          <t>安迪-抖音7</t>
         </is>
       </c>
       <c r="J75" s="0" t="inlineStr">
@@ -4575,11 +4580,11 @@
     </row>
     <row r="76" spans="1:14">
       <c r="A76" s="0">
-        <v>46171818</v>
+        <v>46208231</v>
       </c>
       <c r="B76" s="0" t="inlineStr">
         <is>
-          <t>梦宇</t>
+          <t>玲儿</t>
         </is>
       </c>
       <c r="C76" s="0" t="inlineStr">
@@ -4604,7 +4609,7 @@
       </c>
       <c r="G76" s="0" t="inlineStr">
         <is>
-          <t>2026-05-23 11:18:05</t>
+          <t>2026-05-24 15:32:53</t>
         </is>
       </c>
       <c r="H76" s="0" t="inlineStr">
@@ -4614,7 +4619,7 @@
       </c>
       <c r="I76" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音9</t>
+          <t>安迪-抖音5</t>
         </is>
       </c>
       <c r="J76" s="0" t="inlineStr">
@@ -4635,11 +4640,11 @@
     </row>
     <row r="77" spans="1:14">
       <c r="A77" s="0">
-        <v>46171808</v>
+        <v>46178493</v>
       </c>
       <c r="B77" s="0" t="inlineStr">
         <is>
-          <t>苹</t>
+          <t>于水</t>
         </is>
       </c>
       <c r="C77" s="0" t="inlineStr">
@@ -4664,7 +4669,7 @@
       </c>
       <c r="G77" s="0" t="inlineStr">
         <is>
-          <t>2026-05-23 11:17:48</t>
+          <t>2026-05-23 15:38:59</t>
         </is>
       </c>
       <c r="H77" s="0" t="inlineStr">
@@ -4695,11 +4700,11 @@
     </row>
     <row r="78" spans="1:14">
       <c r="A78" s="0">
-        <v>46169937</v>
+        <v>46178489</v>
       </c>
       <c r="B78" s="0" t="inlineStr">
         <is>
-          <t></t>
+          <t>利群五金</t>
         </is>
       </c>
       <c r="C78" s="0" t="inlineStr">
@@ -4724,7 +4729,7 @@
       </c>
       <c r="G78" s="0" t="inlineStr">
         <is>
-          <t>2026-05-23 10:07:59</t>
+          <t>2026-05-23 15:38:47</t>
         </is>
       </c>
       <c r="H78" s="0" t="inlineStr">
@@ -4734,7 +4739,7 @@
       </c>
       <c r="I78" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音8</t>
+          <t>安迪-抖音9</t>
         </is>
       </c>
       <c r="J78" s="0" t="inlineStr">
@@ -4755,11 +4760,11 @@
     </row>
     <row r="79" spans="1:14">
       <c r="A79" s="0">
-        <v>46169334</v>
+        <v>46178467</v>
       </c>
       <c r="B79" s="0" t="inlineStr">
         <is>
-          <t>春华秋实</t>
+          <t>青禾</t>
         </is>
       </c>
       <c r="C79" s="0" t="inlineStr">
@@ -4784,7 +4789,7 @@
       </c>
       <c r="G79" s="0" t="inlineStr">
         <is>
-          <t>2026-05-23 09:48:01</t>
+          <t>2026-05-23 15:37:31</t>
         </is>
       </c>
       <c r="H79" s="0" t="inlineStr">
@@ -4794,7 +4799,7 @@
       </c>
       <c r="I79" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音5</t>
+          <t>安迪-抖音9</t>
         </is>
       </c>
       <c r="J79" s="0" t="inlineStr">
@@ -4815,11 +4820,11 @@
     </row>
     <row r="80" spans="1:14">
       <c r="A80" s="0">
-        <v>46168281</v>
+        <v>46178057</v>
       </c>
       <c r="B80" s="0" t="inlineStr">
         <is>
-          <t>黑白电视</t>
+          <t>anna</t>
         </is>
       </c>
       <c r="C80" s="0" t="inlineStr">
@@ -4844,7 +4849,7 @@
       </c>
       <c r="G80" s="0" t="inlineStr">
         <is>
-          <t>2026-05-23 09:10:45</t>
+          <t>2026-05-23 15:18:17</t>
         </is>
       </c>
       <c r="H80" s="0" t="inlineStr">
@@ -4854,7 +4859,7 @@
       </c>
       <c r="I80" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音5</t>
+          <t>安迪-抖音9</t>
         </is>
       </c>
       <c r="J80" s="0" t="inlineStr">
@@ -4875,11 +4880,11 @@
     </row>
     <row r="81" spans="1:14">
       <c r="A81" s="0">
-        <v>46168230</v>
+        <v>46178012</v>
       </c>
       <c r="B81" s="0" t="inlineStr">
         <is>
-          <t>水水</t>
+          <t>劉龍</t>
         </is>
       </c>
       <c r="C81" s="0" t="inlineStr">
@@ -4904,7 +4909,7 @@
       </c>
       <c r="G81" s="0" t="inlineStr">
         <is>
-          <t>2026-05-23 09:09:49</t>
+          <t>2026-05-23 15:16:07</t>
         </is>
       </c>
       <c r="H81" s="0" t="inlineStr">
@@ -4914,7 +4919,7 @@
       </c>
       <c r="I81" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音5</t>
+          <t>安迪-抖音9</t>
         </is>
       </c>
       <c r="J81" s="0" t="inlineStr">
@@ -4935,11 +4940,11 @@
     </row>
     <row r="82" spans="1:14">
       <c r="A82" s="0">
-        <v>46168193</v>
+        <v>46178002</v>
       </c>
       <c r="B82" s="0" t="inlineStr">
         <is>
-          <t>施瓦布的学生</t>
+          <t>杰</t>
         </is>
       </c>
       <c r="C82" s="0" t="inlineStr">
@@ -4964,7 +4969,7 @@
       </c>
       <c r="G82" s="0" t="inlineStr">
         <is>
-          <t>2026-05-23 09:08:55</t>
+          <t>2026-05-23 15:15:19</t>
         </is>
       </c>
       <c r="H82" s="0" t="inlineStr">
@@ -4974,7 +4979,7 @@
       </c>
       <c r="I82" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音5</t>
+          <t>安迪-抖音9</t>
         </is>
       </c>
       <c r="J82" s="0" t="inlineStr">
@@ -4990,21 +4995,16 @@
       <c r="L82" s="0" t="inlineStr">
         <is>
           <t>已完成</t>
-        </is>
-      </c>
-      <c r="N82" s="0" t="inlineStr">
-        <is>
-          <t>沈阳</t>
         </is>
       </c>
     </row>
     <row r="83" spans="1:14">
       <c r="A83" s="0">
-        <v>46168182</v>
+        <v>46172668</v>
       </c>
       <c r="B83" s="0" t="inlineStr">
         <is>
-          <t>光子</t>
+          <t>ZHANGHAO</t>
         </is>
       </c>
       <c r="C83" s="0" t="inlineStr">
@@ -5029,7 +5029,7 @@
       </c>
       <c r="G83" s="0" t="inlineStr">
         <is>
-          <t>2026-05-23 09:08:37</t>
+          <t>2026-05-23 11:44:37</t>
         </is>
       </c>
       <c r="H83" s="0" t="inlineStr">
@@ -5039,7 +5039,7 @@
       </c>
       <c r="I83" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音5</t>
+          <t>安迪-抖音9</t>
         </is>
       </c>
       <c r="J83" s="0" t="inlineStr">
@@ -5060,11 +5060,11 @@
     </row>
     <row r="84" spans="1:14">
       <c r="A84" s="0">
-        <v>46168174</v>
+        <v>46172519</v>
       </c>
       <c r="B84" s="0" t="inlineStr">
         <is>
-          <t>拼了！才会赢！</t>
+          <t>SUSU</t>
         </is>
       </c>
       <c r="C84" s="0" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="G84" s="0" t="inlineStr">
         <is>
-          <t>2026-05-23 09:08:21</t>
+          <t>2026-05-23 11:39:01</t>
         </is>
       </c>
       <c r="H84" s="0" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="I84" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音5</t>
+          <t>安迪-抖音7</t>
         </is>
       </c>
       <c r="J84" s="0" t="inlineStr">
@@ -5120,11 +5120,11 @@
     </row>
     <row r="85" spans="1:14">
       <c r="A85" s="0">
-        <v>46141687</v>
+        <v>46171959</v>
       </c>
       <c r="B85" s="0" t="inlineStr">
         <is>
-          <t>玖</t>
+          <t>🐸🌸彭渝斐🌸</t>
         </is>
       </c>
       <c r="C85" s="0" t="inlineStr">
@@ -5149,7 +5149,7 @@
       </c>
       <c r="G85" s="0" t="inlineStr">
         <is>
-          <t>2026-05-22 15:02:39</t>
+          <t>2026-05-23 11:21:19</t>
         </is>
       </c>
       <c r="H85" s="0" t="inlineStr">
@@ -5180,11 +5180,11 @@
     </row>
     <row r="86" spans="1:14">
       <c r="A86" s="0">
-        <v>46141668</v>
+        <v>46171818</v>
       </c>
       <c r="B86" s="0" t="inlineStr">
         <is>
-          <t>a妮💜🦜鹉噹π</t>
+          <t>梦宇</t>
         </is>
       </c>
       <c r="C86" s="0" t="inlineStr">
@@ -5209,7 +5209,7 @@
       </c>
       <c r="G86" s="0" t="inlineStr">
         <is>
-          <t>2026-05-22 15:02:03</t>
+          <t>2026-05-23 11:18:05</t>
         </is>
       </c>
       <c r="H86" s="0" t="inlineStr">
@@ -5240,11 +5240,11 @@
     </row>
     <row r="87" spans="1:14">
       <c r="A87" s="0">
-        <v>46140721</v>
+        <v>46171808</v>
       </c>
       <c r="B87" s="0" t="inlineStr">
         <is>
-          <t>吊车唐孝权13017237388</t>
+          <t>苹</t>
         </is>
       </c>
       <c r="C87" s="0" t="inlineStr">
@@ -5269,7 +5269,7 @@
       </c>
       <c r="G87" s="0" t="inlineStr">
         <is>
-          <t>2026-05-22 14:54:01</t>
+          <t>2026-05-23 11:17:48</t>
         </is>
       </c>
       <c r="H87" s="0" t="inlineStr">
@@ -5279,7 +5279,7 @@
       </c>
       <c r="I87" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音8</t>
+          <t>安迪-抖音9</t>
         </is>
       </c>
       <c r="J87" s="0" t="inlineStr">
@@ -5300,11 +5300,11 @@
     </row>
     <row r="88" spans="1:14">
       <c r="A88" s="0">
-        <v>46140425</v>
+        <v>46169937</v>
       </c>
       <c r="B88" s="0" t="inlineStr">
         <is>
-          <t>向阳而生</t>
+          <t></t>
         </is>
       </c>
       <c r="C88" s="0" t="inlineStr">
@@ -5329,7 +5329,7 @@
       </c>
       <c r="G88" s="0" t="inlineStr">
         <is>
-          <t>2026-05-22 14:42:47</t>
+          <t>2026-05-23 10:07:59</t>
         </is>
       </c>
       <c r="H88" s="0" t="inlineStr">
@@ -5360,11 +5360,11 @@
     </row>
     <row r="89" spans="1:14">
       <c r="A89" s="0">
-        <v>46139836</v>
+        <v>46169334</v>
       </c>
       <c r="B89" s="0" t="inlineStr">
         <is>
-          <t>丹丹</t>
+          <t>春华秋实</t>
         </is>
       </c>
       <c r="C89" s="0" t="inlineStr">
@@ -5389,7 +5389,7 @@
       </c>
       <c r="G89" s="0" t="inlineStr">
         <is>
-          <t>2026-05-22 14:18:17</t>
+          <t>2026-05-23 09:48:01</t>
         </is>
       </c>
       <c r="H89" s="0" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="I89" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音7</t>
+          <t>安迪-抖音5</t>
         </is>
       </c>
       <c r="J89" s="0" t="inlineStr">
@@ -5420,11 +5420,11 @@
     </row>
     <row r="90" spans="1:14">
       <c r="A90" s="0">
-        <v>46137839</v>
+        <v>46168281</v>
       </c>
       <c r="B90" s="0" t="inlineStr">
         <is>
-          <t>润物细无声</t>
+          <t>黑白电视</t>
         </is>
       </c>
       <c r="C90" s="0" t="inlineStr">
@@ -5449,7 +5449,7 @@
       </c>
       <c r="G90" s="0" t="inlineStr">
         <is>
-          <t>2026-05-22 12:57:29</t>
+          <t>2026-05-23 09:10:45</t>
         </is>
       </c>
       <c r="H90" s="0" t="inlineStr">
@@ -5480,11 +5480,11 @@
     </row>
     <row r="91" spans="1:14">
       <c r="A91" s="0">
-        <v>46136152</v>
+        <v>46168230</v>
       </c>
       <c r="B91" s="0" t="inlineStr">
         <is>
-          <t>🎀简爱🍒</t>
+          <t>水水</t>
         </is>
       </c>
       <c r="C91" s="0" t="inlineStr">
@@ -5509,7 +5509,7 @@
       </c>
       <c r="G91" s="0" t="inlineStr">
         <is>
-          <t>2026-05-22 11:46:49</t>
+          <t>2026-05-23 09:09:49</t>
         </is>
       </c>
       <c r="H91" s="0" t="inlineStr">
@@ -5519,7 +5519,7 @@
       </c>
       <c r="I91" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音9</t>
+          <t>安迪-抖音5</t>
         </is>
       </c>
       <c r="J91" s="0" t="inlineStr">
@@ -5540,11 +5540,11 @@
     </row>
     <row r="92" spans="1:14">
       <c r="A92" s="0">
-        <v>46136131</v>
+        <v>46168193</v>
       </c>
       <c r="B92" s="0" t="inlineStr">
         <is>
-          <t>大發</t>
+          <t>施瓦布的学生</t>
         </is>
       </c>
       <c r="C92" s="0" t="inlineStr">
@@ -5569,7 +5569,7 @@
       </c>
       <c r="G92" s="0" t="inlineStr">
         <is>
-          <t>2026-05-22 11:46:07</t>
+          <t>2026-05-23 09:08:55</t>
         </is>
       </c>
       <c r="H92" s="0" t="inlineStr">
@@ -5579,7 +5579,7 @@
       </c>
       <c r="I92" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音9</t>
+          <t>安迪-抖音5</t>
         </is>
       </c>
       <c r="J92" s="0" t="inlineStr">
@@ -5595,16 +5595,21 @@
       <c r="L92" s="0" t="inlineStr">
         <is>
           <t>已完成</t>
+        </is>
+      </c>
+      <c r="N92" s="0" t="inlineStr">
+        <is>
+          <t>沈阳</t>
         </is>
       </c>
     </row>
     <row r="93" spans="1:14">
       <c r="A93" s="0">
-        <v>46135540</v>
+        <v>46168182</v>
       </c>
       <c r="B93" s="0" t="inlineStr">
         <is>
-          <t>风轻云淡</t>
+          <t>光子</t>
         </is>
       </c>
       <c r="C93" s="0" t="inlineStr">
@@ -5629,7 +5634,7 @@
       </c>
       <c r="G93" s="0" t="inlineStr">
         <is>
-          <t>2026-05-22 11:23:36</t>
+          <t>2026-05-23 09:08:37</t>
         </is>
       </c>
       <c r="H93" s="0" t="inlineStr">
@@ -5639,7 +5644,7 @@
       </c>
       <c r="I93" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音9</t>
+          <t>安迪-抖音5</t>
         </is>
       </c>
       <c r="J93" s="0" t="inlineStr">
@@ -5660,11 +5665,11 @@
     </row>
     <row r="94" spans="1:14">
       <c r="A94" s="0">
-        <v>46135253</v>
+        <v>46168174</v>
       </c>
       <c r="B94" s="0" t="inlineStr">
         <is>
-          <t>归期.</t>
+          <t>拼了！才会赢！</t>
         </is>
       </c>
       <c r="C94" s="0" t="inlineStr">
@@ -5689,7 +5694,7 @@
       </c>
       <c r="G94" s="0" t="inlineStr">
         <is>
-          <t>2026-05-22 11:13:11</t>
+          <t>2026-05-23 09:08:21</t>
         </is>
       </c>
       <c r="H94" s="0" t="inlineStr">
@@ -5699,7 +5704,7 @@
       </c>
       <c r="I94" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音7</t>
+          <t>安迪-抖音5</t>
         </is>
       </c>
       <c r="J94" s="0" t="inlineStr">
@@ -5720,11 +5725,11 @@
     </row>
     <row r="95" spans="1:14">
       <c r="A95" s="0">
-        <v>46134952</v>
+        <v>46141687</v>
       </c>
       <c r="B95" s="0" t="inlineStr">
         <is>
-          <t>大周</t>
+          <t>玖</t>
         </is>
       </c>
       <c r="C95" s="0" t="inlineStr">
@@ -5749,7 +5754,7 @@
       </c>
       <c r="G95" s="0" t="inlineStr">
         <is>
-          <t>2026-05-22 11:02:55</t>
+          <t>2026-05-22 15:02:39</t>
         </is>
       </c>
       <c r="H95" s="0" t="inlineStr">
@@ -5780,11 +5785,11 @@
     </row>
     <row r="96" spans="1:14">
       <c r="A96" s="0">
-        <v>46134940</v>
+        <v>46141668</v>
       </c>
       <c r="B96" s="0" t="inlineStr">
         <is>
-          <t>ZX</t>
+          <t>a妮💜🦜鹉噹π</t>
         </is>
       </c>
       <c r="C96" s="0" t="inlineStr">
@@ -5809,7 +5814,7 @@
       </c>
       <c r="G96" s="0" t="inlineStr">
         <is>
-          <t>2026-05-22 11:02:11</t>
+          <t>2026-05-22 15:02:03</t>
         </is>
       </c>
       <c r="H96" s="0" t="inlineStr">
@@ -5840,11 +5845,11 @@
     </row>
     <row r="97" spans="1:14">
       <c r="A97" s="0">
-        <v>46134939</v>
+        <v>46140721</v>
       </c>
       <c r="B97" s="0" t="inlineStr">
         <is>
-          <t>Bella</t>
+          <t>吊车唐孝权13017237388</t>
         </is>
       </c>
       <c r="C97" s="0" t="inlineStr">
@@ -5869,7 +5874,7 @@
       </c>
       <c r="G97" s="0" t="inlineStr">
         <is>
-          <t>2026-05-22 11:02:03</t>
+          <t>2026-05-22 14:54:01</t>
         </is>
       </c>
       <c r="H97" s="0" t="inlineStr">
@@ -5879,7 +5884,7 @@
       </c>
       <c r="I97" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音9</t>
+          <t>安迪-抖音8</t>
         </is>
       </c>
       <c r="J97" s="0" t="inlineStr">
@@ -5900,11 +5905,11 @@
     </row>
     <row r="98" spans="1:14">
       <c r="A98" s="0">
-        <v>46132772</v>
+        <v>46140425</v>
       </c>
       <c r="B98" s="0" t="inlineStr">
         <is>
-          <t>海鸥</t>
+          <t>向阳而生</t>
         </is>
       </c>
       <c r="C98" s="0" t="inlineStr">
@@ -5929,7 +5934,7 @@
       </c>
       <c r="G98" s="0" t="inlineStr">
         <is>
-          <t>2026-05-22 09:40:01</t>
+          <t>2026-05-22 14:42:47</t>
         </is>
       </c>
       <c r="H98" s="0" t="inlineStr">
@@ -5939,7 +5944,7 @@
       </c>
       <c r="I98" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音5</t>
+          <t>安迪-抖音8</t>
         </is>
       </c>
       <c r="J98" s="0" t="inlineStr">
@@ -5960,11 +5965,11 @@
     </row>
     <row r="99" spans="1:14">
       <c r="A99" s="0">
-        <v>46130686</v>
+        <v>46139836</v>
       </c>
       <c r="B99" s="0" t="inlineStr">
         <is>
-          <t>老谢</t>
+          <t>丹丹</t>
         </is>
       </c>
       <c r="C99" s="0" t="inlineStr">
@@ -5989,7 +5994,7 @@
       </c>
       <c r="G99" s="0" t="inlineStr">
         <is>
-          <t>2026-05-22 08:26:17</t>
+          <t>2026-05-22 14:18:17</t>
         </is>
       </c>
       <c r="H99" s="0" t="inlineStr">
@@ -5999,7 +6004,7 @@
       </c>
       <c r="I99" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音5</t>
+          <t>安迪-抖音7</t>
         </is>
       </c>
       <c r="J99" s="0" t="inlineStr">
@@ -6020,11 +6025,11 @@
     </row>
     <row r="100" spans="1:14">
       <c r="A100" s="0">
-        <v>46107477</v>
+        <v>46137839</v>
       </c>
       <c r="B100" s="0" t="inlineStr">
         <is>
-          <t>尛’s</t>
+          <t>润物细无声</t>
         </is>
       </c>
       <c r="C100" s="0" t="inlineStr">
@@ -6049,7 +6054,7 @@
       </c>
       <c r="G100" s="0" t="inlineStr">
         <is>
-          <t>2026-05-21 15:48:59</t>
+          <t>2026-05-22 12:57:29</t>
         </is>
       </c>
       <c r="H100" s="0" t="inlineStr">
@@ -6059,7 +6064,7 @@
       </c>
       <c r="I100" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音9</t>
+          <t>安迪-抖音5</t>
         </is>
       </c>
       <c r="J100" s="0" t="inlineStr">
@@ -6080,11 +6085,11 @@
     </row>
     <row r="101" spans="1:14">
       <c r="A101" s="0">
-        <v>46107427</v>
+        <v>46136152</v>
       </c>
       <c r="B101" s="0" t="inlineStr">
         <is>
-          <t>橄榄树🍂💖</t>
+          <t>🎀简爱🍒</t>
         </is>
       </c>
       <c r="C101" s="0" t="inlineStr">
@@ -6109,7 +6114,7 @@
       </c>
       <c r="G101" s="0" t="inlineStr">
         <is>
-          <t>2026-05-21 15:47:59</t>
+          <t>2026-05-22 11:46:49</t>
         </is>
       </c>
       <c r="H101" s="0" t="inlineStr">
@@ -6140,11 +6145,11 @@
     </row>
     <row r="102" spans="1:14">
       <c r="A102" s="0">
-        <v>46107162</v>
+        <v>46136131</v>
       </c>
       <c r="B102" s="0" t="inlineStr">
         <is>
-          <t>明天更美好</t>
+          <t>大發</t>
         </is>
       </c>
       <c r="C102" s="0" t="inlineStr">
@@ -6169,7 +6174,7 @@
       </c>
       <c r="G102" s="0" t="inlineStr">
         <is>
-          <t>2026-05-21 15:41:15</t>
+          <t>2026-05-22 11:46:07</t>
         </is>
       </c>
       <c r="H102" s="0" t="inlineStr">
@@ -6179,7 +6184,7 @@
       </c>
       <c r="I102" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音8</t>
+          <t>安迪-抖音9</t>
         </is>
       </c>
       <c r="J102" s="0" t="inlineStr">
@@ -6200,11 +6205,11 @@
     </row>
     <row r="103" spans="1:14">
       <c r="A103" s="0">
-        <v>46107040</v>
+        <v>46135540</v>
       </c>
       <c r="B103" s="0" t="inlineStr">
         <is>
-          <t>欣悦</t>
+          <t>风轻云淡</t>
         </is>
       </c>
       <c r="C103" s="0" t="inlineStr">
@@ -6229,7 +6234,7 @@
       </c>
       <c r="G103" s="0" t="inlineStr">
         <is>
-          <t>2026-05-21 15:36:33</t>
+          <t>2026-05-22 11:23:36</t>
         </is>
       </c>
       <c r="H103" s="0" t="inlineStr">
@@ -6239,7 +6244,7 @@
       </c>
       <c r="I103" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音8</t>
+          <t>安迪-抖音9</t>
         </is>
       </c>
       <c r="J103" s="0" t="inlineStr">
@@ -6260,11 +6265,11 @@
     </row>
     <row r="104" spans="1:14">
       <c r="A104" s="0">
-        <v>46106350</v>
+        <v>46135253</v>
       </c>
       <c r="B104" s="0" t="inlineStr">
         <is>
-          <t>陈先生</t>
+          <t>归期.</t>
         </is>
       </c>
       <c r="C104" s="0" t="inlineStr">
@@ -6289,7 +6294,7 @@
       </c>
       <c r="G104" s="0" t="inlineStr">
         <is>
-          <t>2026-05-21 15:18:07</t>
+          <t>2026-05-22 11:13:11</t>
         </is>
       </c>
       <c r="H104" s="0" t="inlineStr">
@@ -6299,7 +6304,7 @@
       </c>
       <c r="I104" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音9</t>
+          <t>安迪-抖音7</t>
         </is>
       </c>
       <c r="J104" s="0" t="inlineStr">
@@ -6320,11 +6325,11 @@
     </row>
     <row r="105" spans="1:14">
       <c r="A105" s="0">
-        <v>46106274</v>
+        <v>46134952</v>
       </c>
       <c r="B105" s="0" t="inlineStr">
         <is>
-          <t>Laura</t>
+          <t>大周</t>
         </is>
       </c>
       <c r="C105" s="0" t="inlineStr">
@@ -6349,7 +6354,7 @@
       </c>
       <c r="G105" s="0" t="inlineStr">
         <is>
-          <t>2026-05-21 15:14:59</t>
+          <t>2026-05-22 11:02:55</t>
         </is>
       </c>
       <c r="H105" s="0" t="inlineStr">
@@ -6380,11 +6385,11 @@
     </row>
     <row r="106" spans="1:14">
       <c r="A106" s="0">
-        <v>46103296</v>
+        <v>46134940</v>
       </c>
       <c r="B106" s="0" t="inlineStr">
         <is>
-          <t>管工:胡春生13980662518</t>
+          <t>ZX</t>
         </is>
       </c>
       <c r="C106" s="0" t="inlineStr">
@@ -6409,7 +6414,7 @@
       </c>
       <c r="G106" s="0" t="inlineStr">
         <is>
-          <t>2026-05-21 14:05:47</t>
+          <t>2026-05-22 11:02:11</t>
         </is>
       </c>
       <c r="H106" s="0" t="inlineStr">
@@ -6419,7 +6424,7 @@
       </c>
       <c r="I106" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音7</t>
+          <t>安迪-抖音9</t>
         </is>
       </c>
       <c r="J106" s="0" t="inlineStr">
@@ -6440,11 +6445,11 @@
     </row>
     <row r="107" spans="1:14">
       <c r="A107" s="0">
-        <v>46099446</v>
+        <v>46134939</v>
       </c>
       <c r="B107" s="0" t="inlineStr">
         <is>
-          <t>七月</t>
+          <t>Bella</t>
         </is>
       </c>
       <c r="C107" s="0" t="inlineStr">
@@ -6469,7 +6474,7 @@
       </c>
       <c r="G107" s="0" t="inlineStr">
         <is>
-          <t>2026-05-21 12:20:37</t>
+          <t>2026-05-22 11:02:03</t>
         </is>
       </c>
       <c r="H107" s="0" t="inlineStr">
@@ -6479,7 +6484,7 @@
       </c>
       <c r="I107" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音5</t>
+          <t>安迪-抖音9</t>
         </is>
       </c>
       <c r="J107" s="0" t="inlineStr">
@@ -6500,11 +6505,11 @@
     </row>
     <row r="108" spans="1:14">
       <c r="A108" s="0">
-        <v>46098571</v>
+        <v>46132772</v>
       </c>
       <c r="B108" s="0" t="inlineStr">
         <is>
-          <t>Cecilia</t>
+          <t>海鸥</t>
         </is>
       </c>
       <c r="C108" s="0" t="inlineStr">
@@ -6529,7 +6534,7 @@
       </c>
       <c r="G108" s="0" t="inlineStr">
         <is>
-          <t>2026-05-21 11:42:37</t>
+          <t>2026-05-22 09:40:01</t>
         </is>
       </c>
       <c r="H108" s="0" t="inlineStr">
@@ -6539,7 +6544,7 @@
       </c>
       <c r="I108" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音9</t>
+          <t>安迪-抖音5</t>
         </is>
       </c>
       <c r="J108" s="0" t="inlineStr">
@@ -6560,11 +6565,11 @@
     </row>
     <row r="109" spans="1:14">
       <c r="A109" s="0">
-        <v>46097963</v>
+        <v>46130686</v>
       </c>
       <c r="B109" s="0" t="inlineStr">
         <is>
-          <t>Miu 苗</t>
+          <t>老谢</t>
         </is>
       </c>
       <c r="C109" s="0" t="inlineStr">
@@ -6589,7 +6594,7 @@
       </c>
       <c r="G109" s="0" t="inlineStr">
         <is>
-          <t>2026-05-21 11:17:53</t>
+          <t>2026-05-22 08:26:17</t>
         </is>
       </c>
       <c r="H109" s="0" t="inlineStr">
@@ -6599,7 +6604,7 @@
       </c>
       <c r="I109" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音9</t>
+          <t>安迪-抖音5</t>
         </is>
       </c>
       <c r="J109" s="0" t="inlineStr">
@@ -6620,11 +6625,11 @@
     </row>
     <row r="110" spans="1:14">
       <c r="A110" s="0">
-        <v>46097466</v>
+        <v>46107477</v>
       </c>
       <c r="B110" s="0" t="inlineStr">
         <is>
-          <t>A陈晨🐟探海刺身鱼生18007703998</t>
+          <t>尛’s</t>
         </is>
       </c>
       <c r="C110" s="0" t="inlineStr">
@@ -6649,7 +6654,7 @@
       </c>
       <c r="G110" s="0" t="inlineStr">
         <is>
-          <t>2026-05-21 10:57:27</t>
+          <t>2026-05-21 15:48:59</t>
         </is>
       </c>
       <c r="H110" s="0" t="inlineStr">
@@ -6680,11 +6685,11 @@
     </row>
     <row r="111" spans="1:14">
       <c r="A111" s="0">
-        <v>46096492</v>
+        <v>46107427</v>
       </c>
       <c r="B111" s="0" t="inlineStr">
         <is>
-          <t>木子（凯旋门350厅）15921106892</t>
+          <t>橄榄树🍂💖</t>
         </is>
       </c>
       <c r="C111" s="0" t="inlineStr">
@@ -6709,7 +6714,7 @@
       </c>
       <c r="G111" s="0" t="inlineStr">
         <is>
-          <t>2026-05-21 10:12:35</t>
+          <t>2026-05-21 15:47:59</t>
         </is>
       </c>
       <c r="H111" s="0" t="inlineStr">
@@ -6719,7 +6724,7 @@
       </c>
       <c r="I111" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音8</t>
+          <t>安迪-抖音9</t>
         </is>
       </c>
       <c r="J111" s="0" t="inlineStr">
@@ -6740,11 +6745,11 @@
     </row>
     <row r="112" spans="1:14">
       <c r="A112" s="0">
-        <v>46095244</v>
+        <v>46107162</v>
       </c>
       <c r="B112" s="0" t="inlineStr">
         <is>
-          <t>陈熙</t>
+          <t>明天更美好</t>
         </is>
       </c>
       <c r="C112" s="0" t="inlineStr">
@@ -6769,7 +6774,7 @@
       </c>
       <c r="G112" s="0" t="inlineStr">
         <is>
-          <t>2026-05-21 09:11:57</t>
+          <t>2026-05-21 15:41:15</t>
         </is>
       </c>
       <c r="H112" s="0" t="inlineStr">
@@ -6779,7 +6784,7 @@
       </c>
       <c r="I112" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音5</t>
+          <t>安迪-抖音8</t>
         </is>
       </c>
       <c r="J112" s="0" t="inlineStr">
@@ -6800,11 +6805,11 @@
     </row>
     <row r="113" spans="1:14">
       <c r="A113" s="0">
-        <v>46095148</v>
+        <v>46107040</v>
       </c>
       <c r="B113" s="0" t="inlineStr">
         <is>
-          <t>星星</t>
+          <t>欣悦</t>
         </is>
       </c>
       <c r="C113" s="0" t="inlineStr">
@@ -6829,7 +6834,7 @@
       </c>
       <c r="G113" s="0" t="inlineStr">
         <is>
-          <t>2026-05-21 09:08:03</t>
+          <t>2026-05-21 15:36:33</t>
         </is>
       </c>
       <c r="H113" s="0" t="inlineStr">
@@ -6839,7 +6844,7 @@
       </c>
       <c r="I113" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音5</t>
+          <t>安迪-抖音8</t>
         </is>
       </c>
       <c r="J113" s="0" t="inlineStr">
@@ -6860,11 +6865,11 @@
     </row>
     <row r="114" spans="1:14">
       <c r="A114" s="0">
-        <v>46095011</v>
+        <v>46106350</v>
       </c>
       <c r="B114" s="0" t="inlineStr">
         <is>
-          <t>丹妮</t>
+          <t>陈先生</t>
         </is>
       </c>
       <c r="C114" s="0" t="inlineStr">
@@ -6889,7 +6894,7 @@
       </c>
       <c r="G114" s="0" t="inlineStr">
         <is>
-          <t>2026-05-21 09:02:11</t>
+          <t>2026-05-21 15:18:07</t>
         </is>
       </c>
       <c r="H114" s="0" t="inlineStr">
@@ -6899,7 +6904,7 @@
       </c>
       <c r="I114" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音5</t>
+          <t>安迪-抖音9</t>
         </is>
       </c>
       <c r="J114" s="0" t="inlineStr">
@@ -6920,11 +6925,11 @@
     </row>
     <row r="115" spans="1:14">
       <c r="A115" s="0">
-        <v>46076634</v>
+        <v>46106274</v>
       </c>
       <c r="B115" s="0" t="inlineStr">
         <is>
-          <t>快乐人生</t>
+          <t>Laura</t>
         </is>
       </c>
       <c r="C115" s="0" t="inlineStr">
@@ -6949,7 +6954,7 @@
       </c>
       <c r="G115" s="0" t="inlineStr">
         <is>
-          <t>2026-05-20 18:32:47</t>
+          <t>2026-05-21 15:14:59</t>
         </is>
       </c>
       <c r="H115" s="0" t="inlineStr">
@@ -6959,7 +6964,7 @@
       </c>
       <c r="I115" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音8</t>
+          <t>安迪-抖音9</t>
         </is>
       </c>
       <c r="J115" s="0" t="inlineStr">
@@ -6980,11 +6985,11 @@
     </row>
     <row r="116" spans="1:14">
       <c r="A116" s="0">
-        <v>46070193</v>
+        <v>46103296</v>
       </c>
       <c r="B116" s="0" t="inlineStr">
         <is>
-          <t>水钰美食</t>
+          <t>管工:胡春生13980662518</t>
         </is>
       </c>
       <c r="C116" s="0" t="inlineStr">
@@ -7009,7 +7014,7 @@
       </c>
       <c r="G116" s="0" t="inlineStr">
         <is>
-          <t>2026-05-20 13:52:33</t>
+          <t>2026-05-21 14:05:47</t>
         </is>
       </c>
       <c r="H116" s="0" t="inlineStr">
@@ -7040,11 +7045,11 @@
     </row>
     <row r="117" spans="1:14">
       <c r="A117" s="0">
-        <v>46070062</v>
+        <v>46099446</v>
       </c>
       <c r="B117" s="0" t="inlineStr">
         <is>
-          <t>命运自有它的轨迹和理由</t>
+          <t>七月</t>
         </is>
       </c>
       <c r="C117" s="0" t="inlineStr">
@@ -7069,7 +7074,7 @@
       </c>
       <c r="G117" s="0" t="inlineStr">
         <is>
-          <t>2026-05-20 13:45:21</t>
+          <t>2026-05-21 12:20:37</t>
         </is>
       </c>
       <c r="H117" s="0" t="inlineStr">
@@ -7100,11 +7105,11 @@
     </row>
     <row r="118" spans="1:14">
       <c r="A118" s="0">
-        <v>46069438</v>
+        <v>46098571</v>
       </c>
       <c r="B118" s="0" t="inlineStr">
         <is>
-          <t>🍃</t>
+          <t>Cecilia</t>
         </is>
       </c>
       <c r="C118" s="0" t="inlineStr">
@@ -7129,7 +7134,7 @@
       </c>
       <c r="G118" s="0" t="inlineStr">
         <is>
-          <t>2026-05-20 13:16:35</t>
+          <t>2026-05-21 11:42:37</t>
         </is>
       </c>
       <c r="H118" s="0" t="inlineStr">
@@ -7139,7 +7144,7 @@
       </c>
       <c r="I118" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音5</t>
+          <t>安迪-抖音9</t>
         </is>
       </c>
       <c r="J118" s="0" t="inlineStr">
@@ -7160,11 +7165,11 @@
     </row>
     <row r="119" spans="1:14">
       <c r="A119" s="0">
-        <v>46068998</v>
+        <v>46097963</v>
       </c>
       <c r="B119" s="0" t="inlineStr">
         <is>
-          <t>伟</t>
+          <t>Miu 苗</t>
         </is>
       </c>
       <c r="C119" s="0" t="inlineStr">
@@ -7189,7 +7194,7 @@
       </c>
       <c r="G119" s="0" t="inlineStr">
         <is>
-          <t>2026-05-20 12:55:02</t>
+          <t>2026-05-21 11:17:53</t>
         </is>
       </c>
       <c r="H119" s="0" t="inlineStr">
@@ -7199,7 +7204,7 @@
       </c>
       <c r="I119" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音5</t>
+          <t>安迪-抖音9</t>
         </is>
       </c>
       <c r="J119" s="0" t="inlineStr">
@@ -7220,11 +7225,11 @@
     </row>
     <row r="120" spans="1:14">
       <c r="A120" s="0">
-        <v>46068927</v>
+        <v>46097466</v>
       </c>
       <c r="B120" s="0" t="inlineStr">
         <is>
-          <t>鸿雁</t>
+          <t>A陈晨🐟探海刺身鱼生18007703998</t>
         </is>
       </c>
       <c r="C120" s="0" t="inlineStr">
@@ -7249,7 +7254,7 @@
       </c>
       <c r="G120" s="0" t="inlineStr">
         <is>
-          <t>2026-05-20 12:51:51</t>
+          <t>2026-05-21 10:57:27</t>
         </is>
       </c>
       <c r="H120" s="0" t="inlineStr">
@@ -7259,7 +7264,7 @@
       </c>
       <c r="I120" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音5</t>
+          <t>安迪-抖音9</t>
         </is>
       </c>
       <c r="J120" s="0" t="inlineStr">
@@ -7280,11 +7285,11 @@
     </row>
     <row r="121" spans="1:14">
       <c r="A121" s="0">
-        <v>46068858</v>
+        <v>46096492</v>
       </c>
       <c r="B121" s="0" t="inlineStr">
         <is>
-          <t>peterpan</t>
+          <t>木子（凯旋门350厅）15921106892</t>
         </is>
       </c>
       <c r="C121" s="0" t="inlineStr">
@@ -7309,7 +7314,7 @@
       </c>
       <c r="G121" s="0" t="inlineStr">
         <is>
-          <t>2026-05-20 12:49:11</t>
+          <t>2026-05-21 10:12:35</t>
         </is>
       </c>
       <c r="H121" s="0" t="inlineStr">
@@ -7319,7 +7324,7 @@
       </c>
       <c r="I121" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音5</t>
+          <t>安迪-抖音8</t>
         </is>
       </c>
       <c r="J121" s="0" t="inlineStr">
@@ -7340,11 +7345,11 @@
     </row>
     <row r="122" spans="1:14">
       <c r="A122" s="0">
-        <v>46068851</v>
+        <v>46095244</v>
       </c>
       <c r="B122" s="0" t="inlineStr">
         <is>
-          <t>曼陀罗</t>
+          <t>陈熙</t>
         </is>
       </c>
       <c r="C122" s="0" t="inlineStr">
@@ -7369,7 +7374,7 @@
       </c>
       <c r="G122" s="0" t="inlineStr">
         <is>
-          <t>2026-05-20 12:48:51</t>
+          <t>2026-05-21 09:11:57</t>
         </is>
       </c>
       <c r="H122" s="0" t="inlineStr">
@@ -7400,11 +7405,11 @@
     </row>
     <row r="123" spans="1:14">
       <c r="A123" s="0">
-        <v>46064553</v>
+        <v>46095148</v>
       </c>
       <c r="B123" s="0" t="inlineStr">
         <is>
-          <t>慢慢</t>
+          <t>星星</t>
         </is>
       </c>
       <c r="C123" s="0" t="inlineStr">
@@ -7429,7 +7434,7 @@
       </c>
       <c r="G123" s="0" t="inlineStr">
         <is>
-          <t>2026-05-20 09:58:57</t>
+          <t>2026-05-21 09:08:03</t>
         </is>
       </c>
       <c r="H123" s="0" t="inlineStr">
@@ -7439,7 +7444,7 @@
       </c>
       <c r="I123" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音8</t>
+          <t>安迪-抖音5</t>
         </is>
       </c>
       <c r="J123" s="0" t="inlineStr">
@@ -7460,11 +7465,11 @@
     </row>
     <row r="124" spans="1:14">
       <c r="A124" s="0">
-        <v>46041504</v>
+        <v>46095011</v>
       </c>
       <c r="B124" s="0" t="inlineStr">
         <is>
-          <t>峰</t>
+          <t>丹妮</t>
         </is>
       </c>
       <c r="C124" s="0" t="inlineStr">
@@ -7489,7 +7494,7 @@
       </c>
       <c r="G124" s="0" t="inlineStr">
         <is>
-          <t>2026-05-19 15:22:47</t>
+          <t>2026-05-21 09:02:11</t>
         </is>
       </c>
       <c r="H124" s="0" t="inlineStr">
@@ -7499,7 +7504,7 @@
       </c>
       <c r="I124" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音9</t>
+          <t>安迪-抖音5</t>
         </is>
       </c>
       <c r="J124" s="0" t="inlineStr">
@@ -7520,11 +7525,11 @@
     </row>
     <row r="125" spans="1:14">
       <c r="A125" s="0">
-        <v>46035880</v>
+        <v>46076634</v>
       </c>
       <c r="B125" s="0" t="inlineStr">
         <is>
-          <t>知足者常乐</t>
+          <t>快乐人生</t>
         </is>
       </c>
       <c r="C125" s="0" t="inlineStr">
@@ -7549,7 +7554,7 @@
       </c>
       <c r="G125" s="0" t="inlineStr">
         <is>
-          <t>2026-05-19 14:45:01</t>
+          <t>2026-05-20 18:32:47</t>
         </is>
       </c>
       <c r="H125" s="0" t="inlineStr">
@@ -7559,7 +7564,7 @@
       </c>
       <c r="I125" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音5</t>
+          <t>安迪-抖音8</t>
         </is>
       </c>
       <c r="J125" s="0" t="inlineStr">
@@ -7580,11 +7585,11 @@
     </row>
     <row r="126" spans="1:14">
       <c r="A126" s="0">
-        <v>46031377</v>
+        <v>46070193</v>
       </c>
       <c r="B126" s="0" t="inlineStr">
         <is>
-          <t>玥芝🌅</t>
+          <t>水钰美食</t>
         </is>
       </c>
       <c r="C126" s="0" t="inlineStr">
@@ -7609,7 +7614,7 @@
       </c>
       <c r="G126" s="0" t="inlineStr">
         <is>
-          <t>2026-05-19 12:42:05</t>
+          <t>2026-05-20 13:52:33</t>
         </is>
       </c>
       <c r="H126" s="0" t="inlineStr">
@@ -7619,7 +7624,7 @@
       </c>
       <c r="I126" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音5</t>
+          <t>安迪-抖音7</t>
         </is>
       </c>
       <c r="J126" s="0" t="inlineStr">
@@ -7640,11 +7645,11 @@
     </row>
     <row r="127" spans="1:14">
       <c r="A127" s="0">
-        <v>46031189</v>
+        <v>46070062</v>
       </c>
       <c r="B127" s="0" t="inlineStr">
         <is>
-          <t>恋香花开</t>
+          <t>命运自有它的轨迹和理由</t>
         </is>
       </c>
       <c r="C127" s="0" t="inlineStr">
@@ -7669,7 +7674,7 @@
       </c>
       <c r="G127" s="0" t="inlineStr">
         <is>
-          <t>2026-05-19 12:36:29</t>
+          <t>2026-05-20 13:45:21</t>
         </is>
       </c>
       <c r="H127" s="0" t="inlineStr">
@@ -7700,11 +7705,11 @@
     </row>
     <row r="128" spans="1:14">
       <c r="A128" s="0">
-        <v>46029620</v>
+        <v>46069438</v>
       </c>
       <c r="B128" s="0" t="inlineStr">
         <is>
-          <t>👑Ava</t>
+          <t>🍃</t>
         </is>
       </c>
       <c r="C128" s="0" t="inlineStr">
@@ -7729,7 +7734,7 @@
       </c>
       <c r="G128" s="0" t="inlineStr">
         <is>
-          <t>2026-05-19 11:34:37</t>
+          <t>2026-05-20 13:16:35</t>
         </is>
       </c>
       <c r="H128" s="0" t="inlineStr">
@@ -7739,7 +7744,7 @@
       </c>
       <c r="I128" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音9</t>
+          <t>安迪-抖音5</t>
         </is>
       </c>
       <c r="J128" s="0" t="inlineStr">
@@ -7760,11 +7765,11 @@
     </row>
     <row r="129" spans="1:14">
       <c r="A129" s="0">
-        <v>46027132</v>
+        <v>46068998</v>
       </c>
       <c r="B129" s="0" t="inlineStr">
         <is>
-          <t>你的笑温暖每秒万志英6栋12楼03室</t>
+          <t>伟</t>
         </is>
       </c>
       <c r="C129" s="0" t="inlineStr">
@@ -7789,7 +7794,7 @@
       </c>
       <c r="G129" s="0" t="inlineStr">
         <is>
-          <t>2026-05-19 10:00:29</t>
+          <t>2026-05-20 12:55:02</t>
         </is>
       </c>
       <c r="H129" s="0" t="inlineStr">
@@ -7799,7 +7804,7 @@
       </c>
       <c r="I129" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音8</t>
+          <t>安迪-抖音5</t>
         </is>
       </c>
       <c r="J129" s="0" t="inlineStr">
@@ -7820,11 +7825,11 @@
     </row>
     <row r="130" spans="1:14">
       <c r="A130" s="0">
-        <v>46027131</v>
+        <v>46068927</v>
       </c>
       <c r="B130" s="0" t="inlineStr">
         <is>
-          <t>朱小希</t>
+          <t>鸿雁</t>
         </is>
       </c>
       <c r="C130" s="0" t="inlineStr">
@@ -7849,7 +7854,7 @@
       </c>
       <c r="G130" s="0" t="inlineStr">
         <is>
-          <t>2026-05-19 10:00:23</t>
+          <t>2026-05-20 12:51:51</t>
         </is>
       </c>
       <c r="H130" s="0" t="inlineStr">
@@ -7859,7 +7864,7 @@
       </c>
       <c r="I130" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音8</t>
+          <t>安迪-抖音5</t>
         </is>
       </c>
       <c r="J130" s="0" t="inlineStr">
@@ -7880,11 +7885,11 @@
     </row>
     <row r="131" spans="1:14">
       <c r="A131" s="0">
-        <v>46022421</v>
+        <v>46068858</v>
       </c>
       <c r="B131" s="0" t="inlineStr">
         <is>
-          <t>静若安然🎊</t>
+          <t>peterpan</t>
         </is>
       </c>
       <c r="C131" s="0" t="inlineStr">
@@ -7909,7 +7914,7 @@
       </c>
       <c r="G131" s="0" t="inlineStr">
         <is>
-          <t>2026-05-19 07:07:45</t>
+          <t>2026-05-20 12:49:11</t>
         </is>
       </c>
       <c r="H131" s="0" t="inlineStr">
@@ -7919,7 +7924,7 @@
       </c>
       <c r="I131" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音4</t>
+          <t>安迪-抖音5</t>
         </is>
       </c>
       <c r="J131" s="0" t="inlineStr">
@@ -7940,11 +7945,11 @@
     </row>
     <row r="132" spans="1:14">
       <c r="A132" s="0">
-        <v>46007972</v>
+        <v>46068851</v>
       </c>
       <c r="B132" s="0" t="inlineStr">
         <is>
-          <t>樊爱国</t>
+          <t>曼陀罗</t>
         </is>
       </c>
       <c r="C132" s="0" t="inlineStr">
@@ -7969,7 +7974,7 @@
       </c>
       <c r="G132" s="0" t="inlineStr">
         <is>
-          <t>2026-05-18 19:26:33</t>
+          <t>2026-05-20 12:48:51</t>
         </is>
       </c>
       <c r="H132" s="0" t="inlineStr">
@@ -8000,11 +8005,11 @@
     </row>
     <row r="133" spans="1:14">
       <c r="A133" s="0">
-        <v>46001184</v>
+        <v>46064553</v>
       </c>
       <c r="B133" s="0" t="inlineStr">
         <is>
-          <t>紫蝶</t>
+          <t>慢慢</t>
         </is>
       </c>
       <c r="C133" s="0" t="inlineStr">
@@ -8029,7 +8034,7 @@
       </c>
       <c r="G133" s="0" t="inlineStr">
         <is>
-          <t>2026-05-18 15:22:55</t>
+          <t>2026-05-20 09:58:57</t>
         </is>
       </c>
       <c r="H133" s="0" t="inlineStr">
@@ -8039,7 +8044,7 @@
       </c>
       <c r="I133" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音9</t>
+          <t>安迪-抖音8</t>
         </is>
       </c>
       <c r="J133" s="0" t="inlineStr">
@@ -8060,11 +8065,11 @@
     </row>
     <row r="134" spans="1:14">
       <c r="A134" s="0">
-        <v>46000484</v>
+        <v>46041504</v>
       </c>
       <c r="B134" s="0" t="inlineStr">
         <is>
-          <t>Aimee.Z💋</t>
+          <t>峰</t>
         </is>
       </c>
       <c r="C134" s="0" t="inlineStr">
@@ -8089,7 +8094,7 @@
       </c>
       <c r="G134" s="0" t="inlineStr">
         <is>
-          <t>2026-05-18 15:07:01</t>
+          <t>2026-05-19 15:22:47</t>
         </is>
       </c>
       <c r="H134" s="0" t="inlineStr">
@@ -8120,11 +8125,11 @@
     </row>
     <row r="135" spans="1:14">
       <c r="A135" s="0">
-        <v>46000461</v>
+        <v>46035880</v>
       </c>
       <c r="B135" s="0" t="inlineStr">
         <is>
-          <t>雨露</t>
+          <t>知足者常乐</t>
         </is>
       </c>
       <c r="C135" s="0" t="inlineStr">
@@ -8149,7 +8154,7 @@
       </c>
       <c r="G135" s="0" t="inlineStr">
         <is>
-          <t>2026-05-18 15:06:55</t>
+          <t>2026-05-19 14:45:01</t>
         </is>
       </c>
       <c r="H135" s="0" t="inlineStr">
@@ -8159,7 +8164,7 @@
       </c>
       <c r="I135" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音9</t>
+          <t>安迪-抖音5</t>
         </is>
       </c>
       <c r="J135" s="0" t="inlineStr">
@@ -8180,11 +8185,11 @@
     </row>
     <row r="136" spans="1:14">
       <c r="A136" s="0">
-        <v>46000438</v>
+        <v>46031377</v>
       </c>
       <c r="B136" s="0" t="inlineStr">
         <is>
-          <t>但行好事，莫问前程！</t>
+          <t>玥芝🌅</t>
         </is>
       </c>
       <c r="C136" s="0" t="inlineStr">
@@ -8209,7 +8214,7 @@
       </c>
       <c r="G136" s="0" t="inlineStr">
         <is>
-          <t>2026-05-18 15:06:37</t>
+          <t>2026-05-19 12:42:05</t>
         </is>
       </c>
       <c r="H136" s="0" t="inlineStr">
@@ -8219,7 +8224,7 @@
       </c>
       <c r="I136" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音9</t>
+          <t>安迪-抖音5</t>
         </is>
       </c>
       <c r="J136" s="0" t="inlineStr">
@@ -8240,11 +8245,11 @@
     </row>
     <row r="137" spans="1:14">
       <c r="A137" s="0">
-        <v>45992640</v>
+        <v>46031189</v>
       </c>
       <c r="B137" s="0" t="inlineStr">
         <is>
-          <t>麦田里的守望者🌤</t>
+          <t>恋香花开</t>
         </is>
       </c>
       <c r="C137" s="0" t="inlineStr">
@@ -8269,7 +8274,7 @@
       </c>
       <c r="G137" s="0" t="inlineStr">
         <is>
-          <t>2026-05-18 11:47:59</t>
+          <t>2026-05-19 12:36:29</t>
         </is>
       </c>
       <c r="H137" s="0" t="inlineStr">
@@ -8279,7 +8284,7 @@
       </c>
       <c r="I137" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音9</t>
+          <t>安迪-抖音5</t>
         </is>
       </c>
       <c r="J137" s="0" t="inlineStr">
@@ -8300,11 +8305,11 @@
     </row>
     <row r="138" spans="1:14">
       <c r="A138" s="0">
-        <v>45992100</v>
+        <v>46029620</v>
       </c>
       <c r="B138" s="0" t="inlineStr">
         <is>
-          <t>陈萍.18889728336</t>
+          <t>👑Ava</t>
         </is>
       </c>
       <c r="C138" s="0" t="inlineStr">
@@ -8329,7 +8334,7 @@
       </c>
       <c r="G138" s="0" t="inlineStr">
         <is>
-          <t>2026-05-18 11:26:53</t>
+          <t>2026-05-19 11:34:37</t>
         </is>
       </c>
       <c r="H138" s="0" t="inlineStr">
@@ -8360,11 +8365,11 @@
     </row>
     <row r="139" spans="1:14">
       <c r="A139" s="0">
-        <v>45992082</v>
+        <v>46027132</v>
       </c>
       <c r="B139" s="0" t="inlineStr">
         <is>
-          <t>小雨</t>
+          <t>你的笑温暖每秒万志英6栋12楼03室</t>
         </is>
       </c>
       <c r="C139" s="0" t="inlineStr">
@@ -8389,7 +8394,7 @@
       </c>
       <c r="G139" s="0" t="inlineStr">
         <is>
-          <t>2026-05-18 11:25:59</t>
+          <t>2026-05-19 10:00:29</t>
         </is>
       </c>
       <c r="H139" s="0" t="inlineStr">
@@ -8399,7 +8404,7 @@
       </c>
       <c r="I139" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音9</t>
+          <t>安迪-抖音8</t>
         </is>
       </c>
       <c r="J139" s="0" t="inlineStr">
@@ -8420,11 +8425,11 @@
     </row>
     <row r="140" spans="1:14">
       <c r="A140" s="0">
-        <v>45989727</v>
+        <v>46027131</v>
       </c>
       <c r="B140" s="0" t="inlineStr">
         <is>
-          <t>快乐达人</t>
+          <t>朱小希</t>
         </is>
       </c>
       <c r="C140" s="0" t="inlineStr">
@@ -8449,7 +8454,7 @@
       </c>
       <c r="G140" s="0" t="inlineStr">
         <is>
-          <t>2026-05-18 10:02:25</t>
+          <t>2026-05-19 10:00:23</t>
         </is>
       </c>
       <c r="H140" s="0" t="inlineStr">
@@ -8480,11 +8485,11 @@
     </row>
     <row r="141" spans="1:14">
       <c r="A141" s="0">
-        <v>45988781</v>
+        <v>46022421</v>
       </c>
       <c r="B141" s="0" t="inlineStr">
         <is>
-          <t>南暖北寒ℒᎭℯོ</t>
+          <t>静若安然🎊</t>
         </is>
       </c>
       <c r="C141" s="0" t="inlineStr">
@@ -8509,7 +8514,7 @@
       </c>
       <c r="G141" s="0" t="inlineStr">
         <is>
-          <t>2026-05-18 09:21:58</t>
+          <t>2026-05-19 07:07:45</t>
         </is>
       </c>
       <c r="H141" s="0" t="inlineStr">
@@ -8519,7 +8524,7 @@
       </c>
       <c r="I141" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音5</t>
+          <t>安迪-抖音4</t>
         </is>
       </c>
       <c r="J141" s="0" t="inlineStr">
@@ -8540,11 +8545,11 @@
     </row>
     <row r="142" spans="1:14">
       <c r="A142" s="0">
-        <v>45980140</v>
+        <v>46007972</v>
       </c>
       <c r="B142" s="0" t="inlineStr">
         <is>
-          <t>蓝天</t>
+          <t>樊爱国</t>
         </is>
       </c>
       <c r="C142" s="0" t="inlineStr">
@@ -8569,7 +8574,7 @@
       </c>
       <c r="G142" s="0" t="inlineStr">
         <is>
-          <t>2026-05-17 22:31:53</t>
+          <t>2026-05-18 19:26:33</t>
         </is>
       </c>
       <c r="H142" s="0" t="inlineStr">
@@ -8600,11 +8605,11 @@
     </row>
     <row r="143" spans="1:14">
       <c r="A143" s="0">
-        <v>45973125</v>
+        <v>46001184</v>
       </c>
       <c r="B143" s="0" t="inlineStr">
         <is>
-          <t>王小军  室内装修13622316219</t>
+          <t>紫蝶</t>
         </is>
       </c>
       <c r="C143" s="0" t="inlineStr">
@@ -8629,7 +8634,7 @@
       </c>
       <c r="G143" s="0" t="inlineStr">
         <is>
-          <t>2026-05-17 18:43:10</t>
+          <t>2026-05-18 15:22:55</t>
         </is>
       </c>
       <c r="H143" s="0" t="inlineStr">
@@ -8639,7 +8644,7 @@
       </c>
       <c r="I143" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音4</t>
+          <t>安迪-抖音9</t>
         </is>
       </c>
       <c r="J143" s="0" t="inlineStr">
@@ -8660,11 +8665,11 @@
     </row>
     <row r="144" spans="1:14">
       <c r="A144" s="0">
-        <v>45969758</v>
+        <v>46000484</v>
       </c>
       <c r="B144" s="0" t="inlineStr">
         <is>
-          <t>辰</t>
+          <t>Aimee.Z💋</t>
         </is>
       </c>
       <c r="C144" s="0" t="inlineStr">
@@ -8689,7 +8694,7 @@
       </c>
       <c r="G144" s="0" t="inlineStr">
         <is>
-          <t>2026-05-17 15:55:07</t>
+          <t>2026-05-18 15:07:01</t>
         </is>
       </c>
       <c r="H144" s="0" t="inlineStr">
@@ -8699,7 +8704,7 @@
       </c>
       <c r="I144" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音4</t>
+          <t>安迪-抖音9</t>
         </is>
       </c>
       <c r="J144" s="0" t="inlineStr">
@@ -8720,11 +8725,11 @@
     </row>
     <row r="145" spans="1:14">
       <c r="A145" s="0">
-        <v>45966498</v>
+        <v>46000461</v>
       </c>
       <c r="B145" s="0" t="inlineStr">
         <is>
-          <t>水中月</t>
+          <t>雨露</t>
         </is>
       </c>
       <c r="C145" s="0" t="inlineStr">
@@ -8749,7 +8754,7 @@
       </c>
       <c r="G145" s="0" t="inlineStr">
         <is>
-          <t>2026-05-17 13:37:49</t>
+          <t>2026-05-18 15:06:55</t>
         </is>
       </c>
       <c r="H145" s="0" t="inlineStr">
@@ -8759,7 +8764,7 @@
       </c>
       <c r="I145" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音5</t>
+          <t>安迪-抖音9</t>
         </is>
       </c>
       <c r="J145" s="0" t="inlineStr">
@@ -8775,21 +8780,16 @@
       <c r="L145" s="0" t="inlineStr">
         <is>
           <t>已完成</t>
-        </is>
-      </c>
-      <c r="N145" s="0" t="inlineStr">
-        <is>
-          <t>宝山</t>
         </is>
       </c>
     </row>
     <row r="146" spans="1:14">
       <c r="A146" s="0">
-        <v>45965827</v>
+        <v>46000438</v>
       </c>
       <c r="B146" s="0" t="inlineStr">
         <is>
-          <t>小微</t>
+          <t>但行好事，莫问前程！</t>
         </is>
       </c>
       <c r="C146" s="0" t="inlineStr">
@@ -8814,7 +8814,7 @@
       </c>
       <c r="G146" s="0" t="inlineStr">
         <is>
-          <t>2026-05-17 13:07:49</t>
+          <t>2026-05-18 15:06:37</t>
         </is>
       </c>
       <c r="H146" s="0" t="inlineStr">
@@ -8824,7 +8824,7 @@
       </c>
       <c r="I146" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音5</t>
+          <t>安迪-抖音9</t>
         </is>
       </c>
       <c r="J146" s="0" t="inlineStr">
@@ -8845,11 +8845,11 @@
     </row>
     <row r="147" spans="1:14">
       <c r="A147" s="0">
-        <v>45965682</v>
+        <v>45992640</v>
       </c>
       <c r="B147" s="0" t="inlineStr">
         <is>
-          <t>li</t>
+          <t>麦田里的守望者🌤</t>
         </is>
       </c>
       <c r="C147" s="0" t="inlineStr">
@@ -8874,7 +8874,7 @@
       </c>
       <c r="G147" s="0" t="inlineStr">
         <is>
-          <t>2026-05-17 13:01:15</t>
+          <t>2026-05-18 11:47:59</t>
         </is>
       </c>
       <c r="H147" s="0" t="inlineStr">
@@ -8884,7 +8884,7 @@
       </c>
       <c r="I147" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音5</t>
+          <t>安迪-抖音9</t>
         </is>
       </c>
       <c r="J147" s="0" t="inlineStr">
@@ -8905,11 +8905,11 @@
     </row>
     <row r="148" spans="1:14">
       <c r="A148" s="0">
-        <v>45965625</v>
+        <v>45992100</v>
       </c>
       <c r="B148" s="0" t="inlineStr">
         <is>
-          <t>浅笑安然</t>
+          <t>陈萍.18889728336</t>
         </is>
       </c>
       <c r="C148" s="0" t="inlineStr">
@@ -8934,7 +8934,7 @@
       </c>
       <c r="G148" s="0" t="inlineStr">
         <is>
-          <t>2026-05-17 12:58:53</t>
+          <t>2026-05-18 11:26:53</t>
         </is>
       </c>
       <c r="H148" s="0" t="inlineStr">
@@ -8944,7 +8944,7 @@
       </c>
       <c r="I148" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音5</t>
+          <t>安迪-抖音9</t>
         </is>
       </c>
       <c r="J148" s="0" t="inlineStr">
@@ -8965,11 +8965,11 @@
     </row>
     <row r="149" spans="1:14">
       <c r="A149" s="0">
-        <v>45965301</v>
+        <v>45992082</v>
       </c>
       <c r="B149" s="0" t="inlineStr">
         <is>
-          <t>ZCM</t>
+          <t>小雨</t>
         </is>
       </c>
       <c r="C149" s="0" t="inlineStr">
@@ -8994,7 +8994,7 @@
       </c>
       <c r="G149" s="0" t="inlineStr">
         <is>
-          <t>2026-05-17 12:46:11</t>
+          <t>2026-05-18 11:25:59</t>
         </is>
       </c>
       <c r="H149" s="0" t="inlineStr">
@@ -9004,7 +9004,7 @@
       </c>
       <c r="I149" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音5</t>
+          <t>安迪-抖音9</t>
         </is>
       </c>
       <c r="J149" s="0" t="inlineStr">
@@ -9025,11 +9025,11 @@
     </row>
     <row r="150" spans="1:14">
       <c r="A150" s="0">
-        <v>45965294</v>
+        <v>45989727</v>
       </c>
       <c r="B150" s="0" t="inlineStr">
         <is>
-          <t>鹤翔</t>
+          <t>快乐达人</t>
         </is>
       </c>
       <c r="C150" s="0" t="inlineStr">
@@ -9054,7 +9054,7 @@
       </c>
       <c r="G150" s="0" t="inlineStr">
         <is>
-          <t>2026-05-17 12:46:01</t>
+          <t>2026-05-18 10:02:25</t>
         </is>
       </c>
       <c r="H150" s="0" t="inlineStr">
@@ -9064,7 +9064,7 @@
       </c>
       <c r="I150" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音5</t>
+          <t>安迪-抖音8</t>
         </is>
       </c>
       <c r="J150" s="0" t="inlineStr">
@@ -9085,11 +9085,11 @@
     </row>
     <row r="151" spans="1:14">
       <c r="A151" s="0">
-        <v>45965289</v>
+        <v>45988781</v>
       </c>
       <c r="B151" s="0" t="inlineStr">
         <is>
-          <t>博爱</t>
+          <t>南暖北寒ℒᎭℯོ</t>
         </is>
       </c>
       <c r="C151" s="0" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="G151" s="0" t="inlineStr">
         <is>
-          <t>2026-05-17 12:45:47</t>
+          <t>2026-05-18 09:21:58</t>
         </is>
       </c>
       <c r="H151" s="0" t="inlineStr">
@@ -9145,11 +9145,11 @@
     </row>
     <row r="152" spans="1:14">
       <c r="A152" s="0">
-        <v>45948985</v>
+        <v>45980140</v>
       </c>
       <c r="B152" s="0" t="inlineStr">
         <is>
-          <t>💝xiaoli💝</t>
+          <t>蓝天</t>
         </is>
       </c>
       <c r="C152" s="0" t="inlineStr">
@@ -9174,7 +9174,7 @@
       </c>
       <c r="G152" s="0" t="inlineStr">
         <is>
-          <t>2026-05-16 22:19:19</t>
+          <t>2026-05-17 22:31:53</t>
         </is>
       </c>
       <c r="H152" s="0" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="I152" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音4</t>
+          <t>安迪-抖音5</t>
         </is>
       </c>
       <c r="J152" s="0" t="inlineStr">
@@ -9205,11 +9205,11 @@
     </row>
     <row r="153" spans="1:14">
       <c r="A153" s="0">
-        <v>45938159</v>
+        <v>45973125</v>
       </c>
       <c r="B153" s="0" t="inlineStr">
         <is>
-          <t>万事如意</t>
+          <t>王小军  室内装修13622316219</t>
         </is>
       </c>
       <c r="C153" s="0" t="inlineStr">
@@ -9234,7 +9234,7 @@
       </c>
       <c r="G153" s="0" t="inlineStr">
         <is>
-          <t>2026-05-16 15:42:09</t>
+          <t>2026-05-17 18:43:10</t>
         </is>
       </c>
       <c r="H153" s="0" t="inlineStr">
@@ -9244,7 +9244,7 @@
       </c>
       <c r="I153" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音9</t>
+          <t>安迪-抖音4</t>
         </is>
       </c>
       <c r="J153" s="0" t="inlineStr">
@@ -9265,11 +9265,11 @@
     </row>
     <row r="154" spans="1:14">
       <c r="A154" s="0">
-        <v>45937523</v>
+        <v>45969758</v>
       </c>
       <c r="B154" s="0" t="inlineStr">
         <is>
-          <t>我爱辣条&amp;</t>
+          <t>辰</t>
         </is>
       </c>
       <c r="C154" s="0" t="inlineStr">
@@ -9294,7 +9294,7 @@
       </c>
       <c r="G154" s="0" t="inlineStr">
         <is>
-          <t>2026-05-16 15:21:35</t>
+          <t>2026-05-17 15:55:07</t>
         </is>
       </c>
       <c r="H154" s="0" t="inlineStr">
@@ -9304,7 +9304,7 @@
       </c>
       <c r="I154" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音9</t>
+          <t>安迪-抖音4</t>
         </is>
       </c>
       <c r="J154" s="0" t="inlineStr">
@@ -9325,11 +9325,11 @@
     </row>
     <row r="155" spans="1:14">
       <c r="A155" s="0">
-        <v>45937081</v>
+        <v>45966498</v>
       </c>
       <c r="B155" s="0" t="inlineStr">
         <is>
-          <t>华</t>
+          <t>水中月</t>
         </is>
       </c>
       <c r="C155" s="0" t="inlineStr">
@@ -9354,7 +9354,7 @@
       </c>
       <c r="G155" s="0" t="inlineStr">
         <is>
-          <t>2026-05-16 15:05:37</t>
+          <t>2026-05-17 13:37:49</t>
         </is>
       </c>
       <c r="H155" s="0" t="inlineStr">
@@ -9364,7 +9364,7 @@
       </c>
       <c r="I155" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音9</t>
+          <t>安迪-抖音5</t>
         </is>
       </c>
       <c r="J155" s="0" t="inlineStr">
@@ -9380,16 +9380,21 @@
       <c r="L155" s="0" t="inlineStr">
         <is>
           <t>已完成</t>
+        </is>
+      </c>
+      <c r="N155" s="0" t="inlineStr">
+        <is>
+          <t>宝山</t>
         </is>
       </c>
     </row>
     <row r="156" spans="1:14">
       <c r="A156" s="0">
-        <v>45934501</v>
+        <v>45965827</v>
       </c>
       <c r="B156" s="0" t="inlineStr">
         <is>
-          <t>默默</t>
+          <t>小微</t>
         </is>
       </c>
       <c r="C156" s="0" t="inlineStr">
@@ -9414,7 +9419,7 @@
       </c>
       <c r="G156" s="0" t="inlineStr">
         <is>
-          <t>2026-05-16 13:36:54</t>
+          <t>2026-05-17 13:07:49</t>
         </is>
       </c>
       <c r="H156" s="0" t="inlineStr">
@@ -9445,11 +9450,11 @@
     </row>
     <row r="157" spans="1:14">
       <c r="A157" s="0">
-        <v>45934458</v>
+        <v>45965682</v>
       </c>
       <c r="B157" s="0" t="inlineStr">
         <is>
-          <t>芊眠.</t>
+          <t>li</t>
         </is>
       </c>
       <c r="C157" s="0" t="inlineStr">
@@ -9474,7 +9479,7 @@
       </c>
       <c r="G157" s="0" t="inlineStr">
         <is>
-          <t>2026-05-16 13:34:39</t>
+          <t>2026-05-17 13:01:15</t>
         </is>
       </c>
       <c r="H157" s="0" t="inlineStr">
@@ -9484,7 +9489,7 @@
       </c>
       <c r="I157" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音4</t>
+          <t>安迪-抖音5</t>
         </is>
       </c>
       <c r="J157" s="0" t="inlineStr">
@@ -9505,11 +9510,11 @@
     </row>
     <row r="158" spans="1:14">
       <c r="A158" s="0">
-        <v>45933730</v>
+        <v>45965625</v>
       </c>
       <c r="B158" s="0" t="inlineStr">
         <is>
-          <t>发发啊～</t>
+          <t>浅笑安然</t>
         </is>
       </c>
       <c r="C158" s="0" t="inlineStr">
@@ -9534,7 +9539,7 @@
       </c>
       <c r="G158" s="0" t="inlineStr">
         <is>
-          <t>2026-05-16 13:07:11</t>
+          <t>2026-05-17 12:58:53</t>
         </is>
       </c>
       <c r="H158" s="0" t="inlineStr">
@@ -9565,11 +9570,11 @@
     </row>
     <row r="159" spans="1:14">
       <c r="A159" s="0">
-        <v>45933697</v>
+        <v>45965301</v>
       </c>
       <c r="B159" s="0" t="inlineStr">
         <is>
-          <t>事缓圆人缓安</t>
+          <t>ZCM</t>
         </is>
       </c>
       <c r="C159" s="0" t="inlineStr">
@@ -9594,7 +9599,7 @@
       </c>
       <c r="G159" s="0" t="inlineStr">
         <is>
-          <t>2026-05-16 13:05:41</t>
+          <t>2026-05-17 12:46:11</t>
         </is>
       </c>
       <c r="H159" s="0" t="inlineStr">
@@ -9625,11 +9630,11 @@
     </row>
     <row r="160" spans="1:14">
       <c r="A160" s="0">
-        <v>45931075</v>
+        <v>45965294</v>
       </c>
       <c r="B160" s="0" t="inlineStr">
         <is>
-          <t>沐月🍒兰</t>
+          <t>鹤翔</t>
         </is>
       </c>
       <c r="C160" s="0" t="inlineStr">
@@ -9654,7 +9659,7 @@
       </c>
       <c r="G160" s="0" t="inlineStr">
         <is>
-          <t>2026-05-16 11:36:15</t>
+          <t>2026-05-17 12:46:01</t>
         </is>
       </c>
       <c r="H160" s="0" t="inlineStr">
@@ -9664,7 +9669,7 @@
       </c>
       <c r="I160" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音7</t>
+          <t>安迪-抖音5</t>
         </is>
       </c>
       <c r="J160" s="0" t="inlineStr">
@@ -9685,11 +9690,11 @@
     </row>
     <row r="161" spans="1:14">
       <c r="A161" s="0">
-        <v>45928730</v>
+        <v>45965289</v>
       </c>
       <c r="B161" s="0" t="inlineStr">
         <is>
-          <t>sky</t>
+          <t>博爱</t>
         </is>
       </c>
       <c r="C161" s="0" t="inlineStr">
@@ -9714,7 +9719,7 @@
       </c>
       <c r="G161" s="0" t="inlineStr">
         <is>
-          <t>2026-05-16 10:22:07</t>
+          <t>2026-05-17 12:45:47</t>
         </is>
       </c>
       <c r="H161" s="0" t="inlineStr">
@@ -9724,7 +9729,7 @@
       </c>
       <c r="I161" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音8</t>
+          <t>安迪-抖音5</t>
         </is>
       </c>
       <c r="J161" s="0" t="inlineStr">
@@ -9745,11 +9750,11 @@
     </row>
     <row r="162" spans="1:14">
       <c r="A162" s="0">
-        <v>45928692</v>
+        <v>45948985</v>
       </c>
       <c r="B162" s="0" t="inlineStr">
         <is>
-          <t>蓝天</t>
+          <t>💝xiaoli💝</t>
         </is>
       </c>
       <c r="C162" s="0" t="inlineStr">
@@ -9774,7 +9779,7 @@
       </c>
       <c r="G162" s="0" t="inlineStr">
         <is>
-          <t>2026-05-16 10:20:17</t>
+          <t>2026-05-16 22:19:19</t>
         </is>
       </c>
       <c r="H162" s="0" t="inlineStr">
@@ -9784,7 +9789,7 @@
       </c>
       <c r="I162" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音8</t>
+          <t>安迪-抖音4</t>
         </is>
       </c>
       <c r="J162" s="0" t="inlineStr">
@@ -9805,11 +9810,11 @@
     </row>
     <row r="163" spans="1:14">
       <c r="A163" s="0">
-        <v>45900431</v>
+        <v>45938159</v>
       </c>
       <c r="B163" s="0" t="inlineStr">
         <is>
-          <t>A燕子</t>
+          <t>万事如意</t>
         </is>
       </c>
       <c r="C163" s="0" t="inlineStr">
@@ -9834,7 +9839,7 @@
       </c>
       <c r="G163" s="0" t="inlineStr">
         <is>
-          <t>2026-05-15 15:18:35</t>
+          <t>2026-05-16 15:42:09</t>
         </is>
       </c>
       <c r="H163" s="0" t="inlineStr">
@@ -9865,11 +9870,11 @@
     </row>
     <row r="164" spans="1:14">
       <c r="A164" s="0">
-        <v>45900357</v>
+        <v>45937523</v>
       </c>
       <c r="B164" s="0" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>我爱辣条&amp;</t>
         </is>
       </c>
       <c r="C164" s="0" t="inlineStr">
@@ -9894,7 +9899,7 @@
       </c>
       <c r="G164" s="0" t="inlineStr">
         <is>
-          <t>2026-05-15 15:16:49</t>
+          <t>2026-05-16 15:21:35</t>
         </is>
       </c>
       <c r="H164" s="0" t="inlineStr">
@@ -9925,11 +9930,11 @@
     </row>
     <row r="165" spans="1:14">
       <c r="A165" s="0">
-        <v>45891970</v>
+        <v>45937081</v>
       </c>
       <c r="B165" s="0" t="inlineStr">
         <is>
-          <t>XIao王</t>
+          <t>华</t>
         </is>
       </c>
       <c r="C165" s="0" t="inlineStr">
@@ -9954,7 +9959,7 @@
       </c>
       <c r="G165" s="0" t="inlineStr">
         <is>
-          <t>2026-05-15 11:19:35</t>
+          <t>2026-05-16 15:05:37</t>
         </is>
       </c>
       <c r="H165" s="0" t="inlineStr">
@@ -9964,7 +9969,7 @@
       </c>
       <c r="I165" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音7</t>
+          <t>安迪-抖音9</t>
         </is>
       </c>
       <c r="J165" s="0" t="inlineStr">
@@ -9985,11 +9990,11 @@
     </row>
     <row r="166" spans="1:14">
       <c r="A166" s="0">
-        <v>45864167</v>
+        <v>45934501</v>
       </c>
       <c r="B166" s="0" t="inlineStr">
         <is>
-          <t>黑妹</t>
+          <t>默默</t>
         </is>
       </c>
       <c r="C166" s="0" t="inlineStr">
@@ -10014,7 +10019,7 @@
       </c>
       <c r="G166" s="0" t="inlineStr">
         <is>
-          <t>2026-05-14 15:04:03</t>
+          <t>2026-05-16 13:36:54</t>
         </is>
       </c>
       <c r="H166" s="0" t="inlineStr">
@@ -10024,7 +10029,7 @@
       </c>
       <c r="I166" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音9</t>
+          <t>安迪-抖音5</t>
         </is>
       </c>
       <c r="J166" s="0" t="inlineStr">
@@ -10045,11 +10050,11 @@
     </row>
     <row r="167" spans="1:14">
       <c r="A167" s="0">
-        <v>45861458</v>
+        <v>45934458</v>
       </c>
       <c r="B167" s="0" t="inlineStr">
         <is>
-          <t>ʚ陈玲ɞ</t>
+          <t>芊眠.</t>
         </is>
       </c>
       <c r="C167" s="0" t="inlineStr">
@@ -10074,7 +10079,7 @@
       </c>
       <c r="G167" s="0" t="inlineStr">
         <is>
-          <t>2026-05-14 13:10:29</t>
+          <t>2026-05-16 13:34:39</t>
         </is>
       </c>
       <c r="H167" s="0" t="inlineStr">
@@ -10084,7 +10089,7 @@
       </c>
       <c r="I167" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音6</t>
+          <t>安迪-抖音4</t>
         </is>
       </c>
       <c r="J167" s="0" t="inlineStr">
@@ -10105,11 +10110,11 @@
     </row>
     <row r="168" spans="1:14">
       <c r="A168" s="0">
-        <v>45836291</v>
+        <v>45933730</v>
       </c>
       <c r="B168" s="0" t="inlineStr">
         <is>
-          <t>lv</t>
+          <t>发发啊～</t>
         </is>
       </c>
       <c r="C168" s="0" t="inlineStr">
@@ -10134,7 +10139,7 @@
       </c>
       <c r="G168" s="0" t="inlineStr">
         <is>
-          <t>2026-05-13 17:24:15</t>
+          <t>2026-05-16 13:07:11</t>
         </is>
       </c>
       <c r="H168" s="0" t="inlineStr">
@@ -10144,7 +10149,7 @@
       </c>
       <c r="I168" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音8</t>
+          <t>安迪-抖音5</t>
         </is>
       </c>
       <c r="J168" s="0" t="inlineStr">
@@ -10165,11 +10170,11 @@
     </row>
     <row r="169" spans="1:14">
       <c r="A169" s="0">
-        <v>45835641</v>
+        <v>45933697</v>
       </c>
       <c r="B169" s="0" t="inlineStr">
         <is>
-          <t>shurainbow</t>
+          <t>事缓圆人缓安</t>
         </is>
       </c>
       <c r="C169" s="0" t="inlineStr">
@@ -10194,7 +10199,7 @@
       </c>
       <c r="G169" s="0" t="inlineStr">
         <is>
-          <t>2026-05-13 16:57:25</t>
+          <t>2026-05-16 13:05:41</t>
         </is>
       </c>
       <c r="H169" s="0" t="inlineStr">
@@ -10204,7 +10209,7 @@
       </c>
       <c r="I169" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音8</t>
+          <t>安迪-抖音5</t>
         </is>
       </c>
       <c r="J169" s="0" t="inlineStr">
@@ -10225,11 +10230,11 @@
     </row>
     <row r="170" spans="1:14">
       <c r="A170" s="0">
-        <v>45833393</v>
+        <v>45931075</v>
       </c>
       <c r="B170" s="0" t="inlineStr">
         <is>
-          <t>慧</t>
+          <t>沐月🍒兰</t>
         </is>
       </c>
       <c r="C170" s="0" t="inlineStr">
@@ -10254,7 +10259,7 @@
       </c>
       <c r="G170" s="0" t="inlineStr">
         <is>
-          <t>2026-05-13 15:40:05</t>
+          <t>2026-05-16 11:36:15</t>
         </is>
       </c>
       <c r="H170" s="0" t="inlineStr">
@@ -10264,7 +10269,7 @@
       </c>
       <c r="I170" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音8</t>
+          <t>安迪-抖音7</t>
         </is>
       </c>
       <c r="J170" s="0" t="inlineStr">
@@ -10285,11 +10290,11 @@
     </row>
     <row r="171" spans="1:14">
       <c r="A171" s="0">
-        <v>45833114</v>
+        <v>45928730</v>
       </c>
       <c r="B171" s="0" t="inlineStr">
         <is>
-          <t>lucky</t>
+          <t>sky</t>
         </is>
       </c>
       <c r="C171" s="0" t="inlineStr">
@@ -10314,7 +10319,7 @@
       </c>
       <c r="G171" s="0" t="inlineStr">
         <is>
-          <t>2026-05-13 15:31:05</t>
+          <t>2026-05-16 10:22:07</t>
         </is>
       </c>
       <c r="H171" s="0" t="inlineStr">
@@ -10324,7 +10329,7 @@
       </c>
       <c r="I171" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音9</t>
+          <t>安迪-抖音8</t>
         </is>
       </c>
       <c r="J171" s="0" t="inlineStr">
@@ -10345,11 +10350,11 @@
     </row>
     <row r="172" spans="1:14">
       <c r="A172" s="0">
-        <v>45830520</v>
+        <v>45928692</v>
       </c>
       <c r="B172" s="0" t="inlineStr">
         <is>
-          <t>Cici</t>
+          <t>蓝天</t>
         </is>
       </c>
       <c r="C172" s="0" t="inlineStr">
@@ -10374,7 +10379,7 @@
       </c>
       <c r="G172" s="0" t="inlineStr">
         <is>
-          <t>2026-05-13 14:19:15</t>
+          <t>2026-05-16 10:20:17</t>
         </is>
       </c>
       <c r="H172" s="0" t="inlineStr">
@@ -10405,11 +10410,11 @@
     </row>
     <row r="173" spans="1:14">
       <c r="A173" s="0">
-        <v>45821932</v>
+        <v>45900431</v>
       </c>
       <c r="B173" s="0" t="inlineStr">
         <is>
-          <t>笃定，</t>
+          <t>A燕子</t>
         </is>
       </c>
       <c r="C173" s="0" t="inlineStr">
@@ -10434,7 +10439,7 @@
       </c>
       <c r="G173" s="0" t="inlineStr">
         <is>
-          <t>2026-05-13 11:54:55</t>
+          <t>2026-05-15 15:18:35</t>
         </is>
       </c>
       <c r="H173" s="0" t="inlineStr">
@@ -10444,7 +10449,7 @@
       </c>
       <c r="I173" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音4</t>
+          <t>安迪-抖音9</t>
         </is>
       </c>
       <c r="J173" s="0" t="inlineStr">
@@ -10465,11 +10470,11 @@
     </row>
     <row r="174" spans="1:14">
       <c r="A174" s="0">
-        <v>45744722</v>
+        <v>45900357</v>
       </c>
       <c r="B174" s="0" t="inlineStr">
         <is>
-          <t>深谷之兰</t>
+          <t>un</t>
         </is>
       </c>
       <c r="C174" s="0" t="inlineStr">
@@ -10494,7 +10499,7 @@
       </c>
       <c r="G174" s="0" t="inlineStr">
         <is>
-          <t>2026-05-10 23:25:22</t>
+          <t>2026-05-15 15:16:49</t>
         </is>
       </c>
       <c r="H174" s="0" t="inlineStr">
@@ -10504,7 +10509,7 @@
       </c>
       <c r="I174" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音6</t>
+          <t>安迪-抖音9</t>
         </is>
       </c>
       <c r="J174" s="0" t="inlineStr">
@@ -10525,11 +10530,11 @@
     </row>
     <row r="175" spans="1:14">
       <c r="A175" s="0">
-        <v>45737716</v>
+        <v>45891970</v>
       </c>
       <c r="B175" s="0" t="inlineStr">
         <is>
-          <t>于艳</t>
+          <t>XIao王</t>
         </is>
       </c>
       <c r="C175" s="0" t="inlineStr">
@@ -10554,7 +10559,7 @@
       </c>
       <c r="G175" s="0" t="inlineStr">
         <is>
-          <t>2026-05-10 20:04:49</t>
+          <t>2026-05-15 11:19:35</t>
         </is>
       </c>
       <c r="H175" s="0" t="inlineStr">
@@ -10564,7 +10569,7 @@
       </c>
       <c r="I175" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音5</t>
+          <t>安迪-抖音7</t>
         </is>
       </c>
       <c r="J175" s="0" t="inlineStr">
@@ -10585,11 +10590,11 @@
     </row>
     <row r="176" spans="1:14">
       <c r="A176" s="0">
-        <v>45732013</v>
+        <v>45864167</v>
       </c>
       <c r="B176" s="0" t="inlineStr">
         <is>
-          <t>Lykke</t>
+          <t>黑妹</t>
         </is>
       </c>
       <c r="C176" s="0" t="inlineStr">
@@ -10614,7 +10619,7 @@
       </c>
       <c r="G176" s="0" t="inlineStr">
         <is>
-          <t>2026-05-10 15:38:57</t>
+          <t>2026-05-14 15:04:03</t>
         </is>
       </c>
       <c r="H176" s="0" t="inlineStr">
@@ -10624,7 +10629,7 @@
       </c>
       <c r="I176" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音3</t>
+          <t>安迪-抖音9</t>
         </is>
       </c>
       <c r="J176" s="0" t="inlineStr">
@@ -10645,11 +10650,11 @@
     </row>
     <row r="177" spans="1:14">
       <c r="A177" s="0">
-        <v>45730047</v>
+        <v>45861458</v>
       </c>
       <c r="B177" s="0" t="inlineStr">
         <is>
-          <t>朝～颜</t>
+          <t>ʚ陈玲ɞ</t>
         </is>
       </c>
       <c r="C177" s="0" t="inlineStr">
@@ -10674,7 +10679,7 @@
       </c>
       <c r="G177" s="0" t="inlineStr">
         <is>
-          <t>2026-05-10 14:04:01</t>
+          <t>2026-05-14 13:10:29</t>
         </is>
       </c>
       <c r="H177" s="0" t="inlineStr">
@@ -10684,7 +10689,7 @@
       </c>
       <c r="I177" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音3</t>
+          <t>安迪-抖音6</t>
         </is>
       </c>
       <c r="J177" s="0" t="inlineStr">
@@ -10705,11 +10710,11 @@
     </row>
     <row r="178" spans="1:14">
       <c r="A178" s="0">
-        <v>45728994</v>
+        <v>45836291</v>
       </c>
       <c r="B178" s="0" t="inlineStr">
         <is>
-          <t>土豆</t>
+          <t>lv</t>
         </is>
       </c>
       <c r="C178" s="0" t="inlineStr">
@@ -10734,7 +10739,7 @@
       </c>
       <c r="G178" s="0" t="inlineStr">
         <is>
-          <t>2026-05-10 13:12:14</t>
+          <t>2026-05-13 17:24:15</t>
         </is>
       </c>
       <c r="H178" s="0" t="inlineStr">
@@ -10744,7 +10749,7 @@
       </c>
       <c r="I178" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音5</t>
+          <t>安迪-抖音8</t>
         </is>
       </c>
       <c r="J178" s="0" t="inlineStr">
@@ -10765,11 +10770,11 @@
     </row>
     <row r="179" spans="1:14">
       <c r="A179" s="0">
-        <v>45728921</v>
+        <v>45835641</v>
       </c>
       <c r="B179" s="0" t="inlineStr">
         <is>
-          <t>杨光🇨🇳</t>
+          <t>shurainbow</t>
         </is>
       </c>
       <c r="C179" s="0" t="inlineStr">
@@ -10794,7 +10799,7 @@
       </c>
       <c r="G179" s="0" t="inlineStr">
         <is>
-          <t>2026-05-10 13:08:59</t>
+          <t>2026-05-13 16:57:25</t>
         </is>
       </c>
       <c r="H179" s="0" t="inlineStr">
@@ -10804,7 +10809,7 @@
       </c>
       <c r="I179" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音5</t>
+          <t>安迪-抖音8</t>
         </is>
       </c>
       <c r="J179" s="0" t="inlineStr">
@@ -10825,11 +10830,11 @@
     </row>
     <row r="180" spans="1:14">
       <c r="A180" s="0">
-        <v>45728770</v>
+        <v>45833393</v>
       </c>
       <c r="B180" s="0" t="inlineStr">
         <is>
-          <t>花</t>
+          <t>慧</t>
         </is>
       </c>
       <c r="C180" s="0" t="inlineStr">
@@ -10854,7 +10859,7 @@
       </c>
       <c r="G180" s="0" t="inlineStr">
         <is>
-          <t>2026-05-10 12:59:21</t>
+          <t>2026-05-13 15:40:05</t>
         </is>
       </c>
       <c r="H180" s="0" t="inlineStr">
@@ -10864,7 +10869,7 @@
       </c>
       <c r="I180" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音5</t>
+          <t>安迪-抖音8</t>
         </is>
       </c>
       <c r="J180" s="0" t="inlineStr">
@@ -10885,11 +10890,11 @@
     </row>
     <row r="181" spans="1:14">
       <c r="A181" s="0">
-        <v>45728752</v>
+        <v>45833114</v>
       </c>
       <c r="B181" s="0" t="inlineStr">
         <is>
-          <t>好名字可以让你的朋友更容易记住你</t>
+          <t>lucky</t>
         </is>
       </c>
       <c r="C181" s="0" t="inlineStr">
@@ -10914,7 +10919,7 @@
       </c>
       <c r="G181" s="0" t="inlineStr">
         <is>
-          <t>2026-05-10 12:58:57</t>
+          <t>2026-05-13 15:31:05</t>
         </is>
       </c>
       <c r="H181" s="0" t="inlineStr">
@@ -10924,7 +10929,7 @@
       </c>
       <c r="I181" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音5</t>
+          <t>安迪-抖音9</t>
         </is>
       </c>
       <c r="J181" s="0" t="inlineStr">
@@ -10945,11 +10950,11 @@
     </row>
     <row r="182" spans="1:14">
       <c r="A182" s="0">
-        <v>45728750</v>
+        <v>45830520</v>
       </c>
       <c r="B182" s="0" t="inlineStr">
         <is>
-          <t>吉庆</t>
+          <t>Cici</t>
         </is>
       </c>
       <c r="C182" s="0" t="inlineStr">
@@ -10974,7 +10979,7 @@
       </c>
       <c r="G182" s="0" t="inlineStr">
         <is>
-          <t>2026-05-10 12:58:51</t>
+          <t>2026-05-13 14:19:15</t>
         </is>
       </c>
       <c r="H182" s="0" t="inlineStr">
@@ -10984,7 +10989,7 @@
       </c>
       <c r="I182" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音5</t>
+          <t>安迪-抖音8</t>
         </is>
       </c>
       <c r="J182" s="0" t="inlineStr">
@@ -11005,11 +11010,11 @@
     </row>
     <row r="183" spans="1:14">
       <c r="A183" s="0">
-        <v>45728565</v>
+        <v>45821932</v>
       </c>
       <c r="B183" s="0" t="inlineStr">
         <is>
-          <t>Janny</t>
+          <t>笃定，</t>
         </is>
       </c>
       <c r="C183" s="0" t="inlineStr">
@@ -11034,7 +11039,7 @@
       </c>
       <c r="G183" s="0" t="inlineStr">
         <is>
-          <t>2026-05-10 12:48:33</t>
+          <t>2026-05-13 11:54:55</t>
         </is>
       </c>
       <c r="H183" s="0" t="inlineStr">
@@ -11044,7 +11049,7 @@
       </c>
       <c r="I183" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音5</t>
+          <t>安迪-抖音4</t>
         </is>
       </c>
       <c r="J183" s="0" t="inlineStr">
@@ -11065,11 +11070,11 @@
     </row>
     <row r="184" spans="1:14">
       <c r="A184" s="0">
-        <v>45728550</v>
+        <v>45744722</v>
       </c>
       <c r="B184" s="0" t="inlineStr">
         <is>
-          <t>李建民</t>
+          <t>深谷之兰</t>
         </is>
       </c>
       <c r="C184" s="0" t="inlineStr">
@@ -11094,7 +11099,7 @@
       </c>
       <c r="G184" s="0" t="inlineStr">
         <is>
-          <t>2026-05-10 12:47:35</t>
+          <t>2026-05-10 23:25:22</t>
         </is>
       </c>
       <c r="H184" s="0" t="inlineStr">
@@ -11104,7 +11109,7 @@
       </c>
       <c r="I184" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音5</t>
+          <t>安迪-抖音6</t>
         </is>
       </c>
       <c r="J184" s="0" t="inlineStr">
@@ -11125,11 +11130,11 @@
     </row>
     <row r="185" spans="1:14">
       <c r="A185" s="0">
-        <v>45728473</v>
+        <v>45737716</v>
       </c>
       <c r="B185" s="0" t="inlineStr">
         <is>
-          <t>路得</t>
+          <t>于艳</t>
         </is>
       </c>
       <c r="C185" s="0" t="inlineStr">
@@ -11154,7 +11159,7 @@
       </c>
       <c r="G185" s="0" t="inlineStr">
         <is>
-          <t>2026-05-10 12:43:44</t>
+          <t>2026-05-10 20:04:49</t>
         </is>
       </c>
       <c r="H185" s="0" t="inlineStr">
@@ -11185,11 +11190,11 @@
     </row>
     <row r="186" spans="1:14">
       <c r="A186" s="0">
-        <v>45728462</v>
+        <v>45732013</v>
       </c>
       <c r="B186" s="0" t="inlineStr">
         <is>
-          <t>🎶sax🎷萧酲¹</t>
+          <t>Lykke</t>
         </is>
       </c>
       <c r="C186" s="0" t="inlineStr">
@@ -11214,7 +11219,7 @@
       </c>
       <c r="G186" s="0" t="inlineStr">
         <is>
-          <t>2026-05-10 12:43:17</t>
+          <t>2026-05-10 15:38:57</t>
         </is>
       </c>
       <c r="H186" s="0" t="inlineStr">
@@ -11224,7 +11229,7 @@
       </c>
       <c r="I186" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音5</t>
+          <t>安迪-抖音3</t>
         </is>
       </c>
       <c r="J186" s="0" t="inlineStr">
@@ -11245,11 +11250,11 @@
     </row>
     <row r="187" spans="1:14">
       <c r="A187" s="0">
-        <v>45728293</v>
+        <v>45730047</v>
       </c>
       <c r="B187" s="0" t="inlineStr">
         <is>
-          <t>夏日黄昏（花莲）</t>
+          <t>朝～颜</t>
         </is>
       </c>
       <c r="C187" s="0" t="inlineStr">
@@ -11274,7 +11279,7 @@
       </c>
       <c r="G187" s="0" t="inlineStr">
         <is>
-          <t>2026-05-10 12:34:33</t>
+          <t>2026-05-10 14:04:01</t>
         </is>
       </c>
       <c r="H187" s="0" t="inlineStr">
@@ -11284,7 +11289,7 @@
       </c>
       <c r="I187" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音5</t>
+          <t>安迪-抖音3</t>
         </is>
       </c>
       <c r="J187" s="0" t="inlineStr">
@@ -11305,11 +11310,11 @@
     </row>
     <row r="188" spans="1:14">
       <c r="A188" s="0">
-        <v>45711052</v>
+        <v>45728994</v>
       </c>
       <c r="B188" s="0" t="inlineStr">
         <is>
-          <t>老林</t>
+          <t>土豆</t>
         </is>
       </c>
       <c r="C188" s="0" t="inlineStr">
@@ -11334,7 +11339,7 @@
       </c>
       <c r="G188" s="0" t="inlineStr">
         <is>
-          <t>2026-05-09 21:03:31</t>
+          <t>2026-05-10 13:12:14</t>
         </is>
       </c>
       <c r="H188" s="0" t="inlineStr">
@@ -11365,11 +11370,11 @@
     </row>
     <row r="189" spans="1:14">
       <c r="A189" s="0">
-        <v>45688840</v>
+        <v>45728921</v>
       </c>
       <c r="B189" s="0" t="inlineStr">
         <is>
-          <t>女皇</t>
+          <t>杨光🇨🇳</t>
         </is>
       </c>
       <c r="C189" s="0" t="inlineStr">
@@ -11394,7 +11399,7 @@
       </c>
       <c r="G189" s="0" t="inlineStr">
         <is>
-          <t>2026-05-09 15:32:13</t>
+          <t>2026-05-10 13:08:59</t>
         </is>
       </c>
       <c r="H189" s="0" t="inlineStr">
@@ -11425,11 +11430,11 @@
     </row>
     <row r="190" spans="1:14">
       <c r="A190" s="0">
-        <v>45688817</v>
+        <v>45728770</v>
       </c>
       <c r="B190" s="0" t="inlineStr">
         <is>
-          <t>冯继珍</t>
+          <t>花</t>
         </is>
       </c>
       <c r="C190" s="0" t="inlineStr">
@@ -11454,7 +11459,7 @@
       </c>
       <c r="G190" s="0" t="inlineStr">
         <is>
-          <t>2026-05-09 15:31:19</t>
+          <t>2026-05-10 12:59:21</t>
         </is>
       </c>
       <c r="H190" s="0" t="inlineStr">
@@ -11485,11 +11490,11 @@
     </row>
     <row r="191" spans="1:14">
       <c r="A191" s="0">
-        <v>45687034</v>
+        <v>45728752</v>
       </c>
       <c r="B191" s="0" t="inlineStr">
         <is>
-          <t>珍珍果业丹丹妹🍃</t>
+          <t>好名字可以让你的朋友更容易记住你</t>
         </is>
       </c>
       <c r="C191" s="0" t="inlineStr">
@@ -11514,7 +11519,7 @@
       </c>
       <c r="G191" s="0" t="inlineStr">
         <is>
-          <t>2026-05-09 14:36:59</t>
+          <t>2026-05-10 12:58:57</t>
         </is>
       </c>
       <c r="H191" s="0" t="inlineStr">
@@ -11545,11 +11550,11 @@
     </row>
     <row r="192" spans="1:14">
       <c r="A192" s="0">
-        <v>45685104</v>
+        <v>45728750</v>
       </c>
       <c r="B192" s="0" t="inlineStr">
         <is>
-          <t>姜庆洋</t>
+          <t>吉庆</t>
         </is>
       </c>
       <c r="C192" s="0" t="inlineStr">
@@ -11574,7 +11579,7 @@
       </c>
       <c r="G192" s="0" t="inlineStr">
         <is>
-          <t>2026-05-09 13:14:45</t>
+          <t>2026-05-10 12:58:51</t>
         </is>
       </c>
       <c r="H192" s="0" t="inlineStr">
@@ -11605,11 +11610,11 @@
     </row>
     <row r="193" spans="1:14">
       <c r="A193" s="0">
-        <v>45685004</v>
+        <v>45728565</v>
       </c>
       <c r="B193" s="0" t="inlineStr">
         <is>
-          <t>薇</t>
+          <t>Janny</t>
         </is>
       </c>
       <c r="C193" s="0" t="inlineStr">
@@ -11634,7 +11639,7 @@
       </c>
       <c r="G193" s="0" t="inlineStr">
         <is>
-          <t>2026-05-09 13:11:01</t>
+          <t>2026-05-10 12:48:33</t>
         </is>
       </c>
       <c r="H193" s="0" t="inlineStr">
@@ -11660,21 +11665,16 @@
       <c r="L193" s="0" t="inlineStr">
         <is>
           <t>已完成</t>
-        </is>
-      </c>
-      <c r="N193" s="0" t="inlineStr">
-        <is>
-          <t>廊坊</t>
         </is>
       </c>
     </row>
     <row r="194" spans="1:14">
       <c r="A194" s="0">
-        <v>45684975</v>
+        <v>45728550</v>
       </c>
       <c r="B194" s="0" t="inlineStr">
         <is>
-          <t>黎麻麻</t>
+          <t>李建民</t>
         </is>
       </c>
       <c r="C194" s="0" t="inlineStr">
@@ -11699,7 +11699,7 @@
       </c>
       <c r="G194" s="0" t="inlineStr">
         <is>
-          <t>2026-05-09 13:09:48</t>
+          <t>2026-05-10 12:47:35</t>
         </is>
       </c>
       <c r="H194" s="0" t="inlineStr">
@@ -11730,11 +11730,11 @@
     </row>
     <row r="195" spans="1:14">
       <c r="A195" s="0">
-        <v>45684952</v>
+        <v>45728473</v>
       </c>
       <c r="B195" s="0" t="inlineStr">
         <is>
-          <t>一叶知秋</t>
+          <t>路得</t>
         </is>
       </c>
       <c r="C195" s="0" t="inlineStr">
@@ -11759,7 +11759,7 @@
       </c>
       <c r="G195" s="0" t="inlineStr">
         <is>
-          <t>2026-05-09 13:08:43</t>
+          <t>2026-05-10 12:43:44</t>
         </is>
       </c>
       <c r="H195" s="0" t="inlineStr">
@@ -11790,11 +11790,11 @@
     </row>
     <row r="196" spans="1:14">
       <c r="A196" s="0">
-        <v>45684935</v>
+        <v>45728462</v>
       </c>
       <c r="B196" s="0" t="inlineStr">
         <is>
-          <t>骐鹏</t>
+          <t>🎶sax🎷萧酲¹</t>
         </is>
       </c>
       <c r="C196" s="0" t="inlineStr">
@@ -11819,7 +11819,7 @@
       </c>
       <c r="G196" s="0" t="inlineStr">
         <is>
-          <t>2026-05-09 13:08:21</t>
+          <t>2026-05-10 12:43:17</t>
         </is>
       </c>
       <c r="H196" s="0" t="inlineStr">
@@ -11850,11 +11850,11 @@
     </row>
     <row r="197" spans="1:14">
       <c r="A197" s="0">
-        <v>45684784</v>
+        <v>45728293</v>
       </c>
       <c r="B197" s="0" t="inlineStr">
         <is>
-          <t>云朵</t>
+          <t>夏日黄昏（花莲）</t>
         </is>
       </c>
       <c r="C197" s="0" t="inlineStr">
@@ -11879,7 +11879,7 @@
       </c>
       <c r="G197" s="0" t="inlineStr">
         <is>
-          <t>2026-05-09 13:02:09</t>
+          <t>2026-05-10 12:34:33</t>
         </is>
       </c>
       <c r="H197" s="0" t="inlineStr">
@@ -11910,11 +11910,11 @@
     </row>
     <row r="198" spans="1:14">
       <c r="A198" s="0">
-        <v>45684609</v>
+        <v>45711052</v>
       </c>
       <c r="B198" s="0" t="inlineStr">
         <is>
-          <t>神韵龙狮</t>
+          <t>老林</t>
         </is>
       </c>
       <c r="C198" s="0" t="inlineStr">
@@ -11939,7 +11939,7 @@
       </c>
       <c r="G198" s="0" t="inlineStr">
         <is>
-          <t>2026-05-09 12:55:11</t>
+          <t>2026-05-09 21:03:31</t>
         </is>
       </c>
       <c r="H198" s="0" t="inlineStr">
@@ -11970,11 +11970,11 @@
     </row>
     <row r="199" spans="1:14">
       <c r="A199" s="0">
-        <v>45684606</v>
+        <v>45688840</v>
       </c>
       <c r="B199" s="0" t="inlineStr">
         <is>
-          <t>舍得</t>
+          <t>女皇</t>
         </is>
       </c>
       <c r="C199" s="0" t="inlineStr">
@@ -11999,7 +11999,7 @@
       </c>
       <c r="G199" s="0" t="inlineStr">
         <is>
-          <t>2026-05-09 12:55:07</t>
+          <t>2026-05-09 15:32:13</t>
         </is>
       </c>
       <c r="H199" s="0" t="inlineStr">
@@ -12030,11 +12030,11 @@
     </row>
     <row r="200" spans="1:14">
       <c r="A200" s="0">
-        <v>45684464</v>
+        <v>45688817</v>
       </c>
       <c r="B200" s="0" t="inlineStr">
         <is>
-          <t>菠菠爷爷刘陆平</t>
+          <t>冯继珍</t>
         </is>
       </c>
       <c r="C200" s="0" t="inlineStr">
@@ -12059,7 +12059,7 @@
       </c>
       <c r="G200" s="0" t="inlineStr">
         <is>
-          <t>2026-05-09 12:51:03</t>
+          <t>2026-05-09 15:31:19</t>
         </is>
       </c>
       <c r="H200" s="0" t="inlineStr">
@@ -12090,11 +12090,11 @@
     </row>
     <row r="201" spans="1:14">
       <c r="A201" s="0">
-        <v>45684141</v>
+        <v>45687034</v>
       </c>
       <c r="B201" s="0" t="inlineStr">
         <is>
-          <t>薄荷</t>
+          <t>珍珍果业丹丹妹🍃</t>
         </is>
       </c>
       <c r="C201" s="0" t="inlineStr">
@@ -12119,7 +12119,7 @@
       </c>
       <c r="G201" s="0" t="inlineStr">
         <is>
-          <t>2026-05-09 12:40:53</t>
+          <t>2026-05-09 14:36:59</t>
         </is>
       </c>
       <c r="H201" s="0" t="inlineStr">
@@ -12150,11 +12150,11 @@
     </row>
     <row r="202" spans="1:14">
       <c r="A202" s="0">
-        <v>45651451</v>
+        <v>45685104</v>
       </c>
       <c r="B202" s="0" t="inlineStr">
         <is>
-          <t>SqZr</t>
+          <t>姜庆洋</t>
         </is>
       </c>
       <c r="C202" s="0" t="inlineStr">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="G202" s="0" t="inlineStr">
         <is>
-          <t>2026-05-08 14:38:17</t>
+          <t>2026-05-09 13:14:45</t>
         </is>
       </c>
       <c r="H202" s="0" t="inlineStr">
@@ -12210,11 +12210,11 @@
     </row>
     <row r="203" spans="1:14">
       <c r="A203" s="0">
-        <v>45648528</v>
+        <v>45685004</v>
       </c>
       <c r="B203" s="0" t="inlineStr">
         <is>
-          <t>Zhan</t>
+          <t>薇</t>
         </is>
       </c>
       <c r="C203" s="0" t="inlineStr">
@@ -12239,7 +12239,7 @@
       </c>
       <c r="G203" s="0" t="inlineStr">
         <is>
-          <t>2026-05-08 13:13:05</t>
+          <t>2026-05-09 13:11:01</t>
         </is>
       </c>
       <c r="H203" s="0" t="inlineStr">
@@ -12265,16 +12265,21 @@
       <c r="L203" s="0" t="inlineStr">
         <is>
           <t>已完成</t>
+        </is>
+      </c>
+      <c r="N203" s="0" t="inlineStr">
+        <is>
+          <t>廊坊</t>
         </is>
       </c>
     </row>
     <row r="204" spans="1:14">
       <c r="A204" s="0">
-        <v>45647504</v>
+        <v>45684975</v>
       </c>
       <c r="B204" s="0" t="inlineStr">
         <is>
-          <t>清云</t>
+          <t>黎麻麻</t>
         </is>
       </c>
       <c r="C204" s="0" t="inlineStr">
@@ -12299,7 +12304,7 @@
       </c>
       <c r="G204" s="0" t="inlineStr">
         <is>
-          <t>2026-05-08 12:36:37</t>
+          <t>2026-05-09 13:09:48</t>
         </is>
       </c>
       <c r="H204" s="0" t="inlineStr">
@@ -12330,11 +12335,11 @@
     </row>
     <row r="205" spans="1:14">
       <c r="A205" s="0">
-        <v>45642468</v>
+        <v>45684952</v>
       </c>
       <c r="B205" s="0" t="inlineStr">
         <is>
-          <t>笙磬同音</t>
+          <t>一叶知秋</t>
         </is>
       </c>
       <c r="C205" s="0" t="inlineStr">
@@ -12359,7 +12364,7 @@
       </c>
       <c r="G205" s="0" t="inlineStr">
         <is>
-          <t>2026-05-08 09:16:58</t>
+          <t>2026-05-09 13:08:43</t>
         </is>
       </c>
       <c r="H205" s="0" t="inlineStr">
@@ -12390,11 +12395,11 @@
     </row>
     <row r="206" spans="1:14">
       <c r="A206" s="0">
-        <v>45635229</v>
+        <v>45684935</v>
       </c>
       <c r="B206" s="0" t="inlineStr">
         <is>
-          <t>糖果🍥</t>
+          <t>骐鹏</t>
         </is>
       </c>
       <c r="C206" s="0" t="inlineStr">
@@ -12419,7 +12424,7 @@
       </c>
       <c r="G206" s="0" t="inlineStr">
         <is>
-          <t>2026-05-07 23:47:09</t>
+          <t>2026-05-09 13:08:21</t>
         </is>
       </c>
       <c r="H206" s="0" t="inlineStr">
@@ -12450,11 +12455,11 @@
     </row>
     <row r="207" spans="1:14">
       <c r="A207" s="0">
-        <v>45620977</v>
+        <v>45684784</v>
       </c>
       <c r="B207" s="0" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>云朵</t>
         </is>
       </c>
       <c r="C207" s="0" t="inlineStr">
@@ -12479,7 +12484,7 @@
       </c>
       <c r="G207" s="0" t="inlineStr">
         <is>
-          <t>2026-05-07 14:22:05</t>
+          <t>2026-05-09 13:02:09</t>
         </is>
       </c>
       <c r="H207" s="0" t="inlineStr">
@@ -12505,21 +12510,16 @@
       <c r="L207" s="0" t="inlineStr">
         <is>
           <t>已完成</t>
-        </is>
-      </c>
-      <c r="N207" s="0" t="inlineStr">
-        <is>
-          <t>深圳</t>
         </is>
       </c>
     </row>
     <row r="208" spans="1:14">
       <c r="A208" s="0">
-        <v>45620966</v>
+        <v>45684609</v>
       </c>
       <c r="B208" s="0" t="inlineStr">
         <is>
-          <t>🐭🐭🐭🐭🐭🐭</t>
+          <t>神韵龙狮</t>
         </is>
       </c>
       <c r="C208" s="0" t="inlineStr">
@@ -12544,7 +12544,7 @@
       </c>
       <c r="G208" s="0" t="inlineStr">
         <is>
-          <t>2026-05-07 14:21:17</t>
+          <t>2026-05-09 12:55:11</t>
         </is>
       </c>
       <c r="H208" s="0" t="inlineStr">
@@ -12554,7 +12554,7 @@
       </c>
       <c r="I208" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音6</t>
+          <t>安迪-抖音5</t>
         </is>
       </c>
       <c r="J208" s="0" t="inlineStr">
@@ -12575,11 +12575,11 @@
     </row>
     <row r="209" spans="1:14">
       <c r="A209" s="0">
-        <v>45619636</v>
+        <v>45684606</v>
       </c>
       <c r="B209" s="0" t="inlineStr">
         <is>
-          <t>静水寒</t>
+          <t>舍得</t>
         </is>
       </c>
       <c r="C209" s="0" t="inlineStr">
@@ -12604,7 +12604,7 @@
       </c>
       <c r="G209" s="0" t="inlineStr">
         <is>
-          <t>2026-05-07 13:53:39</t>
+          <t>2026-05-09 12:55:07</t>
         </is>
       </c>
       <c r="H209" s="0" t="inlineStr">
@@ -12635,11 +12635,11 @@
     </row>
     <row r="210" spans="1:14">
       <c r="A210" s="0">
-        <v>45618896</v>
+        <v>45684464</v>
       </c>
       <c r="B210" s="0" t="inlineStr">
         <is>
-          <t>邹和平</t>
+          <t>菠菠爷爷刘陆平</t>
         </is>
       </c>
       <c r="C210" s="0" t="inlineStr">
@@ -12664,7 +12664,7 @@
       </c>
       <c r="G210" s="0" t="inlineStr">
         <is>
-          <t>2026-05-07 13:15:43</t>
+          <t>2026-05-09 12:51:03</t>
         </is>
       </c>
       <c r="H210" s="0" t="inlineStr">
@@ -12695,11 +12695,11 @@
     </row>
     <row r="211" spans="1:14">
       <c r="A211" s="0">
-        <v>45618827</v>
+        <v>45684141</v>
       </c>
       <c r="B211" s="0" t="inlineStr">
         <is>
-          <t>易圣杰</t>
+          <t>薄荷</t>
         </is>
       </c>
       <c r="C211" s="0" t="inlineStr">
@@ -12724,7 +12724,7 @@
       </c>
       <c r="G211" s="0" t="inlineStr">
         <is>
-          <t>2026-05-07 13:13:21</t>
+          <t>2026-05-09 12:40:53</t>
         </is>
       </c>
       <c r="H211" s="0" t="inlineStr">
@@ -12755,11 +12755,11 @@
     </row>
     <row r="212" spans="1:14">
       <c r="A212" s="0">
-        <v>45618536</v>
+        <v>45651451</v>
       </c>
       <c r="B212" s="0" t="inlineStr">
         <is>
-          <t>Lucky</t>
+          <t>SqZr</t>
         </is>
       </c>
       <c r="C212" s="0" t="inlineStr">
@@ -12784,7 +12784,7 @@
       </c>
       <c r="G212" s="0" t="inlineStr">
         <is>
-          <t>2026-05-07 13:01:03</t>
+          <t>2026-05-08 14:38:17</t>
         </is>
       </c>
       <c r="H212" s="0" t="inlineStr">
@@ -12815,11 +12815,11 @@
     </row>
     <row r="213" spans="1:14">
       <c r="A213" s="0">
-        <v>45618227</v>
+        <v>45648528</v>
       </c>
       <c r="B213" s="0" t="inlineStr">
         <is>
-          <t>林子</t>
+          <t>Zhan</t>
         </is>
       </c>
       <c r="C213" s="0" t="inlineStr">
@@ -12844,7 +12844,7 @@
       </c>
       <c r="G213" s="0" t="inlineStr">
         <is>
-          <t>2026-05-07 12:47:29</t>
+          <t>2026-05-08 13:13:05</t>
         </is>
       </c>
       <c r="H213" s="0" t="inlineStr">
@@ -12870,21 +12870,16 @@
       <c r="L213" s="0" t="inlineStr">
         <is>
           <t>已完成</t>
-        </is>
-      </c>
-      <c r="N213" s="0" t="inlineStr">
-        <is>
-          <t>自贡</t>
         </is>
       </c>
     </row>
     <row r="214" spans="1:14">
       <c r="A214" s="0">
-        <v>45617830</v>
+        <v>45647504</v>
       </c>
       <c r="B214" s="0" t="inlineStr">
         <is>
-          <t>🦋</t>
+          <t>清云</t>
         </is>
       </c>
       <c r="C214" s="0" t="inlineStr">
@@ -12909,7 +12904,7 @@
       </c>
       <c r="G214" s="0" t="inlineStr">
         <is>
-          <t>2026-05-07 12:30:29</t>
+          <t>2026-05-08 12:36:37</t>
         </is>
       </c>
       <c r="H214" s="0" t="inlineStr">
@@ -12940,11 +12935,11 @@
     </row>
     <row r="215" spans="1:14">
       <c r="A215" s="0">
-        <v>45608425</v>
+        <v>45642468</v>
       </c>
       <c r="B215" s="0" t="inlineStr">
         <is>
-          <t>Dwayne  Duan</t>
+          <t>笙磬同音</t>
         </is>
       </c>
       <c r="C215" s="0" t="inlineStr">
@@ -12969,7 +12964,7 @@
       </c>
       <c r="G215" s="0" t="inlineStr">
         <is>
-          <t>2026-05-07 06:48:43</t>
+          <t>2026-05-08 09:16:58</t>
         </is>
       </c>
       <c r="H215" s="0" t="inlineStr">
@@ -12979,7 +12974,7 @@
       </c>
       <c r="I215" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音6</t>
+          <t>安迪-抖音5</t>
         </is>
       </c>
       <c r="J215" s="0" t="inlineStr">
@@ -13000,11 +12995,11 @@
     </row>
     <row r="216" spans="1:14">
       <c r="A216" s="0">
-        <v>45590801</v>
+        <v>45635229</v>
       </c>
       <c r="B216" s="0" t="inlineStr">
         <is>
-          <t>A～仰望sky</t>
+          <t>糖果🍥</t>
         </is>
       </c>
       <c r="C216" s="0" t="inlineStr">
@@ -13029,7 +13024,7 @@
       </c>
       <c r="G216" s="0" t="inlineStr">
         <is>
-          <t>2026-05-06 15:30:21</t>
+          <t>2026-05-07 23:47:09</t>
         </is>
       </c>
       <c r="H216" s="0" t="inlineStr">
@@ -13039,7 +13034,7 @@
       </c>
       <c r="I216" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音6</t>
+          <t>安迪-抖音5</t>
         </is>
       </c>
       <c r="J216" s="0" t="inlineStr">
@@ -13060,11 +13055,11 @@
     </row>
     <row r="217" spans="1:14">
       <c r="A217" s="0">
-        <v>45561516</v>
+        <v>45620977</v>
       </c>
       <c r="B217" s="0" t="inlineStr">
         <is>
-          <t>新风拂面</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="C217" s="0" t="inlineStr">
@@ -13089,7 +13084,7 @@
       </c>
       <c r="G217" s="0" t="inlineStr">
         <is>
-          <t>2026-05-05 16:23:07</t>
+          <t>2026-05-07 14:22:05</t>
         </is>
       </c>
       <c r="H217" s="0" t="inlineStr">
@@ -13099,7 +13094,7 @@
       </c>
       <c r="I217" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音6</t>
+          <t>安迪-抖音5</t>
         </is>
       </c>
       <c r="J217" s="0" t="inlineStr">
@@ -13115,16 +13110,21 @@
       <c r="L217" s="0" t="inlineStr">
         <is>
           <t>已完成</t>
+        </is>
+      </c>
+      <c r="N217" s="0" t="inlineStr">
+        <is>
+          <t>深圳</t>
         </is>
       </c>
     </row>
     <row r="218" spans="1:14">
       <c r="A218" s="0">
-        <v>45550981</v>
+        <v>45620966</v>
       </c>
       <c r="B218" s="0" t="inlineStr">
         <is>
-          <t>lance</t>
+          <t>🐭🐭🐭🐭🐭🐭</t>
         </is>
       </c>
       <c r="C218" s="0" t="inlineStr">
@@ -13149,7 +13149,7 @@
       </c>
       <c r="G218" s="0" t="inlineStr">
         <is>
-          <t>2026-05-05 07:56:49</t>
+          <t>2026-05-07 14:21:17</t>
         </is>
       </c>
       <c r="H218" s="0" t="inlineStr">
@@ -13159,7 +13159,7 @@
       </c>
       <c r="I218" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音5</t>
+          <t>安迪-抖音6</t>
         </is>
       </c>
       <c r="J218" s="0" t="inlineStr">
@@ -13180,11 +13180,11 @@
     </row>
     <row r="219" spans="1:14">
       <c r="A219" s="0">
-        <v>45535452</v>
+        <v>45619636</v>
       </c>
       <c r="B219" s="0" t="inlineStr">
         <is>
-          <t>辉辉</t>
+          <t>静水寒</t>
         </is>
       </c>
       <c r="C219" s="0" t="inlineStr">
@@ -13209,7 +13209,7 @@
       </c>
       <c r="G219" s="0" t="inlineStr">
         <is>
-          <t>2026-05-04 14:49:27</t>
+          <t>2026-05-07 13:53:39</t>
         </is>
       </c>
       <c r="H219" s="0" t="inlineStr">
@@ -13219,7 +13219,7 @@
       </c>
       <c r="I219" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音6</t>
+          <t>安迪-抖音5</t>
         </is>
       </c>
       <c r="J219" s="0" t="inlineStr">
@@ -13240,11 +13240,11 @@
     </row>
     <row r="220" spans="1:14">
       <c r="A220" s="0">
-        <v>45522249</v>
+        <v>45618896</v>
       </c>
       <c r="B220" s="0" t="inlineStr">
         <is>
-          <t>娟子</t>
+          <t>邹和平</t>
         </is>
       </c>
       <c r="C220" s="0" t="inlineStr">
@@ -13269,7 +13269,7 @@
       </c>
       <c r="G220" s="0" t="inlineStr">
         <is>
-          <t>2026-05-03 23:56:37</t>
+          <t>2026-05-07 13:15:43</t>
         </is>
       </c>
       <c r="H220" s="0" t="inlineStr">
@@ -13279,7 +13279,7 @@
       </c>
       <c r="I220" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音6</t>
+          <t>安迪-抖音5</t>
         </is>
       </c>
       <c r="J220" s="0" t="inlineStr">
@@ -13300,11 +13300,11 @@
     </row>
     <row r="221" spans="1:14">
       <c r="A221" s="0">
-        <v>45490798</v>
+        <v>45618827</v>
       </c>
       <c r="B221" s="0" t="inlineStr">
         <is>
-          <t>青</t>
+          <t>易圣杰</t>
         </is>
       </c>
       <c r="C221" s="0" t="inlineStr">
@@ -13329,7 +13329,7 @@
       </c>
       <c r="G221" s="0" t="inlineStr">
         <is>
-          <t>2026-05-02 16:18:11</t>
+          <t>2026-05-07 13:13:21</t>
         </is>
       </c>
       <c r="H221" s="0" t="inlineStr">
@@ -13360,11 +13360,11 @@
     </row>
     <row r="222" spans="1:14">
       <c r="A222" s="0">
-        <v>45487466</v>
+        <v>45618536</v>
       </c>
       <c r="B222" s="0" t="inlineStr">
         <is>
-          <t>夸夸妹</t>
+          <t>Lucky</t>
         </is>
       </c>
       <c r="C222" s="0" t="inlineStr">
@@ -13389,7 +13389,7 @@
       </c>
       <c r="G222" s="0" t="inlineStr">
         <is>
-          <t>2026-05-02 13:10:53</t>
+          <t>2026-05-07 13:01:03</t>
         </is>
       </c>
       <c r="H222" s="0" t="inlineStr">
@@ -13420,11 +13420,11 @@
     </row>
     <row r="223" spans="1:14">
       <c r="A223" s="0">
-        <v>45487393</v>
+        <v>45618227</v>
       </c>
       <c r="B223" s="0" t="inlineStr">
         <is>
-          <t>乐悠悠</t>
+          <t>林子</t>
         </is>
       </c>
       <c r="C223" s="0" t="inlineStr">
@@ -13449,7 +13449,7 @@
       </c>
       <c r="G223" s="0" t="inlineStr">
         <is>
-          <t>2026-05-02 13:05:40</t>
+          <t>2026-05-07 12:47:29</t>
         </is>
       </c>
       <c r="H223" s="0" t="inlineStr">
@@ -13475,16 +13475,21 @@
       <c r="L223" s="0" t="inlineStr">
         <is>
           <t>已完成</t>
+        </is>
+      </c>
+      <c r="N223" s="0" t="inlineStr">
+        <is>
+          <t>自贡</t>
         </is>
       </c>
     </row>
     <row r="224" spans="1:14">
       <c r="A224" s="0">
-        <v>45487328</v>
+        <v>45617830</v>
       </c>
       <c r="B224" s="0" t="inlineStr">
         <is>
-          <t>甘草</t>
+          <t>🦋</t>
         </is>
       </c>
       <c r="C224" s="0" t="inlineStr">
@@ -13509,7 +13514,7 @@
       </c>
       <c r="G224" s="0" t="inlineStr">
         <is>
-          <t>2026-05-02 13:01:57</t>
+          <t>2026-05-07 12:30:29</t>
         </is>
       </c>
       <c r="H224" s="0" t="inlineStr">
@@ -13535,21 +13540,16 @@
       <c r="L224" s="0" t="inlineStr">
         <is>
           <t>已完成</t>
-        </is>
-      </c>
-      <c r="N224" s="0" t="inlineStr">
-        <is>
-          <t>大同</t>
         </is>
       </c>
     </row>
     <row r="225" spans="1:14">
       <c r="A225" s="0">
-        <v>45487316</v>
+        <v>45608425</v>
       </c>
       <c r="B225" s="0" t="inlineStr">
         <is>
-          <t>苗妈家苗宝(5月26号生日)</t>
+          <t>Dwayne  Duan</t>
         </is>
       </c>
       <c r="C225" s="0" t="inlineStr">
@@ -13574,7 +13574,7 @@
       </c>
       <c r="G225" s="0" t="inlineStr">
         <is>
-          <t>2026-05-02 13:01:11</t>
+          <t>2026-05-07 06:48:43</t>
         </is>
       </c>
       <c r="H225" s="0" t="inlineStr">
@@ -13584,7 +13584,7 @@
       </c>
       <c r="I225" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音5</t>
+          <t>安迪-抖音6</t>
         </is>
       </c>
       <c r="J225" s="0" t="inlineStr">
@@ -13605,11 +13605,11 @@
     </row>
     <row r="226" spans="1:14">
       <c r="A226" s="0">
-        <v>45487303</v>
+        <v>45590801</v>
       </c>
       <c r="B226" s="0" t="inlineStr">
         <is>
-          <t>人生若只如初见</t>
+          <t>A～仰望sky</t>
         </is>
       </c>
       <c r="C226" s="0" t="inlineStr">
@@ -13634,7 +13634,7 @@
       </c>
       <c r="G226" s="0" t="inlineStr">
         <is>
-          <t>2026-05-02 13:00:27</t>
+          <t>2026-05-06 15:30:21</t>
         </is>
       </c>
       <c r="H226" s="0" t="inlineStr">
@@ -13644,7 +13644,7 @@
       </c>
       <c r="I226" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音5</t>
+          <t>安迪-抖音6</t>
         </is>
       </c>
       <c r="J226" s="0" t="inlineStr">
@@ -13665,11 +13665,11 @@
     </row>
     <row r="227" spans="1:14">
       <c r="A227" s="0">
-        <v>45487283</v>
+        <v>45561516</v>
       </c>
       <c r="B227" s="0" t="inlineStr">
         <is>
-          <t>耶晓晓</t>
+          <t>新风拂面</t>
         </is>
       </c>
       <c r="C227" s="0" t="inlineStr">
@@ -13694,7 +13694,7 @@
       </c>
       <c r="G227" s="0" t="inlineStr">
         <is>
-          <t>2026-05-02 12:59:23</t>
+          <t>2026-05-05 16:23:07</t>
         </is>
       </c>
       <c r="H227" s="0" t="inlineStr">
@@ -13704,7 +13704,7 @@
       </c>
       <c r="I227" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音5</t>
+          <t>安迪-抖音6</t>
         </is>
       </c>
       <c r="J227" s="0" t="inlineStr">
@@ -13725,11 +13725,11 @@
     </row>
     <row r="228" spans="1:14">
       <c r="A228" s="0">
-        <v>45486981</v>
+        <v>45550981</v>
       </c>
       <c r="B228" s="0" t="inlineStr">
         <is>
-          <t>草青儿</t>
+          <t>lance</t>
         </is>
       </c>
       <c r="C228" s="0" t="inlineStr">
@@ -13754,7 +13754,7 @@
       </c>
       <c r="G228" s="0" t="inlineStr">
         <is>
-          <t>2026-05-02 12:43:01</t>
+          <t>2026-05-05 07:56:49</t>
         </is>
       </c>
       <c r="H228" s="0" t="inlineStr">
@@ -13785,11 +13785,11 @@
     </row>
     <row r="229" spans="1:14">
       <c r="A229" s="0">
-        <v>45486967</v>
+        <v>45535452</v>
       </c>
       <c r="B229" s="0" t="inlineStr">
         <is>
-          <t>向阳而生</t>
+          <t>辉辉</t>
         </is>
       </c>
       <c r="C229" s="0" t="inlineStr">
@@ -13814,7 +13814,7 @@
       </c>
       <c r="G229" s="0" t="inlineStr">
         <is>
-          <t>2026-05-02 12:41:47</t>
+          <t>2026-05-04 14:49:27</t>
         </is>
       </c>
       <c r="H229" s="0" t="inlineStr">
@@ -13824,7 +13824,7 @@
       </c>
       <c r="I229" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音5</t>
+          <t>安迪-抖音6</t>
         </is>
       </c>
       <c r="J229" s="0" t="inlineStr">
@@ -13845,11 +13845,11 @@
     </row>
     <row r="230" spans="1:14">
       <c r="A230" s="0">
-        <v>45483029</v>
+        <v>45522249</v>
       </c>
       <c r="B230" s="0" t="inlineStr">
         <is>
-          <t>静</t>
+          <t>娟子</t>
         </is>
       </c>
       <c r="C230" s="0" t="inlineStr">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="G230" s="0" t="inlineStr">
         <is>
-          <t>2026-05-02 09:54:35</t>
+          <t>2026-05-03 23:56:37</t>
         </is>
       </c>
       <c r="H230" s="0" t="inlineStr">
@@ -13884,7 +13884,7 @@
       </c>
       <c r="I230" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音4</t>
+          <t>安迪-抖音6</t>
         </is>
       </c>
       <c r="J230" s="0" t="inlineStr">
@@ -13905,11 +13905,11 @@
     </row>
     <row r="231" spans="1:14">
       <c r="A231" s="0">
-        <v>45478798</v>
+        <v>45490798</v>
       </c>
       <c r="B231" s="0" t="inlineStr">
         <is>
-          <t>星星</t>
+          <t>青</t>
         </is>
       </c>
       <c r="C231" s="0" t="inlineStr">
@@ -13934,7 +13934,7 @@
       </c>
       <c r="G231" s="0" t="inlineStr">
         <is>
-          <t>2026-05-02 07:04:05</t>
+          <t>2026-05-02 16:18:11</t>
         </is>
       </c>
       <c r="H231" s="0" t="inlineStr">
@@ -13965,11 +13965,11 @@
     </row>
     <row r="232" spans="1:14">
       <c r="A232" s="0">
-        <v>45475623</v>
+        <v>45487466</v>
       </c>
       <c r="B232" s="0" t="inlineStr">
         <is>
-          <t>芹菜叶</t>
+          <t>夸夸妹</t>
         </is>
       </c>
       <c r="C232" s="0" t="inlineStr">
@@ -13994,7 +13994,7 @@
       </c>
       <c r="G232" s="0" t="inlineStr">
         <is>
-          <t>2026-05-02 00:16:27</t>
+          <t>2026-05-02 13:10:53</t>
         </is>
       </c>
       <c r="H232" s="0" t="inlineStr">
@@ -14025,11 +14025,11 @@
     </row>
     <row r="233" spans="1:14">
       <c r="A233" s="0">
-        <v>45473213</v>
+        <v>45487393</v>
       </c>
       <c r="B233" s="0" t="inlineStr">
         <is>
-          <t>🐠</t>
+          <t>乐悠悠</t>
         </is>
       </c>
       <c r="C233" s="0" t="inlineStr">
@@ -14054,7 +14054,7 @@
       </c>
       <c r="G233" s="0" t="inlineStr">
         <is>
-          <t>2026-05-01 21:39:09</t>
+          <t>2026-05-02 13:05:40</t>
         </is>
       </c>
       <c r="H233" s="0" t="inlineStr">
@@ -14064,7 +14064,7 @@
       </c>
       <c r="I233" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音6</t>
+          <t>安迪-抖音5</t>
         </is>
       </c>
       <c r="J233" s="0" t="inlineStr">
@@ -14085,11 +14085,11 @@
     </row>
     <row r="234" spans="1:14">
       <c r="A234" s="0">
-        <v>45464187</v>
+        <v>45487328</v>
       </c>
       <c r="B234" s="0" t="inlineStr">
         <is>
-          <t>萍萍</t>
+          <t>甘草</t>
         </is>
       </c>
       <c r="C234" s="0" t="inlineStr">
@@ -14114,7 +14114,7 @@
       </c>
       <c r="G234" s="0" t="inlineStr">
         <is>
-          <t>2026-05-01 13:44:43</t>
+          <t>2026-05-02 13:01:57</t>
         </is>
       </c>
       <c r="H234" s="0" t="inlineStr">
@@ -14140,16 +14140,21 @@
       <c r="L234" s="0" t="inlineStr">
         <is>
           <t>已完成</t>
+        </is>
+      </c>
+      <c r="N234" s="0" t="inlineStr">
+        <is>
+          <t>大同</t>
         </is>
       </c>
     </row>
     <row r="235" spans="1:14">
       <c r="A235" s="0">
-        <v>45461040</v>
+        <v>45487316</v>
       </c>
       <c r="B235" s="0" t="inlineStr">
         <is>
-          <t>高大为</t>
+          <t>苗妈家苗宝(5月26号生日)</t>
         </is>
       </c>
       <c r="C235" s="0" t="inlineStr">
@@ -14174,7 +14179,7 @@
       </c>
       <c r="G235" s="0" t="inlineStr">
         <is>
-          <t>2026-05-01 11:01:39</t>
+          <t>2026-05-02 13:01:11</t>
         </is>
       </c>
       <c r="H235" s="0" t="inlineStr">
@@ -14184,7 +14189,7 @@
       </c>
       <c r="I235" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音6</t>
+          <t>安迪-抖音5</t>
         </is>
       </c>
       <c r="J235" s="0" t="inlineStr">
@@ -14205,11 +14210,11 @@
     </row>
     <row r="236" spans="1:14">
       <c r="A236" s="0">
-        <v>45448208</v>
+        <v>45487303</v>
       </c>
       <c r="B236" s="0" t="inlineStr">
         <is>
-          <t>温暖</t>
+          <t>人生若只如初见</t>
         </is>
       </c>
       <c r="C236" s="0" t="inlineStr">
@@ -14234,7 +14239,7 @@
       </c>
       <c r="G236" s="0" t="inlineStr">
         <is>
-          <t>2026-04-30 21:37:15</t>
+          <t>2026-05-02 13:00:27</t>
         </is>
       </c>
       <c r="H236" s="0" t="inlineStr">
@@ -14244,7 +14249,7 @@
       </c>
       <c r="I236" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音6</t>
+          <t>安迪-抖音5</t>
         </is>
       </c>
       <c r="J236" s="0" t="inlineStr">
@@ -14265,11 +14270,11 @@
     </row>
     <row r="237" spans="1:14">
       <c r="A237" s="0">
-        <v>45447310</v>
+        <v>45487283</v>
       </c>
       <c r="B237" s="0" t="inlineStr">
         <is>
-          <t>Noob 豪</t>
+          <t>耶晓晓</t>
         </is>
       </c>
       <c r="C237" s="0" t="inlineStr">
@@ -14294,7 +14299,7 @@
       </c>
       <c r="G237" s="0" t="inlineStr">
         <is>
-          <t>2026-04-30 21:15:37</t>
+          <t>2026-05-02 12:59:23</t>
         </is>
       </c>
       <c r="H237" s="0" t="inlineStr">
@@ -14325,11 +14330,11 @@
     </row>
     <row r="238" spans="1:14">
       <c r="A238" s="0">
-        <v>45446718</v>
+        <v>45486981</v>
       </c>
       <c r="B238" s="0" t="inlineStr">
         <is>
-          <t>姗姗来迟</t>
+          <t>草青儿</t>
         </is>
       </c>
       <c r="C238" s="0" t="inlineStr">
@@ -14354,7 +14359,7 @@
       </c>
       <c r="G238" s="0" t="inlineStr">
         <is>
-          <t>2026-04-30 21:00:03</t>
+          <t>2026-05-02 12:43:01</t>
         </is>
       </c>
       <c r="H238" s="0" t="inlineStr">
@@ -14385,11 +14390,11 @@
     </row>
     <row r="239" spans="1:14">
       <c r="A239" s="0">
-        <v>45446658</v>
+        <v>45486967</v>
       </c>
       <c r="B239" s="0" t="inlineStr">
         <is>
-          <t>陈友学</t>
+          <t>向阳而生</t>
         </is>
       </c>
       <c r="C239" s="0" t="inlineStr">
@@ -14414,7 +14419,7 @@
       </c>
       <c r="G239" s="0" t="inlineStr">
         <is>
-          <t>2026-04-30 20:58:53</t>
+          <t>2026-05-02 12:41:47</t>
         </is>
       </c>
       <c r="H239" s="0" t="inlineStr">
@@ -14445,11 +14450,11 @@
     </row>
     <row r="240" spans="1:14">
       <c r="A240" s="0">
-        <v>45446181</v>
+        <v>45483029</v>
       </c>
       <c r="B240" s="0" t="inlineStr">
         <is>
-          <t>张</t>
+          <t>静</t>
         </is>
       </c>
       <c r="C240" s="0" t="inlineStr">
@@ -14474,7 +14479,7 @@
       </c>
       <c r="G240" s="0" t="inlineStr">
         <is>
-          <t>2026-04-30 20:47:17</t>
+          <t>2026-05-02 09:54:35</t>
         </is>
       </c>
       <c r="H240" s="0" t="inlineStr">
@@ -14484,7 +14489,7 @@
       </c>
       <c r="I240" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音5</t>
+          <t>安迪-抖音4</t>
         </is>
       </c>
       <c r="J240" s="0" t="inlineStr">
@@ -14505,11 +14510,11 @@
     </row>
     <row r="241" spans="1:14">
       <c r="A241" s="0">
-        <v>45440506</v>
+        <v>45478798</v>
       </c>
       <c r="B241" s="0" t="inlineStr">
         <is>
-          <t>蓬莱松</t>
+          <t>星星</t>
         </is>
       </c>
       <c r="C241" s="0" t="inlineStr">
@@ -14534,7 +14539,7 @@
       </c>
       <c r="G241" s="0" t="inlineStr">
         <is>
-          <t>2026-04-30 17:28:05</t>
+          <t>2026-05-02 07:04:05</t>
         </is>
       </c>
       <c r="H241" s="0" t="inlineStr">
@@ -14565,11 +14570,11 @@
     </row>
     <row r="242" spans="1:14">
       <c r="A242" s="0">
-        <v>45435499</v>
+        <v>45475623</v>
       </c>
       <c r="B242" s="0" t="inlineStr">
         <is>
-          <t>偶成</t>
+          <t>芹菜叶</t>
         </is>
       </c>
       <c r="C242" s="0" t="inlineStr">
@@ -14594,7 +14599,7 @@
       </c>
       <c r="G242" s="0" t="inlineStr">
         <is>
-          <t>2026-04-30 14:42:39</t>
+          <t>2026-05-02 00:16:27</t>
         </is>
       </c>
       <c r="H242" s="0" t="inlineStr">
@@ -14604,7 +14609,7 @@
       </c>
       <c r="I242" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音6</t>
+          <t>安迪-抖音5</t>
         </is>
       </c>
       <c r="J242" s="0" t="inlineStr">
@@ -14625,11 +14630,11 @@
     </row>
     <row r="243" spans="1:14">
       <c r="A243" s="0">
-        <v>45435397</v>
+        <v>45473213</v>
       </c>
       <c r="B243" s="0" t="inlineStr">
         <is>
-          <t>顺势而为</t>
+          <t>🐠</t>
         </is>
       </c>
       <c r="C243" s="0" t="inlineStr">
@@ -14654,7 +14659,7 @@
       </c>
       <c r="G243" s="0" t="inlineStr">
         <is>
-          <t>2026-04-30 14:40:21</t>
+          <t>2026-05-01 21:39:09</t>
         </is>
       </c>
       <c r="H243" s="0" t="inlineStr">
@@ -14685,11 +14690,11 @@
     </row>
     <row r="244" spans="1:14">
       <c r="A244" s="0">
-        <v>45431491</v>
+        <v>45464187</v>
       </c>
       <c r="B244" s="0" t="inlineStr">
         <is>
-          <t>🇨🇳 一马当先 万马奔腾</t>
+          <t>萍萍</t>
         </is>
       </c>
       <c r="C244" s="0" t="inlineStr">
@@ -14714,7 +14719,7 @@
       </c>
       <c r="G244" s="0" t="inlineStr">
         <is>
-          <t>2026-04-30 13:15:42</t>
+          <t>2026-05-01 13:44:43</t>
         </is>
       </c>
       <c r="H244" s="0" t="inlineStr">
@@ -14745,11 +14750,11 @@
     </row>
     <row r="245" spans="1:14">
       <c r="A245" s="0">
-        <v>45431124</v>
+        <v>45461040</v>
       </c>
       <c r="B245" s="0" t="inlineStr">
         <is>
-          <t>阳光</t>
+          <t>高大为</t>
         </is>
       </c>
       <c r="C245" s="0" t="inlineStr">
@@ -14774,7 +14779,7 @@
       </c>
       <c r="G245" s="0" t="inlineStr">
         <is>
-          <t>2026-04-30 12:58:49</t>
+          <t>2026-05-01 11:01:39</t>
         </is>
       </c>
       <c r="H245" s="0" t="inlineStr">
@@ -14784,7 +14789,7 @@
       </c>
       <c r="I245" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音5</t>
+          <t>安迪-抖音6</t>
         </is>
       </c>
       <c r="J245" s="0" t="inlineStr">
@@ -14805,11 +14810,11 @@
     </row>
     <row r="246" spans="1:14">
       <c r="A246" s="0">
-        <v>45430897</v>
+        <v>45448208</v>
       </c>
       <c r="B246" s="0" t="inlineStr">
         <is>
-          <t>青囊形理®易医研学社</t>
+          <t>温暖</t>
         </is>
       </c>
       <c r="C246" s="0" t="inlineStr">
@@ -14834,7 +14839,7 @@
       </c>
       <c r="G246" s="0" t="inlineStr">
         <is>
-          <t>2026-04-30 12:48:39</t>
+          <t>2026-04-30 21:37:15</t>
         </is>
       </c>
       <c r="H246" s="0" t="inlineStr">
@@ -14844,7 +14849,7 @@
       </c>
       <c r="I246" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音5</t>
+          <t>安迪-抖音6</t>
         </is>
       </c>
       <c r="J246" s="0" t="inlineStr">
@@ -14865,11 +14870,11 @@
     </row>
     <row r="247" spans="1:14">
       <c r="A247" s="0">
-        <v>45430869</v>
+        <v>45447310</v>
       </c>
       <c r="B247" s="0" t="inlineStr">
         <is>
-          <t>好运莲莲</t>
+          <t>Noob 豪</t>
         </is>
       </c>
       <c r="C247" s="0" t="inlineStr">
@@ -14894,7 +14899,7 @@
       </c>
       <c r="G247" s="0" t="inlineStr">
         <is>
-          <t>2026-04-30 12:47:25</t>
+          <t>2026-04-30 21:15:37</t>
         </is>
       </c>
       <c r="H247" s="0" t="inlineStr">
@@ -14925,11 +14930,11 @@
     </row>
     <row r="248" spans="1:14">
       <c r="A248" s="0">
-        <v>45430806</v>
+        <v>45446718</v>
       </c>
       <c r="B248" s="0" t="inlineStr">
         <is>
-          <t>毛毛</t>
+          <t>姗姗来迟</t>
         </is>
       </c>
       <c r="C248" s="0" t="inlineStr">
@@ -14954,7 +14959,7 @@
       </c>
       <c r="G248" s="0" t="inlineStr">
         <is>
-          <t>2026-04-30 12:45:21</t>
+          <t>2026-04-30 21:00:03</t>
         </is>
       </c>
       <c r="H248" s="0" t="inlineStr">
@@ -14985,11 +14990,11 @@
     </row>
     <row r="249" spans="1:14">
       <c r="A249" s="0">
-        <v>45427878</v>
+        <v>45446658</v>
       </c>
       <c r="B249" s="0" t="inlineStr">
         <is>
-          <t>李俊</t>
+          <t>陈友学</t>
         </is>
       </c>
       <c r="C249" s="0" t="inlineStr">
@@ -15014,7 +15019,7 @@
       </c>
       <c r="G249" s="0" t="inlineStr">
         <is>
-          <t>2026-04-30 10:44:25</t>
+          <t>2026-04-30 20:58:53</t>
         </is>
       </c>
       <c r="H249" s="0" t="inlineStr">
@@ -15024,7 +15029,7 @@
       </c>
       <c r="I249" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音6</t>
+          <t>安迪-抖音5</t>
         </is>
       </c>
       <c r="J249" s="0" t="inlineStr">
@@ -15045,11 +15050,11 @@
     </row>
     <row r="250" spans="1:14">
       <c r="A250" s="0">
-        <v>45421150</v>
+        <v>45446181</v>
       </c>
       <c r="B250" s="0" t="inlineStr">
         <is>
-          <t>龙要水护</t>
+          <t>张</t>
         </is>
       </c>
       <c r="C250" s="0" t="inlineStr">
@@ -15074,7 +15079,7 @@
       </c>
       <c r="G250" s="0" t="inlineStr">
         <is>
-          <t>2026-04-30 05:47:24</t>
+          <t>2026-04-30 20:47:17</t>
         </is>
       </c>
       <c r="H250" s="0" t="inlineStr">
@@ -15084,7 +15089,7 @@
       </c>
       <c r="I250" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音1</t>
+          <t>安迪-抖音5</t>
         </is>
       </c>
       <c r="J250" s="0" t="inlineStr">
@@ -15105,11 +15110,11 @@
     </row>
     <row r="251" spans="1:14">
       <c r="A251" s="0">
-        <v>45415785</v>
+        <v>45440506</v>
       </c>
       <c r="B251" s="0" t="inlineStr">
         <is>
-          <t>董红平</t>
+          <t>蓬莱松</t>
         </is>
       </c>
       <c r="C251" s="0" t="inlineStr">
@@ -15134,7 +15139,7 @@
       </c>
       <c r="G251" s="0" t="inlineStr">
         <is>
-          <t>2026-04-29 21:35:43</t>
+          <t>2026-04-30 17:28:05</t>
         </is>
       </c>
       <c r="H251" s="0" t="inlineStr">
@@ -15144,7 +15149,7 @@
       </c>
       <c r="I251" s="0" t="inlineStr">
         <is>
-          <t>安迪-抖音6</t>
+          <t>安迪-抖音5</t>
         </is>
       </c>
       <c r="J251" s="0" t="inlineStr">
@@ -15160,69 +15165,669 @@
       <c r="L251" s="0" t="inlineStr">
         <is>
           <t>已完成</t>
-        </is>
-      </c>
-      <c r="N251" s="0" t="inlineStr">
-        <is>
-          <t>六盘水</t>
         </is>
       </c>
     </row>
     <row r="252" spans="1:14">
       <c r="A252" s="0">
+        <v>45435499</v>
+      </c>
+      <c r="B252" s="0" t="inlineStr">
+        <is>
+          <t>偶成</t>
+        </is>
+      </c>
+      <c r="C252" s="0" t="inlineStr">
+        <is>
+          <t>6天0基础钢琴入门课</t>
+        </is>
+      </c>
+      <c r="D252" s="0" t="inlineStr">
+        <is>
+          <t>训练营</t>
+        </is>
+      </c>
+      <c r="E252" s="0" t="inlineStr">
+        <is>
+          <t>￥0</t>
+        </is>
+      </c>
+      <c r="F252" s="0" t="inlineStr">
+        <is>
+          <t>￥0</t>
+        </is>
+      </c>
+      <c r="G252" s="0" t="inlineStr">
+        <is>
+          <t>2026-04-30 14:42:39</t>
+        </is>
+      </c>
+      <c r="H252" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I252" s="0" t="inlineStr">
+        <is>
+          <t>安迪-抖音6</t>
+        </is>
+      </c>
+      <c r="J252" s="0" t="inlineStr">
+        <is>
+          <t>安迪钢琴-获客助手专用</t>
+        </is>
+      </c>
+      <c r="K252" s="0" t="inlineStr">
+        <is>
+          <t>获客助手加好友</t>
+        </is>
+      </c>
+      <c r="L252" s="0" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="253" spans="1:14">
+      <c r="A253" s="0">
+        <v>45435397</v>
+      </c>
+      <c r="B253" s="0" t="inlineStr">
+        <is>
+          <t>顺势而为</t>
+        </is>
+      </c>
+      <c r="C253" s="0" t="inlineStr">
+        <is>
+          <t>6天0基础钢琴入门课</t>
+        </is>
+      </c>
+      <c r="D253" s="0" t="inlineStr">
+        <is>
+          <t>训练营</t>
+        </is>
+      </c>
+      <c r="E253" s="0" t="inlineStr">
+        <is>
+          <t>￥0</t>
+        </is>
+      </c>
+      <c r="F253" s="0" t="inlineStr">
+        <is>
+          <t>￥0</t>
+        </is>
+      </c>
+      <c r="G253" s="0" t="inlineStr">
+        <is>
+          <t>2026-04-30 14:40:21</t>
+        </is>
+      </c>
+      <c r="H253" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I253" s="0" t="inlineStr">
+        <is>
+          <t>安迪-抖音6</t>
+        </is>
+      </c>
+      <c r="J253" s="0" t="inlineStr">
+        <is>
+          <t>安迪钢琴-获客助手专用</t>
+        </is>
+      </c>
+      <c r="K253" s="0" t="inlineStr">
+        <is>
+          <t>获客助手加好友</t>
+        </is>
+      </c>
+      <c r="L253" s="0" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="254" spans="1:14">
+      <c r="A254" s="0">
+        <v>45431491</v>
+      </c>
+      <c r="B254" s="0" t="inlineStr">
+        <is>
+          <t>🇨🇳 一马当先 万马奔腾</t>
+        </is>
+      </c>
+      <c r="C254" s="0" t="inlineStr">
+        <is>
+          <t>6天0基础钢琴入门课</t>
+        </is>
+      </c>
+      <c r="D254" s="0" t="inlineStr">
+        <is>
+          <t>训练营</t>
+        </is>
+      </c>
+      <c r="E254" s="0" t="inlineStr">
+        <is>
+          <t>￥0</t>
+        </is>
+      </c>
+      <c r="F254" s="0" t="inlineStr">
+        <is>
+          <t>￥0</t>
+        </is>
+      </c>
+      <c r="G254" s="0" t="inlineStr">
+        <is>
+          <t>2026-04-30 13:15:42</t>
+        </is>
+      </c>
+      <c r="H254" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I254" s="0" t="inlineStr">
+        <is>
+          <t>安迪-抖音5</t>
+        </is>
+      </c>
+      <c r="J254" s="0" t="inlineStr">
+        <is>
+          <t>安迪钢琴-获客助手专用</t>
+        </is>
+      </c>
+      <c r="K254" s="0" t="inlineStr">
+        <is>
+          <t>获客助手加好友</t>
+        </is>
+      </c>
+      <c r="L254" s="0" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="255" spans="1:14">
+      <c r="A255" s="0">
+        <v>45431124</v>
+      </c>
+      <c r="B255" s="0" t="inlineStr">
+        <is>
+          <t>阳光</t>
+        </is>
+      </c>
+      <c r="C255" s="0" t="inlineStr">
+        <is>
+          <t>6天0基础钢琴入门课</t>
+        </is>
+      </c>
+      <c r="D255" s="0" t="inlineStr">
+        <is>
+          <t>训练营</t>
+        </is>
+      </c>
+      <c r="E255" s="0" t="inlineStr">
+        <is>
+          <t>￥0</t>
+        </is>
+      </c>
+      <c r="F255" s="0" t="inlineStr">
+        <is>
+          <t>￥0</t>
+        </is>
+      </c>
+      <c r="G255" s="0" t="inlineStr">
+        <is>
+          <t>2026-04-30 12:58:49</t>
+        </is>
+      </c>
+      <c r="H255" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I255" s="0" t="inlineStr">
+        <is>
+          <t>安迪-抖音5</t>
+        </is>
+      </c>
+      <c r="J255" s="0" t="inlineStr">
+        <is>
+          <t>安迪钢琴-获客助手专用</t>
+        </is>
+      </c>
+      <c r="K255" s="0" t="inlineStr">
+        <is>
+          <t>获客助手加好友</t>
+        </is>
+      </c>
+      <c r="L255" s="0" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="256" spans="1:14">
+      <c r="A256" s="0">
+        <v>45430897</v>
+      </c>
+      <c r="B256" s="0" t="inlineStr">
+        <is>
+          <t>青囊形理®易医研学社</t>
+        </is>
+      </c>
+      <c r="C256" s="0" t="inlineStr">
+        <is>
+          <t>6天0基础钢琴入门课</t>
+        </is>
+      </c>
+      <c r="D256" s="0" t="inlineStr">
+        <is>
+          <t>训练营</t>
+        </is>
+      </c>
+      <c r="E256" s="0" t="inlineStr">
+        <is>
+          <t>￥0</t>
+        </is>
+      </c>
+      <c r="F256" s="0" t="inlineStr">
+        <is>
+          <t>￥0</t>
+        </is>
+      </c>
+      <c r="G256" s="0" t="inlineStr">
+        <is>
+          <t>2026-04-30 12:48:39</t>
+        </is>
+      </c>
+      <c r="H256" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I256" s="0" t="inlineStr">
+        <is>
+          <t>安迪-抖音5</t>
+        </is>
+      </c>
+      <c r="J256" s="0" t="inlineStr">
+        <is>
+          <t>安迪钢琴-获客助手专用</t>
+        </is>
+      </c>
+      <c r="K256" s="0" t="inlineStr">
+        <is>
+          <t>获客助手加好友</t>
+        </is>
+      </c>
+      <c r="L256" s="0" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="257" spans="1:14">
+      <c r="A257" s="0">
+        <v>45430869</v>
+      </c>
+      <c r="B257" s="0" t="inlineStr">
+        <is>
+          <t>好运莲莲</t>
+        </is>
+      </c>
+      <c r="C257" s="0" t="inlineStr">
+        <is>
+          <t>6天0基础钢琴入门课</t>
+        </is>
+      </c>
+      <c r="D257" s="0" t="inlineStr">
+        <is>
+          <t>训练营</t>
+        </is>
+      </c>
+      <c r="E257" s="0" t="inlineStr">
+        <is>
+          <t>￥0</t>
+        </is>
+      </c>
+      <c r="F257" s="0" t="inlineStr">
+        <is>
+          <t>￥0</t>
+        </is>
+      </c>
+      <c r="G257" s="0" t="inlineStr">
+        <is>
+          <t>2026-04-30 12:47:25</t>
+        </is>
+      </c>
+      <c r="H257" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I257" s="0" t="inlineStr">
+        <is>
+          <t>安迪-抖音5</t>
+        </is>
+      </c>
+      <c r="J257" s="0" t="inlineStr">
+        <is>
+          <t>安迪钢琴-获客助手专用</t>
+        </is>
+      </c>
+      <c r="K257" s="0" t="inlineStr">
+        <is>
+          <t>获客助手加好友</t>
+        </is>
+      </c>
+      <c r="L257" s="0" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="258" spans="1:14">
+      <c r="A258" s="0">
+        <v>45430806</v>
+      </c>
+      <c r="B258" s="0" t="inlineStr">
+        <is>
+          <t>毛毛</t>
+        </is>
+      </c>
+      <c r="C258" s="0" t="inlineStr">
+        <is>
+          <t>6天0基础钢琴入门课</t>
+        </is>
+      </c>
+      <c r="D258" s="0" t="inlineStr">
+        <is>
+          <t>训练营</t>
+        </is>
+      </c>
+      <c r="E258" s="0" t="inlineStr">
+        <is>
+          <t>￥0</t>
+        </is>
+      </c>
+      <c r="F258" s="0" t="inlineStr">
+        <is>
+          <t>￥0</t>
+        </is>
+      </c>
+      <c r="G258" s="0" t="inlineStr">
+        <is>
+          <t>2026-04-30 12:45:21</t>
+        </is>
+      </c>
+      <c r="H258" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I258" s="0" t="inlineStr">
+        <is>
+          <t>安迪-抖音5</t>
+        </is>
+      </c>
+      <c r="J258" s="0" t="inlineStr">
+        <is>
+          <t>安迪钢琴-获客助手专用</t>
+        </is>
+      </c>
+      <c r="K258" s="0" t="inlineStr">
+        <is>
+          <t>获客助手加好友</t>
+        </is>
+      </c>
+      <c r="L258" s="0" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="259" spans="1:14">
+      <c r="A259" s="0">
+        <v>45427878</v>
+      </c>
+      <c r="B259" s="0" t="inlineStr">
+        <is>
+          <t>李俊</t>
+        </is>
+      </c>
+      <c r="C259" s="0" t="inlineStr">
+        <is>
+          <t>6天0基础钢琴入门课</t>
+        </is>
+      </c>
+      <c r="D259" s="0" t="inlineStr">
+        <is>
+          <t>训练营</t>
+        </is>
+      </c>
+      <c r="E259" s="0" t="inlineStr">
+        <is>
+          <t>￥0</t>
+        </is>
+      </c>
+      <c r="F259" s="0" t="inlineStr">
+        <is>
+          <t>￥0</t>
+        </is>
+      </c>
+      <c r="G259" s="0" t="inlineStr">
+        <is>
+          <t>2026-04-30 10:44:25</t>
+        </is>
+      </c>
+      <c r="H259" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I259" s="0" t="inlineStr">
+        <is>
+          <t>安迪-抖音6</t>
+        </is>
+      </c>
+      <c r="J259" s="0" t="inlineStr">
+        <is>
+          <t>安迪钢琴-获客助手专用</t>
+        </is>
+      </c>
+      <c r="K259" s="0" t="inlineStr">
+        <is>
+          <t>获客助手加好友</t>
+        </is>
+      </c>
+      <c r="L259" s="0" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="260" spans="1:14">
+      <c r="A260" s="0">
+        <v>45421150</v>
+      </c>
+      <c r="B260" s="0" t="inlineStr">
+        <is>
+          <t>龙要水护</t>
+        </is>
+      </c>
+      <c r="C260" s="0" t="inlineStr">
+        <is>
+          <t>6天0基础钢琴入门课</t>
+        </is>
+      </c>
+      <c r="D260" s="0" t="inlineStr">
+        <is>
+          <t>训练营</t>
+        </is>
+      </c>
+      <c r="E260" s="0" t="inlineStr">
+        <is>
+          <t>￥0</t>
+        </is>
+      </c>
+      <c r="F260" s="0" t="inlineStr">
+        <is>
+          <t>￥0</t>
+        </is>
+      </c>
+      <c r="G260" s="0" t="inlineStr">
+        <is>
+          <t>2026-04-30 05:47:24</t>
+        </is>
+      </c>
+      <c r="H260" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I260" s="0" t="inlineStr">
+        <is>
+          <t>安迪-抖音1</t>
+        </is>
+      </c>
+      <c r="J260" s="0" t="inlineStr">
+        <is>
+          <t>安迪钢琴-获客助手专用</t>
+        </is>
+      </c>
+      <c r="K260" s="0" t="inlineStr">
+        <is>
+          <t>获客助手加好友</t>
+        </is>
+      </c>
+      <c r="L260" s="0" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="261" spans="1:14">
+      <c r="A261" s="0">
+        <v>45415785</v>
+      </c>
+      <c r="B261" s="0" t="inlineStr">
+        <is>
+          <t>董红平</t>
+        </is>
+      </c>
+      <c r="C261" s="0" t="inlineStr">
+        <is>
+          <t>6天0基础钢琴入门课</t>
+        </is>
+      </c>
+      <c r="D261" s="0" t="inlineStr">
+        <is>
+          <t>训练营</t>
+        </is>
+      </c>
+      <c r="E261" s="0" t="inlineStr">
+        <is>
+          <t>￥0</t>
+        </is>
+      </c>
+      <c r="F261" s="0" t="inlineStr">
+        <is>
+          <t>￥0</t>
+        </is>
+      </c>
+      <c r="G261" s="0" t="inlineStr">
+        <is>
+          <t>2026-04-29 21:35:43</t>
+        </is>
+      </c>
+      <c r="H261" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I261" s="0" t="inlineStr">
+        <is>
+          <t>安迪-抖音6</t>
+        </is>
+      </c>
+      <c r="J261" s="0" t="inlineStr">
+        <is>
+          <t>安迪钢琴-获客助手专用</t>
+        </is>
+      </c>
+      <c r="K261" s="0" t="inlineStr">
+        <is>
+          <t>获客助手加好友</t>
+        </is>
+      </c>
+      <c r="L261" s="0" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="N261" s="0" t="inlineStr">
+        <is>
+          <t>六盘水</t>
+        </is>
+      </c>
+    </row>
+    <row r="262" spans="1:14">
+      <c r="A262" s="0">
         <v>45413374</v>
       </c>
-      <c r="B252" s="0" t="inlineStr">
+      <c r="B262" s="0" t="inlineStr">
         <is>
           <t>SIHAP</t>
         </is>
       </c>
-      <c r="C252" s="0" t="inlineStr">
-        <is>
-          <t>6天0基础钢琴入门课</t>
-        </is>
-      </c>
-      <c r="D252" s="0" t="inlineStr">
-        <is>
-          <t>训练营</t>
-        </is>
-      </c>
-      <c r="E252" s="0" t="inlineStr">
-        <is>
-          <t>￥0</t>
-        </is>
-      </c>
-      <c r="F252" s="0" t="inlineStr">
-        <is>
-          <t>￥0</t>
-        </is>
-      </c>
-      <c r="G252" s="0" t="inlineStr">
+      <c r="C262" s="0" t="inlineStr">
+        <is>
+          <t>6天0基础钢琴入门课</t>
+        </is>
+      </c>
+      <c r="D262" s="0" t="inlineStr">
+        <is>
+          <t>训练营</t>
+        </is>
+      </c>
+      <c r="E262" s="0" t="inlineStr">
+        <is>
+          <t>￥0</t>
+        </is>
+      </c>
+      <c r="F262" s="0" t="inlineStr">
+        <is>
+          <t>￥0</t>
+        </is>
+      </c>
+      <c r="G262" s="0" t="inlineStr">
         <is>
           <t>2026-04-29 20:39:53</t>
         </is>
       </c>
-      <c r="H252" s="0" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I252" s="0" t="inlineStr">
+      <c r="H262" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I262" s="0" t="inlineStr">
         <is>
           <t>安迪-抖音1</t>
         </is>
       </c>
-      <c r="J252" s="0" t="inlineStr">
-        <is>
-          <t>安迪钢琴-获客助手专用</t>
-        </is>
-      </c>
-      <c r="K252" s="0" t="inlineStr">
-        <is>
-          <t>获客助手加好友</t>
-        </is>
-      </c>
-      <c r="L252" s="0" t="inlineStr">
+      <c r="J262" s="0" t="inlineStr">
+        <is>
+          <t>安迪钢琴-获客助手专用</t>
+        </is>
+      </c>
+      <c r="K262" s="0" t="inlineStr">
+        <is>
+          <t>获客助手加好友</t>
+        </is>
+      </c>
+      <c r="L262" s="0" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
